--- a/PensumOriginal1.xlsx
+++ b/PensumOriginal1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE5552D2-A124-4B1F-9CCE-A4EB11601B47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97FC5CE0-D682-4210-8912-4A1DEDB3FEE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="404" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" tabRatio="404" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Actual" sheetId="11" r:id="rId1"/>
@@ -25,6 +25,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1075,23 +1078,17 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1105,29 +1102,35 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2548,15 +2551,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>386074</xdr:colOff>
+      <xdr:colOff>405512</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>19422</xdr:rowOff>
+      <xdr:rowOff>38860</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>62224</xdr:colOff>
+      <xdr:colOff>81662</xdr:colOff>
       <xdr:row>53</xdr:row>
-      <xdr:rowOff>40780</xdr:rowOff>
+      <xdr:rowOff>60218</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2571,8 +2574,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1336100" y="9084253"/>
-          <a:ext cx="1457449" cy="1189098"/>
+          <a:off x="1319134" y="9797125"/>
+          <a:ext cx="1415921" cy="1275159"/>
         </a:xfrm>
         <a:prstGeom prst="mathMultiply">
           <a:avLst/>
@@ -3068,8 +3071,8 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="7030A0">
-            <a:alpha val="58000"/>
+          <a:srgbClr val="C00000">
+            <a:alpha val="34000"/>
           </a:srgbClr>
         </a:solidFill>
       </xdr:spPr>
@@ -3140,8 +3143,8 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="7030A0">
-            <a:alpha val="58000"/>
+          <a:srgbClr val="C00000">
+            <a:alpha val="34000"/>
           </a:srgbClr>
         </a:solidFill>
       </xdr:spPr>
@@ -3174,73 +3177,6 @@
             <a:ea typeface="+mn-ea"/>
             <a:cs typeface="+mn-cs"/>
           </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>160244</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>77246</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>316354</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>156475</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="37" name="Signo de multiplicación 36">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1A71D9F-9E01-4A43-935D-46306B662DEA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10640218" y="6153454"/>
-          <a:ext cx="1462396" cy="1207385"/>
-        </a:xfrm>
-        <a:prstGeom prst="mathMultiply">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-            <a:alpha val="58000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="es-ES" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -3279,8 +3215,8 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="7030A0">
-            <a:alpha val="58000"/>
+          <a:srgbClr val="C00000">
+            <a:alpha val="34000"/>
           </a:srgbClr>
         </a:solidFill>
       </xdr:spPr>
@@ -3304,8 +3240,15 @@
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="es-ES" sz="1100"/>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -3344,8 +3287,8 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="7030A0">
-            <a:alpha val="58000"/>
+          <a:srgbClr val="C00000">
+            <a:alpha val="34000"/>
           </a:srgbClr>
         </a:solidFill>
       </xdr:spPr>
@@ -3458,15 +3401,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>95044</xdr:colOff>
+      <xdr:colOff>38879</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>141638</xdr:rowOff>
+      <xdr:rowOff>58318</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>13400</xdr:colOff>
+      <xdr:colOff>168912</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>55913</xdr:rowOff>
+      <xdr:rowOff>94792</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3481,8 +3424,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7160862" y="3991222"/>
-          <a:ext cx="1076200" cy="824717"/>
+          <a:off x="6900767" y="4227935"/>
+          <a:ext cx="1257482" cy="1027852"/>
         </a:xfrm>
         <a:prstGeom prst="mathMultiply">
           <a:avLst/>
@@ -3862,15 +3805,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>242324</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>32164</xdr:rowOff>
+      <xdr:colOff>417273</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>187674</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>93803</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>54145</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>84083</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>219374</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3885,8 +3828,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1192350" y="8127177"/>
-          <a:ext cx="1454648" cy="1179825"/>
+          <a:off x="1330895" y="8458873"/>
+          <a:ext cx="1406581" cy="1266062"/>
         </a:xfrm>
         <a:prstGeom prst="mathMultiply">
           <a:avLst/>
@@ -3934,15 +3877,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>431779</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>77346</xdr:rowOff>
+      <xdr:colOff>422060</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>174539</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>107155</xdr:colOff>
+      <xdr:colOff>97436</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>148708</xdr:rowOff>
+      <xdr:rowOff>32075</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3957,15 +3900,15 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9308584" y="2818567"/>
-          <a:ext cx="1456675" cy="1179725"/>
+          <a:off x="9052876" y="2925126"/>
+          <a:ext cx="1415147" cy="1276566"/>
         </a:xfrm>
         <a:prstGeom prst="mathMultiply">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="7030A0">
-            <a:alpha val="58000"/>
+          <a:srgbClr val="C00000">
+            <a:alpha val="34000"/>
           </a:srgbClr>
         </a:solidFill>
       </xdr:spPr>
@@ -4008,13 +3951,13 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>399928</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>43172</xdr:rowOff>
+      <xdr:rowOff>169525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>76078</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>123906</xdr:rowOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>36433</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4029,8 +3972,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1349954" y="10077821"/>
-          <a:ext cx="1457449" cy="1189098"/>
+          <a:off x="1313550" y="10967765"/>
+          <a:ext cx="1415921" cy="1285938"/>
         </a:xfrm>
         <a:prstGeom prst="mathMultiply">
           <a:avLst/>
@@ -4078,15 +4021,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>403885</xdr:colOff>
+      <xdr:colOff>394165</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>47131</xdr:rowOff>
+      <xdr:rowOff>144325</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>80035</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>127865</xdr:rowOff>
+      <xdr:colOff>70315</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>11233</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4101,15 +4044,15 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2482067" y="10081780"/>
-          <a:ext cx="1457449" cy="1189098"/>
+          <a:off x="2406078" y="10942565"/>
+          <a:ext cx="1415921" cy="1285938"/>
         </a:xfrm>
         <a:prstGeom prst="mathMultiply">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="7030A0">
-            <a:alpha val="58000"/>
+          <a:srgbClr val="C00000">
+            <a:alpha val="34000"/>
           </a:srgbClr>
         </a:solidFill>
       </xdr:spPr>
@@ -4150,15 +4093,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>395843</xdr:colOff>
+      <xdr:colOff>415281</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>39585</xdr:rowOff>
+      <xdr:rowOff>156218</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>54766</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>128755</xdr:rowOff>
+      <xdr:colOff>74204</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>31562</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4173,8 +4116,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4730337" y="10074234"/>
-          <a:ext cx="1440221" cy="1197534"/>
+          <a:off x="4623776" y="10954458"/>
+          <a:ext cx="1398693" cy="1294374"/>
         </a:xfrm>
         <a:prstGeom prst="mathMultiply">
           <a:avLst/>
@@ -4214,16 +4157,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>23750</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>383366</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>201880</xdr:rowOff>
+      <xdr:rowOff>182441</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>157685</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>4064</xdr:rowOff>
+      <xdr:colOff>60490</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>237329</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4238,8 +4181,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2576945" y="7871361"/>
-          <a:ext cx="1440221" cy="1197534"/>
+          <a:off x="2395279" y="8453640"/>
+          <a:ext cx="1416895" cy="1289250"/>
         </a:xfrm>
         <a:prstGeom prst="mathMultiply">
           <a:avLst/>
@@ -4279,16 +4222,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>27709</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>367888</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>225630</xdr:rowOff>
+      <xdr:rowOff>235349</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>161644</xdr:colOff>
+      <xdr:colOff>45012</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>27814</xdr:rowOff>
+      <xdr:rowOff>37533</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4303,8 +4246,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4837215" y="7895111"/>
-          <a:ext cx="1440221" cy="1197534"/>
+          <a:off x="4576383" y="8506548"/>
+          <a:ext cx="1416894" cy="1289250"/>
         </a:xfrm>
         <a:prstGeom prst="mathMultiply">
           <a:avLst/>
@@ -4345,13 +4288,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>397822</xdr:colOff>
+      <xdr:colOff>378383</xdr:colOff>
       <xdr:row>46</xdr:row>
       <xdr:rowOff>229588</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>56745</xdr:colOff>
+      <xdr:colOff>37306</xdr:colOff>
       <xdr:row>53</xdr:row>
       <xdr:rowOff>11980</xdr:rowOff>
     </xdr:to>
@@ -4368,8 +4311,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3604160" y="9047017"/>
-          <a:ext cx="1440221" cy="1197534"/>
+          <a:off x="3488587" y="9735149"/>
+          <a:ext cx="1398693" cy="1288897"/>
         </a:xfrm>
         <a:prstGeom prst="mathMultiply">
           <a:avLst/>
@@ -4810,15 +4753,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>356258</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>168233</xdr:rowOff>
+      <xdr:colOff>395136</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>226550</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>37356</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>29748</xdr:rowOff>
+      <xdr:colOff>76234</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>49187</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4833,8 +4776,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3562596" y="8075220"/>
-          <a:ext cx="1462396" cy="1207385"/>
+          <a:off x="3505340" y="8497749"/>
+          <a:ext cx="1420868" cy="1309703"/>
         </a:xfrm>
         <a:prstGeom prst="mathMultiply">
           <a:avLst/>
@@ -4877,15 +4820,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>350321</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>142504</xdr:rowOff>
+      <xdr:colOff>398918</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>181381</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>31418</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>182149</xdr:rowOff>
+      <xdr:colOff>80015</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>182148</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4900,8 +4843,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2428503" y="9207335"/>
-          <a:ext cx="1462396" cy="1207385"/>
+          <a:off x="2410831" y="9686942"/>
+          <a:ext cx="1420868" cy="1293446"/>
         </a:xfrm>
         <a:prstGeom prst="mathMultiply">
           <a:avLst/>
@@ -4912,6 +4855,266 @@
             <a:lumOff val="80000"/>
             <a:alpha val="58000"/>
           </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>419839</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>154117</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>100936</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>35424</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="60" name="Signo de multiplicación 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6F00A2D-2EBD-446F-ACF6-909294B7D78B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10148946" y="5315112"/>
+          <a:ext cx="1420868" cy="1300338"/>
+        </a:xfrm>
+        <a:prstGeom prst="mathMultiply">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="7030A0">
+            <a:alpha val="58000"/>
+          </a:srgbClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>436168</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>160726</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>117265</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>42034</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="61" name="Signo de multiplicación 60">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59848488-7775-4955-BF22-D03D5C7E02F2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10165275" y="4116517"/>
+          <a:ext cx="1420868" cy="1300338"/>
+        </a:xfrm>
+        <a:prstGeom prst="mathMultiply">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="7030A0">
+            <a:alpha val="58000"/>
+          </a:srgbClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>384461</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>206212</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>65558</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>87520</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="62" name="Signo de multiplicación 61">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F4E8883-DC01-43E4-8A63-21FB85581689}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10113568" y="2956799"/>
+          <a:ext cx="1420868" cy="1300338"/>
+        </a:xfrm>
+        <a:prstGeom prst="mathMultiply">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="7030A0">
+            <a:alpha val="58000"/>
+          </a:srgbClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>361912</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>144785</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>43009</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>35812</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="63" name="Signo de multiplicación 62">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C45CF3F8-69ED-4C2E-9280-6A67CD84417F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10091019" y="1699887"/>
+          <a:ext cx="1420868" cy="1300338"/>
+        </a:xfrm>
+        <a:prstGeom prst="mathMultiply">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="7030A0">
+            <a:alpha val="58000"/>
+          </a:srgbClr>
         </a:solidFill>
       </xdr:spPr>
       <xdr:style>
@@ -4945,9 +5148,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4985,9 +5188,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -5020,9 +5223,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -5055,9 +5275,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5232,34 +5469,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AI59"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="6.88671875" customWidth="1"/>
-    <col min="4" max="4" width="2.6640625" customWidth="1"/>
-    <col min="5" max="6" width="6.88671875" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" customWidth="1"/>
-    <col min="8" max="9" width="6.88671875" customWidth="1"/>
-    <col min="10" max="10" width="2.6640625" customWidth="1"/>
-    <col min="11" max="12" width="6.88671875" customWidth="1"/>
-    <col min="13" max="13" width="2.6640625" customWidth="1"/>
-    <col min="14" max="15" width="6.88671875" customWidth="1"/>
-    <col min="16" max="16" width="2.6640625" customWidth="1"/>
-    <col min="17" max="18" width="6.88671875" customWidth="1"/>
-    <col min="19" max="19" width="2.6640625" customWidth="1"/>
-    <col min="20" max="20" width="6.88671875" customWidth="1"/>
-    <col min="21" max="21" width="7.33203125" customWidth="1"/>
-    <col min="22" max="22" width="2.6640625" customWidth="1"/>
-    <col min="23" max="24" width="6.88671875" customWidth="1"/>
-    <col min="25" max="25" width="2.6640625" customWidth="1"/>
-    <col min="26" max="27" width="6.88671875" customWidth="1"/>
-    <col min="28" max="28" width="2.6640625" customWidth="1"/>
-    <col min="29" max="30" width="6.88671875" customWidth="1"/>
-    <col min="31" max="31" width="2.6640625" customWidth="1"/>
-    <col min="32" max="32" width="7.6640625" customWidth="1"/>
-    <col min="35" max="35" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="6.85546875" customWidth="1"/>
+    <col min="4" max="4" width="2.7109375" customWidth="1"/>
+    <col min="5" max="6" width="6.85546875" customWidth="1"/>
+    <col min="7" max="7" width="2.7109375" customWidth="1"/>
+    <col min="8" max="9" width="6.85546875" customWidth="1"/>
+    <col min="10" max="10" width="2.7109375" customWidth="1"/>
+    <col min="11" max="12" width="6.85546875" customWidth="1"/>
+    <col min="13" max="13" width="2.7109375" customWidth="1"/>
+    <col min="14" max="15" width="6.85546875" customWidth="1"/>
+    <col min="16" max="16" width="2.7109375" customWidth="1"/>
+    <col min="17" max="18" width="6.85546875" customWidth="1"/>
+    <col min="19" max="19" width="2.7109375" customWidth="1"/>
+    <col min="20" max="20" width="6.85546875" customWidth="1"/>
+    <col min="21" max="21" width="7.28515625" customWidth="1"/>
+    <col min="22" max="22" width="2.7109375" customWidth="1"/>
+    <col min="23" max="24" width="6.85546875" customWidth="1"/>
+    <col min="25" max="25" width="2.7109375" customWidth="1"/>
+    <col min="26" max="27" width="6.85546875" customWidth="1"/>
+    <col min="28" max="28" width="2.7109375" customWidth="1"/>
+    <col min="29" max="30" width="6.85546875" customWidth="1"/>
+    <col min="31" max="31" width="2.7109375" customWidth="1"/>
+    <col min="32" max="32" width="7.7109375" customWidth="1"/>
+    <col min="35" max="35" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" s="9"/>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -5294,156 +5531,156 @@
       <c r="AF1" s="9"/>
       <c r="AG1" s="9"/>
     </row>
-    <row r="2" spans="1:35" ht="18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="9"/>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
-      <c r="D2" s="50" t="s">
+      <c r="D2" s="34" t="s">
         <v>141</v>
       </c>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="50"/>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="50"/>
-      <c r="S2" s="50"/>
-      <c r="T2" s="50"/>
-      <c r="U2" s="50"/>
-      <c r="V2" s="50"/>
-      <c r="W2" s="50"/>
-      <c r="X2" s="50"/>
-      <c r="Y2" s="50"/>
-      <c r="Z2" s="50"/>
-      <c r="AA2" s="50"/>
-      <c r="AB2" s="50"/>
-      <c r="AC2" s="50"/>
-      <c r="AD2" s="50"/>
-      <c r="AE2" s="50"/>
-      <c r="AF2" s="50"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
+      <c r="N2" s="34"/>
+      <c r="O2" s="34"/>
+      <c r="P2" s="34"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
+      <c r="T2" s="34"/>
+      <c r="U2" s="34"/>
+      <c r="V2" s="34"/>
+      <c r="W2" s="34"/>
+      <c r="X2" s="34"/>
+      <c r="Y2" s="34"/>
+      <c r="Z2" s="34"/>
+      <c r="AA2" s="34"/>
+      <c r="AB2" s="34"/>
+      <c r="AC2" s="34"/>
+      <c r="AD2" s="34"/>
+      <c r="AE2" s="34"/>
+      <c r="AF2" s="34"/>
       <c r="AG2" s="9"/>
     </row>
-    <row r="3" spans="1:35" ht="18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
-      <c r="D3" s="50" t="s">
+      <c r="D3" s="34" t="s">
         <v>142</v>
       </c>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50"/>
-      <c r="L3" s="50"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="50"/>
-      <c r="P3" s="50"/>
-      <c r="Q3" s="50"/>
-      <c r="R3" s="50"/>
-      <c r="S3" s="50"/>
-      <c r="T3" s="50"/>
-      <c r="U3" s="50"/>
-      <c r="V3" s="50"/>
-      <c r="W3" s="50"/>
-      <c r="X3" s="50"/>
-      <c r="Y3" s="50"/>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
-      <c r="AB3" s="50"/>
-      <c r="AC3" s="50"/>
-      <c r="AD3" s="50"/>
-      <c r="AE3" s="50"/>
-      <c r="AF3" s="50"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
+      <c r="M3" s="34"/>
+      <c r="N3" s="34"/>
+      <c r="O3" s="34"/>
+      <c r="P3" s="34"/>
+      <c r="Q3" s="34"/>
+      <c r="R3" s="34"/>
+      <c r="S3" s="34"/>
+      <c r="T3" s="34"/>
+      <c r="U3" s="34"/>
+      <c r="V3" s="34"/>
+      <c r="W3" s="34"/>
+      <c r="X3" s="34"/>
+      <c r="Y3" s="34"/>
+      <c r="Z3" s="34"/>
+      <c r="AA3" s="34"/>
+      <c r="AB3" s="34"/>
+      <c r="AC3" s="34"/>
+      <c r="AD3" s="34"/>
+      <c r="AE3" s="34"/>
+      <c r="AF3" s="34"/>
       <c r="AG3" s="9"/>
     </row>
-    <row r="4" spans="1:35" ht="18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
-      <c r="D4" s="50" t="s">
+      <c r="D4" s="34" t="s">
         <v>143</v>
       </c>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="50"/>
-      <c r="O4" s="50"/>
-      <c r="P4" s="50"/>
-      <c r="Q4" s="50"/>
-      <c r="R4" s="50"/>
-      <c r="S4" s="50"/>
-      <c r="T4" s="50"/>
-      <c r="U4" s="50"/>
-      <c r="V4" s="50"/>
-      <c r="W4" s="50"/>
-      <c r="X4" s="50"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="50"/>
-      <c r="AA4" s="50"/>
-      <c r="AB4" s="50"/>
-      <c r="AC4" s="50"/>
-      <c r="AD4" s="50"/>
-      <c r="AE4" s="50"/>
-      <c r="AF4" s="50"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="34"/>
+      <c r="P4" s="34"/>
+      <c r="Q4" s="34"/>
+      <c r="R4" s="34"/>
+      <c r="S4" s="34"/>
+      <c r="T4" s="34"/>
+      <c r="U4" s="34"/>
+      <c r="V4" s="34"/>
+      <c r="W4" s="34"/>
+      <c r="X4" s="34"/>
+      <c r="Y4" s="34"/>
+      <c r="Z4" s="34"/>
+      <c r="AA4" s="34"/>
+      <c r="AB4" s="34"/>
+      <c r="AC4" s="34"/>
+      <c r="AD4" s="34"/>
+      <c r="AE4" s="34"/>
+      <c r="AF4" s="34"/>
       <c r="AG4" s="9"/>
       <c r="AI4" s="31"/>
     </row>
-    <row r="5" spans="1:35" ht="18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
-      <c r="D5" s="50" t="s">
+      <c r="D5" s="34" t="s">
         <v>170</v>
       </c>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-      <c r="L5" s="50"/>
-      <c r="M5" s="50"/>
-      <c r="N5" s="50"/>
-      <c r="O5" s="50"/>
-      <c r="P5" s="50"/>
-      <c r="Q5" s="50"/>
-      <c r="R5" s="50"/>
-      <c r="S5" s="50"/>
-      <c r="T5" s="50"/>
-      <c r="U5" s="50"/>
-      <c r="V5" s="50"/>
-      <c r="W5" s="50"/>
-      <c r="X5" s="50"/>
-      <c r="Y5" s="50"/>
-      <c r="Z5" s="50"/>
-      <c r="AA5" s="50"/>
-      <c r="AB5" s="50"/>
-      <c r="AC5" s="50"/>
-      <c r="AD5" s="50"/>
-      <c r="AE5" s="50"/>
-      <c r="AF5" s="50"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="34"/>
+      <c r="L5" s="34"/>
+      <c r="M5" s="34"/>
+      <c r="N5" s="34"/>
+      <c r="O5" s="34"/>
+      <c r="P5" s="34"/>
+      <c r="Q5" s="34"/>
+      <c r="R5" s="34"/>
+      <c r="S5" s="34"/>
+      <c r="T5" s="34"/>
+      <c r="U5" s="34"/>
+      <c r="V5" s="34"/>
+      <c r="W5" s="34"/>
+      <c r="X5" s="34"/>
+      <c r="Y5" s="34"/>
+      <c r="Z5" s="34"/>
+      <c r="AA5" s="34"/>
+      <c r="AB5" s="34"/>
+      <c r="AC5" s="34"/>
+      <c r="AD5" s="34"/>
+      <c r="AE5" s="34"/>
+      <c r="AF5" s="34"/>
       <c r="AG5" s="9"/>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" s="9"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -5478,57 +5715,57 @@
       <c r="AF6" s="9"/>
       <c r="AG6" s="9"/>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" s="9"/>
-      <c r="B7" s="51" t="s">
+      <c r="B7" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="51"/>
+      <c r="C7" s="35"/>
       <c r="D7" s="9"/>
-      <c r="E7" s="51" t="s">
+      <c r="E7" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="51"/>
+      <c r="F7" s="35"/>
       <c r="G7" s="9"/>
-      <c r="H7" s="51" t="s">
+      <c r="H7" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="I7" s="51"/>
+      <c r="I7" s="35"/>
       <c r="J7" s="9"/>
-      <c r="K7" s="51" t="s">
+      <c r="K7" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="L7" s="51"/>
+      <c r="L7" s="35"/>
       <c r="M7" s="9"/>
-      <c r="N7" s="51" t="s">
+      <c r="N7" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="O7" s="51"/>
+      <c r="O7" s="35"/>
       <c r="P7" s="9"/>
-      <c r="Q7" s="51" t="s">
+      <c r="Q7" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="R7" s="51"/>
+      <c r="R7" s="35"/>
       <c r="S7" s="9"/>
-      <c r="T7" s="51" t="s">
+      <c r="T7" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="U7" s="51"/>
+      <c r="U7" s="35"/>
       <c r="V7" s="9"/>
-      <c r="W7" s="51" t="s">
+      <c r="W7" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="X7" s="51"/>
+      <c r="X7" s="35"/>
       <c r="Y7" s="9"/>
-      <c r="Z7" s="51" t="s">
+      <c r="Z7" s="35" t="s">
         <v>86</v>
       </c>
-      <c r="AA7" s="51"/>
+      <c r="AA7" s="35"/>
       <c r="AB7" s="9"/>
-      <c r="AC7" s="51" t="s">
+      <c r="AC7" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="AD7" s="51"/>
+      <c r="AD7" s="35"/>
       <c r="AE7" s="9"/>
       <c r="AF7" s="24" t="s">
         <v>140</v>
@@ -5539,7 +5776,7 @@
         <v>2.0833333333333335</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -5575,7 +5812,7 @@
       <c r="AG8" s="9"/>
       <c r="AI8" s="32"/>
     </row>
-    <row r="9" spans="1:35" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:35" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9"/>
       <c r="B9" s="1">
         <v>1</v>
@@ -5651,55 +5888,55 @@
       <c r="AG9" s="9"/>
       <c r="AI9" s="33"/>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" s="9"/>
-      <c r="B10" s="48" t="s">
+      <c r="B10" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="49"/>
+      <c r="C10" s="37"/>
       <c r="D10" s="9"/>
-      <c r="E10" s="48" t="s">
+      <c r="E10" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="49"/>
+      <c r="F10" s="37"/>
       <c r="G10" s="9"/>
-      <c r="H10" s="48" t="s">
+      <c r="H10" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="I10" s="49"/>
+      <c r="I10" s="37"/>
       <c r="J10" s="9"/>
-      <c r="K10" s="48" t="s">
+      <c r="K10" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="L10" s="49"/>
+      <c r="L10" s="37"/>
       <c r="M10" s="9"/>
-      <c r="N10" s="48" t="s">
+      <c r="N10" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="O10" s="49"/>
+      <c r="O10" s="37"/>
       <c r="P10" s="9"/>
-      <c r="Q10" s="48"/>
-      <c r="R10" s="49"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="37"/>
       <c r="S10" s="9"/>
-      <c r="T10" s="48" t="s">
+      <c r="T10" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="U10" s="49"/>
+      <c r="U10" s="37"/>
       <c r="V10" s="9"/>
-      <c r="W10" s="48" t="s">
+      <c r="W10" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="X10" s="49"/>
+      <c r="X10" s="37"/>
       <c r="Y10" s="9"/>
-      <c r="Z10" s="48" t="s">
+      <c r="Z10" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="AA10" s="49"/>
+      <c r="AA10" s="37"/>
       <c r="AB10" s="9"/>
-      <c r="AC10" s="48" t="s">
+      <c r="AC10" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="AD10" s="49"/>
+      <c r="AD10" s="37"/>
       <c r="AE10" s="9"/>
       <c r="AF10" s="4" t="s">
         <v>107</v>
@@ -5707,156 +5944,156 @@
       <c r="AG10" s="9"/>
       <c r="AI10" s="32"/>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" s="9"/>
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="41"/>
+      <c r="C11" s="39"/>
       <c r="D11" s="9"/>
-      <c r="E11" s="40" t="s">
+      <c r="E11" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="41"/>
+      <c r="F11" s="39"/>
       <c r="G11" s="9"/>
-      <c r="H11" s="40" t="s">
+      <c r="H11" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="I11" s="41"/>
+      <c r="I11" s="39"/>
       <c r="J11" s="9"/>
-      <c r="K11" s="40" t="s">
+      <c r="K11" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="L11" s="41"/>
+      <c r="L11" s="39"/>
       <c r="M11" s="9"/>
-      <c r="N11" s="40" t="s">
+      <c r="N11" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="O11" s="41"/>
+      <c r="O11" s="39"/>
       <c r="P11" s="9"/>
-      <c r="Q11" s="40" t="s">
+      <c r="Q11" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="R11" s="41"/>
+      <c r="R11" s="39"/>
       <c r="S11" s="9"/>
-      <c r="T11" s="40" t="s">
+      <c r="T11" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="U11" s="41"/>
+      <c r="U11" s="39"/>
       <c r="V11" s="9"/>
-      <c r="W11" s="40" t="s">
+      <c r="W11" s="38" t="s">
         <v>77</v>
       </c>
-      <c r="X11" s="41"/>
+      <c r="X11" s="39"/>
       <c r="Y11" s="9"/>
-      <c r="Z11" s="40" t="s">
+      <c r="Z11" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="AA11" s="41"/>
+      <c r="AA11" s="39"/>
       <c r="AB11" s="9"/>
-      <c r="AC11" s="40" t="s">
+      <c r="AC11" s="38" t="s">
         <v>92</v>
       </c>
-      <c r="AD11" s="41"/>
+      <c r="AD11" s="39"/>
       <c r="AE11" s="9"/>
       <c r="AF11" s="4" t="s">
         <v>108</v>
       </c>
       <c r="AG11" s="9"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="43"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="41"/>
       <c r="D12" s="9"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="43"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="41"/>
       <c r="G12" s="9"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="43"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="41"/>
       <c r="J12" s="9"/>
-      <c r="K12" s="42"/>
-      <c r="L12" s="43"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="41"/>
       <c r="M12" s="9"/>
-      <c r="N12" s="42"/>
-      <c r="O12" s="43"/>
+      <c r="N12" s="40"/>
+      <c r="O12" s="41"/>
       <c r="P12" s="9"/>
-      <c r="Q12" s="42"/>
-      <c r="R12" s="43"/>
+      <c r="Q12" s="40"/>
+      <c r="R12" s="41"/>
       <c r="S12" s="9"/>
-      <c r="T12" s="42"/>
-      <c r="U12" s="43"/>
+      <c r="T12" s="40"/>
+      <c r="U12" s="41"/>
       <c r="V12" s="9"/>
-      <c r="W12" s="42"/>
-      <c r="X12" s="43"/>
+      <c r="W12" s="40"/>
+      <c r="X12" s="41"/>
       <c r="Y12" s="9"/>
-      <c r="Z12" s="42"/>
-      <c r="AA12" s="43"/>
+      <c r="Z12" s="40"/>
+      <c r="AA12" s="41"/>
       <c r="AB12" s="9"/>
-      <c r="AC12" s="42"/>
-      <c r="AD12" s="43"/>
+      <c r="AC12" s="40"/>
+      <c r="AD12" s="41"/>
       <c r="AE12" s="9"/>
       <c r="AF12" s="4" t="s">
         <v>109</v>
       </c>
       <c r="AG12" s="9"/>
     </row>
-    <row r="13" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9"/>
-      <c r="B13" s="46" t="s">
+      <c r="B13" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="47"/>
+      <c r="C13" s="43"/>
       <c r="D13" s="9"/>
-      <c r="E13" s="46" t="s">
+      <c r="E13" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="47"/>
+      <c r="F13" s="43"/>
       <c r="G13" s="9"/>
-      <c r="H13" s="46" t="s">
+      <c r="H13" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="I13" s="47"/>
+      <c r="I13" s="43"/>
       <c r="J13" s="9"/>
-      <c r="K13" s="46">
+      <c r="K13" s="42">
         <v>10</v>
       </c>
-      <c r="L13" s="47"/>
+      <c r="L13" s="43"/>
       <c r="M13" s="9"/>
-      <c r="N13" s="46" t="s">
+      <c r="N13" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="O13" s="47"/>
+      <c r="O13" s="43"/>
       <c r="P13" s="9"/>
-      <c r="Q13" s="46"/>
-      <c r="R13" s="47"/>
+      <c r="Q13" s="42"/>
+      <c r="R13" s="43"/>
       <c r="S13" s="9"/>
-      <c r="T13" s="46">
+      <c r="T13" s="42">
         <v>26</v>
       </c>
-      <c r="U13" s="47"/>
+      <c r="U13" s="43"/>
       <c r="V13" s="9"/>
-      <c r="W13" s="46">
+      <c r="W13" s="42">
         <v>30</v>
       </c>
-      <c r="X13" s="47"/>
+      <c r="X13" s="43"/>
       <c r="Y13" s="9"/>
-      <c r="Z13" s="46" t="s">
+      <c r="Z13" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="AA13" s="47"/>
+      <c r="AA13" s="43"/>
       <c r="AB13" s="9"/>
-      <c r="AC13" s="46" t="s">
+      <c r="AC13" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="AD13" s="47"/>
+      <c r="AD13" s="43"/>
       <c r="AE13" s="9"/>
       <c r="AF13" s="4" t="s">
         <v>110</v>
       </c>
       <c r="AG13" s="9"/>
     </row>
-    <row r="14" spans="1:35" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:35" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -5893,7 +6130,7 @@
       </c>
       <c r="AG14" s="9"/>
     </row>
-    <row r="15" spans="1:35" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:35" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="B15" s="1">
         <v>2</v>
@@ -5970,209 +6207,209 @@
       </c>
       <c r="AG15" s="9"/>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
-      <c r="B16" s="48" t="s">
+      <c r="B16" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C16" s="49"/>
+      <c r="C16" s="37"/>
       <c r="D16" s="9"/>
-      <c r="E16" s="48" t="s">
+      <c r="E16" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="49"/>
+      <c r="F16" s="37"/>
       <c r="G16" s="9"/>
-      <c r="H16" s="48" t="s">
+      <c r="H16" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="49"/>
+      <c r="I16" s="37"/>
       <c r="J16" s="9"/>
-      <c r="K16" s="48" t="s">
+      <c r="K16" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="L16" s="49"/>
+      <c r="L16" s="37"/>
       <c r="M16" s="9"/>
-      <c r="N16" s="48" t="s">
+      <c r="N16" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="O16" s="49"/>
+      <c r="O16" s="37"/>
       <c r="P16" s="9"/>
-      <c r="Q16" s="48" t="s">
+      <c r="Q16" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="R16" s="49"/>
+      <c r="R16" s="37"/>
       <c r="S16" s="9"/>
-      <c r="T16" s="48"/>
-      <c r="U16" s="49"/>
+      <c r="T16" s="36"/>
+      <c r="U16" s="37"/>
       <c r="V16" s="9"/>
-      <c r="W16" s="48" t="s">
+      <c r="W16" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="X16" s="49"/>
+      <c r="X16" s="37"/>
       <c r="Y16" s="9"/>
-      <c r="Z16" s="48" t="s">
+      <c r="Z16" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="AA16" s="49"/>
+      <c r="AA16" s="37"/>
       <c r="AB16" s="9"/>
-      <c r="AC16" s="48" t="s">
+      <c r="AC16" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="AD16" s="49"/>
+      <c r="AD16" s="37"/>
       <c r="AE16" s="9"/>
       <c r="AF16" s="4" t="s">
         <v>112</v>
       </c>
       <c r="AG16" s="9"/>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="41"/>
+      <c r="C17" s="39"/>
       <c r="D17" s="9"/>
-      <c r="E17" s="40" t="s">
+      <c r="E17" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="41"/>
+      <c r="F17" s="39"/>
       <c r="G17" s="9"/>
-      <c r="H17" s="40" t="s">
+      <c r="H17" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="I17" s="41"/>
+      <c r="I17" s="39"/>
       <c r="J17" s="9"/>
-      <c r="K17" s="40" t="s">
+      <c r="K17" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="L17" s="41"/>
+      <c r="L17" s="39"/>
       <c r="M17" s="9"/>
-      <c r="N17" s="40" t="s">
+      <c r="N17" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="O17" s="41"/>
+      <c r="O17" s="39"/>
       <c r="P17" s="9"/>
-      <c r="Q17" s="40" t="s">
+      <c r="Q17" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="R17" s="41"/>
+      <c r="R17" s="39"/>
       <c r="S17" s="9"/>
-      <c r="T17" s="40" t="s">
+      <c r="T17" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="U17" s="41"/>
+      <c r="U17" s="39"/>
       <c r="V17" s="9"/>
-      <c r="W17" s="40" t="s">
+      <c r="W17" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="X17" s="41"/>
+      <c r="X17" s="39"/>
       <c r="Y17" s="9"/>
-      <c r="Z17" s="40" t="s">
+      <c r="Z17" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="AA17" s="41"/>
+      <c r="AA17" s="39"/>
       <c r="AB17" s="9"/>
-      <c r="AC17" s="40" t="s">
+      <c r="AC17" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="AD17" s="41"/>
+      <c r="AD17" s="39"/>
       <c r="AE17" s="9"/>
       <c r="AF17" s="4"/>
       <c r="AG17" s="9"/>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="43"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="41"/>
       <c r="D18" s="9"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="43"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="41"/>
       <c r="G18" s="9"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="43"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="41"/>
       <c r="J18" s="9"/>
-      <c r="K18" s="42"/>
-      <c r="L18" s="43"/>
+      <c r="K18" s="40"/>
+      <c r="L18" s="41"/>
       <c r="M18" s="9"/>
-      <c r="N18" s="42"/>
-      <c r="O18" s="43"/>
+      <c r="N18" s="40"/>
+      <c r="O18" s="41"/>
       <c r="P18" s="9"/>
-      <c r="Q18" s="42"/>
-      <c r="R18" s="43"/>
+      <c r="Q18" s="40"/>
+      <c r="R18" s="41"/>
       <c r="S18" s="9"/>
-      <c r="T18" s="42"/>
-      <c r="U18" s="43"/>
+      <c r="T18" s="40"/>
+      <c r="U18" s="41"/>
       <c r="V18" s="9"/>
-      <c r="W18" s="42"/>
-      <c r="X18" s="43"/>
+      <c r="W18" s="40"/>
+      <c r="X18" s="41"/>
       <c r="Y18" s="9"/>
-      <c r="Z18" s="42"/>
-      <c r="AA18" s="43"/>
+      <c r="Z18" s="40"/>
+      <c r="AA18" s="41"/>
       <c r="AB18" s="9"/>
-      <c r="AC18" s="42"/>
-      <c r="AD18" s="43"/>
+      <c r="AC18" s="40"/>
+      <c r="AD18" s="41"/>
       <c r="AE18" s="9"/>
       <c r="AF18" s="4" t="s">
         <v>113</v>
       </c>
       <c r="AG18" s="9"/>
     </row>
-    <row r="19" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9"/>
-      <c r="B19" s="46" t="s">
+      <c r="B19" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="C19" s="47"/>
+      <c r="C19" s="43"/>
       <c r="D19" s="9"/>
-      <c r="E19" s="46">
+      <c r="E19" s="42">
         <v>2</v>
       </c>
-      <c r="F19" s="47"/>
+      <c r="F19" s="43"/>
       <c r="G19" s="9"/>
-      <c r="H19" s="46">
+      <c r="H19" s="42">
         <v>6</v>
       </c>
-      <c r="I19" s="47"/>
+      <c r="I19" s="43"/>
       <c r="J19" s="9"/>
-      <c r="K19" s="46">
+      <c r="K19" s="42">
         <v>11</v>
       </c>
-      <c r="L19" s="47"/>
+      <c r="L19" s="43"/>
       <c r="M19" s="9"/>
-      <c r="N19" s="46" t="s">
+      <c r="N19" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="O19" s="47"/>
+      <c r="O19" s="43"/>
       <c r="P19" s="9"/>
-      <c r="Q19" s="46" t="s">
+      <c r="Q19" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="R19" s="47"/>
+      <c r="R19" s="43"/>
       <c r="S19" s="9"/>
-      <c r="T19" s="46"/>
-      <c r="U19" s="47"/>
+      <c r="T19" s="42"/>
+      <c r="U19" s="43"/>
       <c r="V19" s="9"/>
-      <c r="W19" s="46">
+      <c r="W19" s="42">
         <v>30</v>
       </c>
-      <c r="X19" s="47"/>
+      <c r="X19" s="43"/>
       <c r="Y19" s="9"/>
-      <c r="Z19" s="46">
+      <c r="Z19" s="42">
         <v>32</v>
       </c>
-      <c r="AA19" s="47"/>
+      <c r="AA19" s="43"/>
       <c r="AB19" s="9"/>
-      <c r="AC19" s="46" t="s">
+      <c r="AC19" s="42" t="s">
         <v>97</v>
       </c>
-      <c r="AD19" s="47"/>
+      <c r="AD19" s="43"/>
       <c r="AE19" s="9"/>
       <c r="AF19" s="4" t="s">
         <v>114</v>
       </c>
       <c r="AG19" s="9"/>
     </row>
-    <row r="20" spans="1:33" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:33" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -6207,7 +6444,7 @@
       <c r="AF20" s="4"/>
       <c r="AG20" s="9"/>
     </row>
-    <row r="21" spans="1:33" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:33" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9"/>
       <c r="B21" s="1">
         <v>3</v>
@@ -6284,215 +6521,215 @@
       </c>
       <c r="AG21" s="9"/>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" s="9"/>
-      <c r="B22" s="48" t="s">
+      <c r="B22" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="49"/>
+      <c r="C22" s="37"/>
       <c r="D22" s="9"/>
-      <c r="E22" s="48" t="s">
+      <c r="E22" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="F22" s="49"/>
+      <c r="F22" s="37"/>
       <c r="G22" s="9"/>
-      <c r="H22" s="48" t="s">
+      <c r="H22" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="I22" s="49"/>
+      <c r="I22" s="37"/>
       <c r="J22" s="9"/>
-      <c r="K22" s="48" t="s">
+      <c r="K22" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="L22" s="49"/>
+      <c r="L22" s="37"/>
       <c r="M22" s="9"/>
-      <c r="N22" s="48" t="s">
+      <c r="N22" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="O22" s="49"/>
+      <c r="O22" s="37"/>
       <c r="P22" s="9"/>
-      <c r="Q22" s="48" t="s">
+      <c r="Q22" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="R22" s="49"/>
+      <c r="R22" s="37"/>
       <c r="S22" s="9"/>
-      <c r="T22" s="48" t="s">
+      <c r="T22" s="36" t="s">
         <v>147</v>
       </c>
-      <c r="U22" s="49"/>
+      <c r="U22" s="37"/>
       <c r="V22" s="9"/>
-      <c r="W22" s="48" t="s">
+      <c r="W22" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="X22" s="49"/>
+      <c r="X22" s="37"/>
       <c r="Y22" s="9"/>
-      <c r="Z22" s="48" t="s">
+      <c r="Z22" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="AA22" s="49"/>
+      <c r="AA22" s="37"/>
       <c r="AB22" s="9"/>
-      <c r="AC22" s="48" t="s">
+      <c r="AC22" s="36" t="s">
         <v>148</v>
       </c>
-      <c r="AD22" s="49"/>
+      <c r="AD22" s="37"/>
       <c r="AE22" s="9"/>
       <c r="AF22" s="4" t="s">
         <v>108</v>
       </c>
       <c r="AG22" s="9"/>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" s="9"/>
-      <c r="B23" s="40" t="s">
+      <c r="B23" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="41"/>
+      <c r="C23" s="39"/>
       <c r="D23" s="9"/>
-      <c r="E23" s="40" t="s">
+      <c r="E23" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="F23" s="41"/>
+      <c r="F23" s="39"/>
       <c r="G23" s="9"/>
-      <c r="H23" s="40" t="s">
+      <c r="H23" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="I23" s="41"/>
+      <c r="I23" s="39"/>
       <c r="J23" s="9"/>
-      <c r="K23" s="40" t="s">
+      <c r="K23" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="L23" s="41"/>
+      <c r="L23" s="39"/>
       <c r="M23" s="9"/>
-      <c r="N23" s="40" t="s">
+      <c r="N23" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="O23" s="41"/>
+      <c r="O23" s="39"/>
       <c r="P23" s="9"/>
-      <c r="Q23" s="40" t="s">
+      <c r="Q23" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="R23" s="41"/>
+      <c r="R23" s="39"/>
       <c r="S23" s="9"/>
-      <c r="T23" s="40" t="s">
+      <c r="T23" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="U23" s="41"/>
+      <c r="U23" s="39"/>
       <c r="V23" s="9"/>
-      <c r="W23" s="40" t="s">
+      <c r="W23" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="X23" s="41"/>
+      <c r="X23" s="39"/>
       <c r="Y23" s="9"/>
-      <c r="Z23" s="40" t="s">
+      <c r="Z23" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="AA23" s="41"/>
+      <c r="AA23" s="39"/>
       <c r="AB23" s="9"/>
-      <c r="AC23" s="40" t="s">
+      <c r="AC23" s="38" t="s">
         <v>104</v>
       </c>
-      <c r="AD23" s="41"/>
+      <c r="AD23" s="39"/>
       <c r="AE23" s="9"/>
       <c r="AF23" s="4" t="s">
         <v>109</v>
       </c>
       <c r="AG23" s="9"/>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" s="9"/>
-      <c r="B24" s="42"/>
-      <c r="C24" s="43"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="41"/>
       <c r="D24" s="9"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="43"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="41"/>
       <c r="G24" s="9"/>
-      <c r="H24" s="42"/>
-      <c r="I24" s="43"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="41"/>
       <c r="J24" s="9"/>
-      <c r="K24" s="42"/>
-      <c r="L24" s="43"/>
+      <c r="K24" s="40"/>
+      <c r="L24" s="41"/>
       <c r="M24" s="9"/>
-      <c r="N24" s="42"/>
-      <c r="O24" s="43"/>
+      <c r="N24" s="40"/>
+      <c r="O24" s="41"/>
       <c r="P24" s="9"/>
-      <c r="Q24" s="42"/>
-      <c r="R24" s="43"/>
+      <c r="Q24" s="40"/>
+      <c r="R24" s="41"/>
       <c r="S24" s="9"/>
-      <c r="T24" s="42"/>
-      <c r="U24" s="43"/>
+      <c r="T24" s="40"/>
+      <c r="U24" s="41"/>
       <c r="V24" s="9"/>
-      <c r="W24" s="42"/>
-      <c r="X24" s="43"/>
+      <c r="W24" s="40"/>
+      <c r="X24" s="41"/>
       <c r="Y24" s="9"/>
-      <c r="Z24" s="42"/>
-      <c r="AA24" s="43"/>
+      <c r="Z24" s="40"/>
+      <c r="AA24" s="41"/>
       <c r="AB24" s="9"/>
-      <c r="AC24" s="42"/>
-      <c r="AD24" s="43"/>
+      <c r="AC24" s="40"/>
+      <c r="AD24" s="41"/>
       <c r="AE24" s="9"/>
       <c r="AF24" s="4" t="s">
         <v>113</v>
       </c>
       <c r="AG24" s="9"/>
     </row>
-    <row r="25" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9"/>
-      <c r="B25" s="46" t="s">
+      <c r="B25" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="C25" s="47"/>
+      <c r="C25" s="43"/>
       <c r="D25" s="9"/>
-      <c r="E25" s="46">
+      <c r="E25" s="42">
         <v>3</v>
       </c>
-      <c r="F25" s="47"/>
+      <c r="F25" s="43"/>
       <c r="G25" s="9"/>
-      <c r="H25" s="46">
+      <c r="H25" s="42">
         <v>7</v>
       </c>
-      <c r="I25" s="47"/>
+      <c r="I25" s="43"/>
       <c r="J25" s="9"/>
-      <c r="K25" s="46">
+      <c r="K25" s="42">
         <v>12</v>
       </c>
-      <c r="L25" s="47"/>
+      <c r="L25" s="43"/>
       <c r="M25" s="9"/>
-      <c r="N25" s="46" t="s">
+      <c r="N25" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="O25" s="47"/>
+      <c r="O25" s="43"/>
       <c r="P25" s="9"/>
-      <c r="Q25" s="46">
+      <c r="Q25" s="42">
         <v>22</v>
       </c>
-      <c r="R25" s="47"/>
+      <c r="R25" s="43"/>
       <c r="S25" s="9"/>
-      <c r="T25" s="46">
+      <c r="T25" s="42">
         <v>27</v>
       </c>
-      <c r="U25" s="47"/>
+      <c r="U25" s="43"/>
       <c r="V25" s="9"/>
-      <c r="W25" s="46" t="s">
+      <c r="W25" s="42" t="s">
         <v>85</v>
       </c>
-      <c r="X25" s="47"/>
+      <c r="X25" s="43"/>
       <c r="Y25" s="9"/>
-      <c r="Z25" s="46" t="s">
+      <c r="Z25" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="AA25" s="47"/>
+      <c r="AA25" s="43"/>
       <c r="AB25" s="9"/>
-      <c r="AC25" s="46" t="s">
+      <c r="AC25" s="42" t="s">
         <v>105</v>
       </c>
-      <c r="AD25" s="47"/>
+      <c r="AD25" s="43"/>
       <c r="AE25" s="9"/>
       <c r="AF25" s="4" t="s">
         <v>116</v>
       </c>
       <c r="AG25" s="9"/>
     </row>
-    <row r="26" spans="1:33" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:33" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -6529,7 +6766,7 @@
       </c>
       <c r="AG26" s="9"/>
     </row>
-    <row r="27" spans="1:33" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:33" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A27" s="9"/>
       <c r="B27" s="1">
         <v>4</v>
@@ -6606,211 +6843,211 @@
       </c>
       <c r="AG27" s="9"/>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" s="9"/>
-      <c r="B28" s="48" t="s">
+      <c r="B28" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="49"/>
+      <c r="C28" s="37"/>
       <c r="D28" s="9"/>
-      <c r="E28" s="48" t="s">
+      <c r="E28" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="F28" s="49"/>
+      <c r="F28" s="37"/>
       <c r="G28" s="9"/>
-      <c r="H28" s="48" t="s">
+      <c r="H28" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="I28" s="49"/>
+      <c r="I28" s="37"/>
       <c r="J28" s="9"/>
-      <c r="K28" s="48" t="s">
+      <c r="K28" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="L28" s="49"/>
+      <c r="L28" s="37"/>
       <c r="M28" s="9"/>
-      <c r="N28" s="48" t="s">
+      <c r="N28" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="O28" s="49"/>
+      <c r="O28" s="37"/>
       <c r="P28" s="9"/>
-      <c r="Q28" s="48" t="s">
+      <c r="Q28" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="R28" s="49"/>
+      <c r="R28" s="37"/>
       <c r="S28" s="9"/>
-      <c r="T28" s="48" t="s">
+      <c r="T28" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="U28" s="49"/>
+      <c r="U28" s="37"/>
       <c r="V28" s="9"/>
-      <c r="W28" s="48" t="s">
+      <c r="W28" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="X28" s="49"/>
+      <c r="X28" s="37"/>
       <c r="Y28" s="9"/>
-      <c r="Z28" s="48" t="s">
+      <c r="Z28" s="36" t="s">
         <v>101</v>
       </c>
-      <c r="AA28" s="49"/>
+      <c r="AA28" s="37"/>
       <c r="AB28" s="9"/>
-      <c r="AC28" s="48"/>
-      <c r="AD28" s="49"/>
+      <c r="AC28" s="36"/>
+      <c r="AD28" s="37"/>
       <c r="AE28" s="9"/>
       <c r="AF28" s="4" t="s">
         <v>4</v>
       </c>
       <c r="AG28" s="9"/>
     </row>
-    <row r="29" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9"/>
-      <c r="B29" s="40" t="s">
+      <c r="B29" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="41"/>
+      <c r="C29" s="39"/>
       <c r="D29" s="9"/>
-      <c r="E29" s="40" t="s">
+      <c r="E29" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="F29" s="41"/>
+      <c r="F29" s="39"/>
       <c r="G29" s="9"/>
-      <c r="H29" s="40" t="s">
+      <c r="H29" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="I29" s="41"/>
+      <c r="I29" s="39"/>
       <c r="J29" s="9"/>
-      <c r="K29" s="40" t="s">
+      <c r="K29" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="41"/>
+      <c r="L29" s="39"/>
       <c r="M29" s="9"/>
-      <c r="N29" s="40" t="s">
+      <c r="N29" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="O29" s="41"/>
+      <c r="O29" s="39"/>
       <c r="P29" s="9"/>
-      <c r="Q29" s="40" t="s">
+      <c r="Q29" s="38" t="s">
         <v>146</v>
       </c>
-      <c r="R29" s="41"/>
+      <c r="R29" s="39"/>
       <c r="S29" s="9"/>
-      <c r="T29" s="40" t="s">
+      <c r="T29" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="U29" s="41"/>
+      <c r="U29" s="39"/>
       <c r="V29" s="9"/>
-      <c r="W29" s="40" t="s">
+      <c r="W29" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="X29" s="41"/>
+      <c r="X29" s="39"/>
       <c r="Y29" s="9"/>
-      <c r="Z29" s="40" t="s">
+      <c r="Z29" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="AA29" s="41"/>
+      <c r="AA29" s="39"/>
       <c r="AB29" s="9"/>
-      <c r="AC29" s="40" t="s">
+      <c r="AC29" s="38" t="s">
         <v>149</v>
       </c>
-      <c r="AD29" s="41"/>
+      <c r="AD29" s="39"/>
       <c r="AE29" s="9"/>
       <c r="AF29" s="4" t="s">
         <v>119</v>
       </c>
       <c r="AG29" s="9"/>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" s="9"/>
-      <c r="B30" s="42"/>
-      <c r="C30" s="43"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="41"/>
       <c r="D30" s="9"/>
-      <c r="E30" s="42"/>
-      <c r="F30" s="43"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="41"/>
       <c r="G30" s="9"/>
-      <c r="H30" s="42"/>
-      <c r="I30" s="43"/>
+      <c r="H30" s="40"/>
+      <c r="I30" s="41"/>
       <c r="J30" s="9"/>
-      <c r="K30" s="42"/>
-      <c r="L30" s="43"/>
+      <c r="K30" s="40"/>
+      <c r="L30" s="41"/>
       <c r="M30" s="9"/>
-      <c r="N30" s="42"/>
-      <c r="O30" s="43"/>
+      <c r="N30" s="40"/>
+      <c r="O30" s="41"/>
       <c r="P30" s="9"/>
-      <c r="Q30" s="42"/>
-      <c r="R30" s="43"/>
+      <c r="Q30" s="40"/>
+      <c r="R30" s="41"/>
       <c r="S30" s="9"/>
-      <c r="T30" s="42"/>
-      <c r="U30" s="43"/>
+      <c r="T30" s="40"/>
+      <c r="U30" s="41"/>
       <c r="V30" s="9"/>
-      <c r="W30" s="42"/>
-      <c r="X30" s="43"/>
+      <c r="W30" s="40"/>
+      <c r="X30" s="41"/>
       <c r="Y30" s="9"/>
-      <c r="Z30" s="42"/>
-      <c r="AA30" s="43"/>
+      <c r="Z30" s="40"/>
+      <c r="AA30" s="41"/>
       <c r="AB30" s="9"/>
-      <c r="AC30" s="42"/>
-      <c r="AD30" s="43"/>
+      <c r="AC30" s="40"/>
+      <c r="AD30" s="41"/>
       <c r="AE30" s="9"/>
       <c r="AF30" s="4" t="s">
         <v>118</v>
       </c>
       <c r="AG30" s="9"/>
     </row>
-    <row r="31" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="9"/>
-      <c r="B31" s="46" t="s">
+      <c r="B31" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="C31" s="47"/>
+      <c r="C31" s="43"/>
       <c r="D31" s="9"/>
-      <c r="E31" s="46">
+      <c r="E31" s="42">
         <v>3</v>
       </c>
-      <c r="F31" s="47"/>
+      <c r="F31" s="43"/>
       <c r="G31" s="9"/>
-      <c r="H31" s="46">
+      <c r="H31" s="42">
         <v>6</v>
       </c>
-      <c r="I31" s="47"/>
+      <c r="I31" s="43"/>
       <c r="J31" s="9"/>
-      <c r="K31" s="46">
+      <c r="K31" s="42">
         <v>12</v>
       </c>
-      <c r="L31" s="47"/>
+      <c r="L31" s="43"/>
       <c r="M31" s="9"/>
-      <c r="N31" s="46">
+      <c r="N31" s="42">
         <v>18</v>
       </c>
-      <c r="O31" s="47"/>
+      <c r="O31" s="43"/>
       <c r="P31" s="9"/>
-      <c r="Q31" s="46">
+      <c r="Q31" s="42">
         <v>12</v>
       </c>
-      <c r="R31" s="47"/>
+      <c r="R31" s="43"/>
       <c r="S31" s="9"/>
-      <c r="T31" s="46" t="s">
+      <c r="T31" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="U31" s="47"/>
+      <c r="U31" s="43"/>
       <c r="V31" s="9"/>
-      <c r="W31" s="46">
+      <c r="W31" s="42">
         <v>33</v>
       </c>
-      <c r="X31" s="47"/>
+      <c r="X31" s="43"/>
       <c r="Y31" s="9"/>
-      <c r="Z31" s="46">
+      <c r="Z31" s="42">
         <v>38</v>
       </c>
-      <c r="AA31" s="47"/>
+      <c r="AA31" s="43"/>
       <c r="AB31" s="9"/>
-      <c r="AC31" s="46"/>
-      <c r="AD31" s="47"/>
+      <c r="AC31" s="42"/>
+      <c r="AD31" s="43"/>
       <c r="AE31" s="9"/>
       <c r="AF31" s="5" t="s">
         <v>162</v>
       </c>
       <c r="AG31" s="9"/>
     </row>
-    <row r="32" spans="1:33" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:33" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="9"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -6845,7 +7082,7 @@
       <c r="AF32" s="9"/>
       <c r="AG32" s="9"/>
     </row>
-    <row r="33" spans="1:33" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:33" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A33" s="9"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
@@ -6912,44 +7149,44 @@
       <c r="AF33" s="9"/>
       <c r="AG33" s="9"/>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" s="9"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
-      <c r="E34" s="48" t="s">
+      <c r="E34" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="F34" s="49"/>
+      <c r="F34" s="37"/>
       <c r="G34" s="9"/>
-      <c r="H34" s="48" t="s">
+      <c r="H34" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="I34" s="49"/>
+      <c r="I34" s="37"/>
       <c r="J34" s="9"/>
-      <c r="K34" s="48" t="s">
+      <c r="K34" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="L34" s="49"/>
+      <c r="L34" s="37"/>
       <c r="M34" s="9"/>
-      <c r="N34" s="48" t="s">
+      <c r="N34" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="O34" s="49"/>
+      <c r="O34" s="37"/>
       <c r="P34" s="9"/>
-      <c r="Q34" s="48" t="s">
+      <c r="Q34" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="R34" s="49"/>
+      <c r="R34" s="37"/>
       <c r="S34" s="9"/>
-      <c r="T34" s="48"/>
-      <c r="U34" s="49"/>
+      <c r="T34" s="36"/>
+      <c r="U34" s="37"/>
       <c r="V34" s="9"/>
-      <c r="W34" s="48"/>
-      <c r="X34" s="49"/>
+      <c r="W34" s="36"/>
+      <c r="X34" s="37"/>
       <c r="Y34" s="9"/>
-      <c r="Z34" s="48"/>
-      <c r="AA34" s="49"/>
+      <c r="Z34" s="36"/>
+      <c r="AA34" s="37"/>
       <c r="AB34" s="9"/>
       <c r="AC34" s="11"/>
       <c r="AD34" s="9"/>
@@ -6957,50 +7194,50 @@
       <c r="AF34" s="9"/>
       <c r="AG34" s="9"/>
     </row>
-    <row r="35" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="9"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
-      <c r="E35" s="40" t="s">
+      <c r="E35" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="F35" s="41"/>
+      <c r="F35" s="39"/>
       <c r="G35" s="9"/>
-      <c r="H35" s="40" t="s">
+      <c r="H35" s="38" t="s">
         <v>145</v>
       </c>
-      <c r="I35" s="41"/>
+      <c r="I35" s="39"/>
       <c r="J35" s="9"/>
-      <c r="K35" s="40" t="s">
+      <c r="K35" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="L35" s="41"/>
+      <c r="L35" s="39"/>
       <c r="M35" s="9"/>
-      <c r="N35" s="40" t="s">
+      <c r="N35" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="O35" s="41"/>
+      <c r="O35" s="39"/>
       <c r="P35" s="9"/>
-      <c r="Q35" s="40" t="s">
+      <c r="Q35" s="38" t="s">
         <v>66</v>
       </c>
-      <c r="R35" s="41"/>
+      <c r="R35" s="39"/>
       <c r="S35" s="9"/>
-      <c r="T35" s="40" t="s">
+      <c r="T35" s="38" t="s">
         <v>76</v>
       </c>
-      <c r="U35" s="41"/>
+      <c r="U35" s="39"/>
       <c r="V35" s="9"/>
-      <c r="W35" s="40" t="s">
+      <c r="W35" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="X35" s="41"/>
+      <c r="X35" s="39"/>
       <c r="Y35" s="9"/>
-      <c r="Z35" s="40" t="s">
+      <c r="Z35" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="AA35" s="41"/>
+      <c r="AA35" s="39"/>
       <c r="AB35" s="9"/>
       <c r="AC35" s="11"/>
       <c r="AD35" s="9"/>
@@ -7008,34 +7245,34 @@
       <c r="AF35" s="24"/>
       <c r="AG35" s="9"/>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36" s="9"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="43"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="41"/>
       <c r="G36" s="9"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="43"/>
+      <c r="H36" s="40"/>
+      <c r="I36" s="41"/>
       <c r="J36" s="9"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="43"/>
+      <c r="K36" s="40"/>
+      <c r="L36" s="41"/>
       <c r="M36" s="9"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="43"/>
+      <c r="N36" s="40"/>
+      <c r="O36" s="41"/>
       <c r="P36" s="9"/>
-      <c r="Q36" s="42"/>
-      <c r="R36" s="43"/>
+      <c r="Q36" s="40"/>
+      <c r="R36" s="41"/>
       <c r="S36" s="9"/>
-      <c r="T36" s="42"/>
-      <c r="U36" s="43"/>
+      <c r="T36" s="40"/>
+      <c r="U36" s="41"/>
       <c r="V36" s="9"/>
-      <c r="W36" s="42"/>
-      <c r="X36" s="43"/>
+      <c r="W36" s="40"/>
+      <c r="X36" s="41"/>
       <c r="Y36" s="9"/>
-      <c r="Z36" s="42"/>
-      <c r="AA36" s="43"/>
+      <c r="Z36" s="40"/>
+      <c r="AA36" s="41"/>
       <c r="AB36" s="9"/>
       <c r="AC36" s="11"/>
       <c r="AD36" s="9"/>
@@ -7043,44 +7280,44 @@
       <c r="AF36" s="9"/>
       <c r="AG36" s="9"/>
     </row>
-    <row r="37" spans="1:33" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:33" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="9"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
-      <c r="E37" s="46">
+      <c r="E37" s="42">
         <v>4</v>
       </c>
-      <c r="F37" s="47"/>
+      <c r="F37" s="43"/>
       <c r="G37" s="9"/>
-      <c r="H37" s="46" t="s">
+      <c r="H37" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="I37" s="47"/>
+      <c r="I37" s="43"/>
       <c r="J37" s="9"/>
-      <c r="K37" s="46">
+      <c r="K37" s="42">
         <v>13</v>
       </c>
-      <c r="L37" s="47"/>
+      <c r="L37" s="43"/>
       <c r="M37" s="9"/>
-      <c r="N37" s="46">
+      <c r="N37" s="42">
         <v>19</v>
       </c>
-      <c r="O37" s="47"/>
+      <c r="O37" s="43"/>
       <c r="P37" s="9"/>
-      <c r="Q37" s="46">
+      <c r="Q37" s="42">
         <v>23</v>
       </c>
-      <c r="R37" s="47"/>
+      <c r="R37" s="43"/>
       <c r="S37" s="9"/>
-      <c r="T37" s="46"/>
-      <c r="U37" s="47"/>
+      <c r="T37" s="42"/>
+      <c r="U37" s="43"/>
       <c r="V37" s="9"/>
-      <c r="W37" s="46"/>
-      <c r="X37" s="47"/>
+      <c r="W37" s="42"/>
+      <c r="X37" s="43"/>
       <c r="Y37" s="9"/>
-      <c r="Z37" s="46"/>
-      <c r="AA37" s="47"/>
+      <c r="Z37" s="42"/>
+      <c r="AA37" s="43"/>
       <c r="AB37" s="9"/>
       <c r="AC37" s="11"/>
       <c r="AD37" s="9"/>
@@ -7088,7 +7325,7 @@
       <c r="AF37" s="9"/>
       <c r="AG37" s="9"/>
     </row>
-    <row r="38" spans="1:33" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:33" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="9"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
@@ -7123,7 +7360,7 @@
       <c r="AF38" s="9"/>
       <c r="AG38" s="9"/>
     </row>
-    <row r="39" spans="1:33" ht="18" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:33" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A39" s="9"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
@@ -7144,11 +7381,11 @@
       <c r="P39" s="9"/>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
-      <c r="S39" s="37"/>
-      <c r="T39" s="37"/>
-      <c r="U39" s="37"/>
-      <c r="V39" s="37"/>
-      <c r="W39" s="37"/>
+      <c r="S39" s="49"/>
+      <c r="T39" s="49"/>
+      <c r="U39" s="49"/>
+      <c r="V39" s="49"/>
+      <c r="W39" s="49"/>
       <c r="X39" s="9"/>
       <c r="Y39" s="9"/>
       <c r="Z39" s="9"/>
@@ -7160,7 +7397,7 @@
       <c r="AF39" s="9"/>
       <c r="AG39" s="9"/>
     </row>
-    <row r="40" spans="1:33" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:33" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="9"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
@@ -7197,7 +7434,7 @@
       <c r="AF40" s="9"/>
       <c r="AG40" s="9"/>
     </row>
-    <row r="41" spans="1:33" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:33" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="9"/>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
@@ -7232,7 +7469,7 @@
       <c r="AF41" s="9"/>
       <c r="AG41" s="9"/>
     </row>
-    <row r="42" spans="1:33" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:33" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A42" s="9"/>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
@@ -7285,42 +7522,42 @@
       </c>
       <c r="AG42" s="9"/>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A43" s="9"/>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
       <c r="D43" s="15"/>
-      <c r="E43" s="48" t="s">
+      <c r="E43" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="F43" s="49"/>
+      <c r="F43" s="37"/>
       <c r="G43" s="9"/>
-      <c r="H43" s="48" t="s">
+      <c r="H43" s="36" t="s">
         <v>130</v>
       </c>
-      <c r="I43" s="49"/>
+      <c r="I43" s="37"/>
       <c r="J43" s="9"/>
-      <c r="K43" s="48" t="s">
+      <c r="K43" s="36" t="s">
         <v>163</v>
       </c>
-      <c r="L43" s="49"/>
+      <c r="L43" s="37"/>
       <c r="M43" s="9"/>
-      <c r="N43" s="48" t="s">
+      <c r="N43" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="O43" s="49"/>
+      <c r="O43" s="37"/>
       <c r="P43" s="9"/>
       <c r="Q43" s="17"/>
       <c r="R43" s="9"/>
       <c r="S43" s="9"/>
-      <c r="T43" s="35"/>
-      <c r="U43" s="35"/>
+      <c r="T43" s="44"/>
+      <c r="U43" s="44"/>
       <c r="V43" s="9"/>
-      <c r="W43" s="35"/>
-      <c r="X43" s="35"/>
+      <c r="W43" s="44"/>
+      <c r="X43" s="44"/>
       <c r="Y43" s="9"/>
-      <c r="Z43" s="35"/>
-      <c r="AA43" s="35"/>
+      <c r="Z43" s="44"/>
+      <c r="AA43" s="44"/>
       <c r="AB43" s="9"/>
       <c r="AC43" s="9"/>
       <c r="AD43" s="9"/>
@@ -7330,42 +7567,42 @@
       </c>
       <c r="AG43" s="9"/>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A44" s="9"/>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
       <c r="D44" s="15"/>
-      <c r="E44" s="40" t="s">
+      <c r="E44" s="38" t="s">
         <v>123</v>
       </c>
-      <c r="F44" s="41"/>
+      <c r="F44" s="39"/>
       <c r="G44" s="9"/>
-      <c r="H44" s="40" t="s">
+      <c r="H44" s="38" t="s">
         <v>131</v>
       </c>
-      <c r="I44" s="41"/>
+      <c r="I44" s="39"/>
       <c r="J44" s="9"/>
-      <c r="K44" s="40" t="s">
+      <c r="K44" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="L44" s="41"/>
+      <c r="L44" s="39"/>
       <c r="M44" s="9"/>
-      <c r="N44" s="40" t="s">
+      <c r="N44" s="38" t="s">
         <v>125</v>
       </c>
-      <c r="O44" s="41"/>
+      <c r="O44" s="39"/>
       <c r="P44" s="9"/>
       <c r="Q44" s="17"/>
       <c r="R44" s="9"/>
       <c r="S44" s="9"/>
-      <c r="T44" s="34"/>
-      <c r="U44" s="34"/>
+      <c r="T44" s="46"/>
+      <c r="U44" s="46"/>
       <c r="V44" s="9"/>
-      <c r="W44" s="34"/>
-      <c r="X44" s="34"/>
+      <c r="W44" s="46"/>
+      <c r="X44" s="46"/>
       <c r="Y44" s="9"/>
-      <c r="Z44" s="34"/>
-      <c r="AA44" s="34"/>
+      <c r="Z44" s="46"/>
+      <c r="AA44" s="46"/>
       <c r="AB44" s="11"/>
       <c r="AC44" s="9"/>
       <c r="AD44" s="9"/>
@@ -7375,34 +7612,34 @@
       </c>
       <c r="AG44" s="9"/>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A45" s="9"/>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
       <c r="D45" s="15"/>
-      <c r="E45" s="42"/>
-      <c r="F45" s="43"/>
+      <c r="E45" s="40"/>
+      <c r="F45" s="41"/>
       <c r="G45" s="9"/>
-      <c r="H45" s="42"/>
-      <c r="I45" s="43"/>
+      <c r="H45" s="40"/>
+      <c r="I45" s="41"/>
       <c r="J45" s="9"/>
-      <c r="K45" s="42"/>
-      <c r="L45" s="43"/>
+      <c r="K45" s="40"/>
+      <c r="L45" s="41"/>
       <c r="M45" s="9"/>
-      <c r="N45" s="42"/>
-      <c r="O45" s="43"/>
+      <c r="N45" s="40"/>
+      <c r="O45" s="41"/>
       <c r="P45" s="9"/>
       <c r="Q45" s="17"/>
       <c r="R45" s="9"/>
       <c r="S45" s="9"/>
-      <c r="T45" s="34"/>
-      <c r="U45" s="34"/>
+      <c r="T45" s="46"/>
+      <c r="U45" s="46"/>
       <c r="V45" s="9"/>
-      <c r="W45" s="34"/>
-      <c r="X45" s="34"/>
+      <c r="W45" s="46"/>
+      <c r="X45" s="46"/>
       <c r="Y45" s="9"/>
-      <c r="Z45" s="34"/>
-      <c r="AA45" s="34"/>
+      <c r="Z45" s="46"/>
+      <c r="AA45" s="46"/>
       <c r="AB45" s="28"/>
       <c r="AC45" s="9"/>
       <c r="AD45" s="9"/>
@@ -7412,42 +7649,42 @@
       </c>
       <c r="AG45" s="9"/>
     </row>
-    <row r="46" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="9"/>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
       <c r="D46" s="15"/>
-      <c r="E46" s="46" t="s">
+      <c r="E46" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="F46" s="47"/>
+      <c r="F46" s="43"/>
       <c r="G46" s="9"/>
-      <c r="H46" s="46" t="s">
+      <c r="H46" s="42" t="s">
         <v>153</v>
       </c>
-      <c r="I46" s="47"/>
+      <c r="I46" s="43"/>
       <c r="J46" s="9"/>
-      <c r="K46" s="46" t="s">
+      <c r="K46" s="42" t="s">
         <v>154</v>
       </c>
-      <c r="L46" s="47"/>
+      <c r="L46" s="43"/>
       <c r="M46" s="9"/>
-      <c r="N46" s="46" t="s">
+      <c r="N46" s="42" t="s">
         <v>160</v>
       </c>
-      <c r="O46" s="47"/>
+      <c r="O46" s="43"/>
       <c r="P46" s="9"/>
       <c r="Q46" s="17"/>
       <c r="R46" s="9"/>
       <c r="S46" s="9"/>
-      <c r="T46" s="36"/>
-      <c r="U46" s="36"/>
+      <c r="T46" s="45"/>
+      <c r="U46" s="45"/>
       <c r="V46" s="9"/>
-      <c r="W46" s="36"/>
-      <c r="X46" s="36"/>
+      <c r="W46" s="45"/>
+      <c r="X46" s="45"/>
       <c r="Y46" s="9"/>
-      <c r="Z46" s="36"/>
-      <c r="AA46" s="36"/>
+      <c r="Z46" s="45"/>
+      <c r="AA46" s="45"/>
       <c r="AB46" s="27"/>
       <c r="AC46" s="9"/>
       <c r="AD46" s="9"/>
@@ -7457,7 +7694,7 @@
       </c>
       <c r="AG46" s="9"/>
     </row>
-    <row r="47" spans="1:33" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:33" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="9"/>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
@@ -7487,12 +7724,12 @@
       <c r="AA47" s="27"/>
       <c r="AB47" s="27"/>
       <c r="AC47" s="9"/>
-      <c r="AD47" s="35"/>
-      <c r="AE47" s="35"/>
+      <c r="AD47" s="44"/>
+      <c r="AE47" s="44"/>
       <c r="AF47" s="9"/>
       <c r="AG47" s="9"/>
     </row>
-    <row r="48" spans="1:33" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:33" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A48" s="9"/>
       <c r="B48" s="9"/>
       <c r="C48" s="9"/>
@@ -7538,125 +7775,125 @@
       <c r="AA48" s="11"/>
       <c r="AB48" s="29"/>
       <c r="AC48" s="9"/>
-      <c r="AD48" s="34"/>
-      <c r="AE48" s="34"/>
+      <c r="AD48" s="46"/>
+      <c r="AE48" s="46"/>
       <c r="AF48" s="9"/>
       <c r="AG48" s="9"/>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A49" s="9"/>
       <c r="B49" s="9"/>
       <c r="C49" s="9"/>
       <c r="D49" s="15"/>
-      <c r="E49" s="48" t="s">
+      <c r="E49" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="F49" s="49"/>
+      <c r="F49" s="37"/>
       <c r="G49" s="9"/>
-      <c r="H49" s="48" t="s">
+      <c r="H49" s="36" t="s">
         <v>132</v>
       </c>
-      <c r="I49" s="49"/>
+      <c r="I49" s="37"/>
       <c r="J49" s="9"/>
-      <c r="K49" s="48" t="s">
+      <c r="K49" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="L49" s="49"/>
+      <c r="L49" s="37"/>
       <c r="M49" s="9"/>
-      <c r="N49" s="48" t="s">
+      <c r="N49" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="O49" s="49"/>
+      <c r="O49" s="37"/>
       <c r="P49" s="9"/>
       <c r="Q49" s="17"/>
       <c r="R49" s="9"/>
       <c r="S49" s="9"/>
-      <c r="T49" s="35"/>
-      <c r="U49" s="35"/>
+      <c r="T49" s="44"/>
+      <c r="U49" s="44"/>
       <c r="V49" s="9"/>
-      <c r="W49" s="35"/>
-      <c r="X49" s="35"/>
+      <c r="W49" s="44"/>
+      <c r="X49" s="44"/>
       <c r="Y49" s="9"/>
-      <c r="Z49" s="35"/>
-      <c r="AA49" s="35"/>
+      <c r="Z49" s="44"/>
+      <c r="AA49" s="44"/>
       <c r="AB49" s="9"/>
       <c r="AC49" s="9"/>
-      <c r="AD49" s="34"/>
-      <c r="AE49" s="34"/>
+      <c r="AD49" s="46"/>
+      <c r="AE49" s="46"/>
       <c r="AF49" s="9"/>
       <c r="AG49" s="9"/>
     </row>
-    <row r="50" spans="1:33" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:33" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="9"/>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
       <c r="D50" s="15"/>
-      <c r="E50" s="40" t="s">
+      <c r="E50" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="F50" s="41"/>
+      <c r="F50" s="39"/>
       <c r="G50" s="9"/>
-      <c r="H50" s="40" t="s">
+      <c r="H50" s="38" t="s">
         <v>133</v>
       </c>
-      <c r="I50" s="41"/>
+      <c r="I50" s="39"/>
       <c r="J50" s="9"/>
-      <c r="K50" s="40" t="s">
+      <c r="K50" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="L50" s="41"/>
+      <c r="L50" s="39"/>
       <c r="M50" s="9"/>
-      <c r="N50" s="40" t="s">
+      <c r="N50" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="O50" s="41"/>
+      <c r="O50" s="39"/>
       <c r="P50" s="9"/>
       <c r="Q50" s="17"/>
       <c r="R50" s="9"/>
       <c r="S50" s="9"/>
-      <c r="T50" s="34"/>
-      <c r="U50" s="34"/>
+      <c r="T50" s="46"/>
+      <c r="U50" s="46"/>
       <c r="V50" s="9"/>
-      <c r="W50" s="34"/>
-      <c r="X50" s="34"/>
+      <c r="W50" s="46"/>
+      <c r="X50" s="46"/>
       <c r="Y50" s="9"/>
-      <c r="Z50" s="34"/>
-      <c r="AA50" s="34"/>
+      <c r="Z50" s="46"/>
+      <c r="AA50" s="46"/>
       <c r="AB50" s="11"/>
       <c r="AC50" s="9"/>
-      <c r="AD50" s="36"/>
-      <c r="AE50" s="36"/>
+      <c r="AD50" s="45"/>
+      <c r="AE50" s="45"/>
       <c r="AF50" s="9"/>
       <c r="AG50" s="9"/>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A51" s="9"/>
       <c r="B51" s="9"/>
       <c r="C51" s="9"/>
       <c r="D51" s="15"/>
-      <c r="E51" s="42"/>
-      <c r="F51" s="43"/>
+      <c r="E51" s="40"/>
+      <c r="F51" s="41"/>
       <c r="G51" s="9"/>
-      <c r="H51" s="42"/>
-      <c r="I51" s="43"/>
+      <c r="H51" s="40"/>
+      <c r="I51" s="41"/>
       <c r="J51" s="9"/>
-      <c r="K51" s="42"/>
-      <c r="L51" s="43"/>
+      <c r="K51" s="40"/>
+      <c r="L51" s="41"/>
       <c r="M51" s="9"/>
-      <c r="N51" s="42"/>
-      <c r="O51" s="43"/>
+      <c r="N51" s="40"/>
+      <c r="O51" s="41"/>
       <c r="P51" s="9"/>
       <c r="Q51" s="17"/>
       <c r="R51" s="9"/>
       <c r="S51" s="9"/>
-      <c r="T51" s="34"/>
-      <c r="U51" s="34"/>
+      <c r="T51" s="46"/>
+      <c r="U51" s="46"/>
       <c r="V51" s="9"/>
-      <c r="W51" s="34"/>
-      <c r="X51" s="34"/>
+      <c r="W51" s="46"/>
+      <c r="X51" s="46"/>
       <c r="Y51" s="9"/>
-      <c r="Z51" s="34"/>
-      <c r="AA51" s="34"/>
+      <c r="Z51" s="46"/>
+      <c r="AA51" s="46"/>
       <c r="AB51" s="28"/>
       <c r="AC51" s="9"/>
       <c r="AD51" s="9"/>
@@ -7664,42 +7901,42 @@
       <c r="AF51" s="9"/>
       <c r="AG51" s="9"/>
     </row>
-    <row r="52" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="9"/>
       <c r="B52" s="9"/>
       <c r="C52" s="9"/>
       <c r="D52" s="15"/>
-      <c r="E52" s="46">
+      <c r="E52" s="42">
         <v>18</v>
       </c>
-      <c r="F52" s="47"/>
+      <c r="F52" s="43"/>
       <c r="G52" s="9"/>
-      <c r="H52" s="46">
+      <c r="H52" s="42">
         <v>35</v>
       </c>
-      <c r="I52" s="47"/>
+      <c r="I52" s="43"/>
       <c r="J52" s="9"/>
-      <c r="K52" s="46" t="s">
+      <c r="K52" s="42" t="s">
         <v>159</v>
       </c>
-      <c r="L52" s="47"/>
+      <c r="L52" s="43"/>
       <c r="M52" s="9"/>
-      <c r="N52" s="46">
+      <c r="N52" s="42">
         <v>42</v>
       </c>
-      <c r="O52" s="47"/>
+      <c r="O52" s="43"/>
       <c r="P52" s="9"/>
       <c r="Q52" s="17"/>
       <c r="R52" s="9"/>
       <c r="S52" s="9"/>
-      <c r="T52" s="36"/>
-      <c r="U52" s="36"/>
+      <c r="T52" s="45"/>
+      <c r="U52" s="45"/>
       <c r="V52" s="9"/>
-      <c r="W52" s="36"/>
-      <c r="X52" s="36"/>
+      <c r="W52" s="45"/>
+      <c r="X52" s="45"/>
       <c r="Y52" s="9"/>
-      <c r="Z52" s="36"/>
-      <c r="AA52" s="36"/>
+      <c r="Z52" s="45"/>
+      <c r="AA52" s="45"/>
       <c r="AB52" s="27"/>
       <c r="AC52" s="9"/>
       <c r="AD52" s="9"/>
@@ -7707,7 +7944,7 @@
       <c r="AF52" s="9"/>
       <c r="AG52" s="9"/>
     </row>
-    <row r="53" spans="1:33" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:33" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="9"/>
       <c r="B53" s="9"/>
       <c r="C53" s="9"/>
@@ -7742,7 +7979,7 @@
       <c r="AF53" s="9"/>
       <c r="AG53" s="9"/>
     </row>
-    <row r="54" spans="1:33" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:33" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A54" s="9"/>
       <c r="B54" s="9"/>
       <c r="C54" s="9"/>
@@ -7793,39 +8030,39 @@
       <c r="AF54" s="9"/>
       <c r="AG54" s="9"/>
     </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A55" s="9"/>
       <c r="B55" s="9"/>
       <c r="C55" s="9"/>
       <c r="D55" s="15"/>
-      <c r="E55" s="48" t="s">
+      <c r="E55" s="36" t="s">
         <v>165</v>
       </c>
-      <c r="F55" s="49"/>
+      <c r="F55" s="37"/>
       <c r="G55" s="9"/>
-      <c r="H55" s="44" t="s">
+      <c r="H55" s="47" t="s">
         <v>167</v>
       </c>
-      <c r="I55" s="45"/>
+      <c r="I55" s="48"/>
       <c r="J55" s="9"/>
-      <c r="K55" s="44" t="s">
+      <c r="K55" s="47" t="s">
         <v>166</v>
       </c>
-      <c r="L55" s="45"/>
+      <c r="L55" s="48"/>
       <c r="M55" s="9"/>
-      <c r="N55" s="48" t="s">
+      <c r="N55" s="36" t="s">
         <v>164</v>
       </c>
-      <c r="O55" s="49"/>
+      <c r="O55" s="37"/>
       <c r="P55" s="9"/>
       <c r="Q55" s="17"/>
       <c r="R55" s="9"/>
       <c r="S55" s="9"/>
-      <c r="T55" s="35"/>
-      <c r="U55" s="35"/>
+      <c r="T55" s="44"/>
+      <c r="U55" s="44"/>
       <c r="V55" s="9"/>
-      <c r="W55" s="35"/>
-      <c r="X55" s="35"/>
+      <c r="W55" s="44"/>
+      <c r="X55" s="44"/>
       <c r="Y55" s="9"/>
       <c r="Z55" s="9"/>
       <c r="AA55" s="9"/>
@@ -7836,39 +8073,39 @@
       <c r="AF55" s="9"/>
       <c r="AG55" s="9"/>
     </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A56" s="9"/>
       <c r="B56" s="9"/>
       <c r="C56" s="9"/>
       <c r="D56" s="15"/>
-      <c r="E56" s="40" t="s">
+      <c r="E56" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="F56" s="41"/>
+      <c r="F56" s="39"/>
       <c r="G56" s="9"/>
-      <c r="H56" s="40" t="s">
+      <c r="H56" s="38" t="s">
         <v>168</v>
       </c>
-      <c r="I56" s="41"/>
+      <c r="I56" s="39"/>
       <c r="J56" s="9"/>
-      <c r="K56" s="40" t="s">
+      <c r="K56" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="L56" s="41"/>
+      <c r="L56" s="39"/>
       <c r="M56" s="9"/>
-      <c r="N56" s="40" t="s">
+      <c r="N56" s="38" t="s">
         <v>138</v>
       </c>
-      <c r="O56" s="41"/>
+      <c r="O56" s="39"/>
       <c r="P56" s="9"/>
       <c r="Q56" s="17"/>
       <c r="R56" s="9"/>
       <c r="S56" s="9"/>
-      <c r="T56" s="34"/>
-      <c r="U56" s="34"/>
+      <c r="T56" s="46"/>
+      <c r="U56" s="46"/>
       <c r="V56" s="9"/>
-      <c r="W56" s="34"/>
-      <c r="X56" s="34"/>
+      <c r="W56" s="46"/>
+      <c r="X56" s="46"/>
       <c r="Y56" s="9"/>
       <c r="Z56" s="9"/>
       <c r="AA56" s="9"/>
@@ -7879,31 +8116,31 @@
       <c r="AF56" s="9"/>
       <c r="AG56" s="9"/>
     </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A57" s="9"/>
       <c r="B57" s="9"/>
       <c r="C57" s="9"/>
       <c r="D57" s="15"/>
-      <c r="E57" s="42"/>
-      <c r="F57" s="43"/>
+      <c r="E57" s="40"/>
+      <c r="F57" s="41"/>
       <c r="G57" s="9"/>
-      <c r="H57" s="42"/>
-      <c r="I57" s="43"/>
+      <c r="H57" s="40"/>
+      <c r="I57" s="41"/>
       <c r="J57" s="9"/>
-      <c r="K57" s="42"/>
-      <c r="L57" s="43"/>
+      <c r="K57" s="40"/>
+      <c r="L57" s="41"/>
       <c r="M57" s="9"/>
-      <c r="N57" s="42"/>
-      <c r="O57" s="43"/>
+      <c r="N57" s="40"/>
+      <c r="O57" s="41"/>
       <c r="P57" s="9"/>
       <c r="Q57" s="17"/>
       <c r="R57" s="9"/>
       <c r="S57" s="9"/>
-      <c r="T57" s="34"/>
-      <c r="U57" s="34"/>
+      <c r="T57" s="46"/>
+      <c r="U57" s="46"/>
       <c r="V57" s="9"/>
-      <c r="W57" s="34"/>
-      <c r="X57" s="34"/>
+      <c r="W57" s="46"/>
+      <c r="X57" s="46"/>
       <c r="Y57" s="9"/>
       <c r="Z57" s="9"/>
       <c r="AA57" s="9"/>
@@ -7914,38 +8151,38 @@
       <c r="AF57" s="9"/>
       <c r="AG57" s="9"/>
     </row>
-    <row r="58" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="9"/>
       <c r="B58" s="9"/>
       <c r="C58" s="9"/>
       <c r="D58" s="15"/>
-      <c r="E58" s="46" t="s">
+      <c r="E58" s="42" t="s">
         <v>161</v>
       </c>
-      <c r="F58" s="47"/>
+      <c r="F58" s="43"/>
       <c r="G58" s="9"/>
-      <c r="H58" s="38" t="s">
+      <c r="H58" s="50" t="s">
         <v>169</v>
       </c>
-      <c r="I58" s="39"/>
+      <c r="I58" s="51"/>
       <c r="J58" s="9"/>
-      <c r="K58" s="38">
+      <c r="K58" s="50">
         <v>43</v>
       </c>
-      <c r="L58" s="39"/>
+      <c r="L58" s="51"/>
       <c r="M58" s="9"/>
-      <c r="N58" s="46" t="s">
+      <c r="N58" s="42" t="s">
         <v>153</v>
       </c>
-      <c r="O58" s="47"/>
+      <c r="O58" s="43"/>
       <c r="P58" s="9"/>
       <c r="Q58" s="17"/>
       <c r="S58" s="9"/>
-      <c r="T58" s="36"/>
-      <c r="U58" s="36"/>
+      <c r="T58" s="45"/>
+      <c r="U58" s="45"/>
       <c r="V58" s="9"/>
-      <c r="W58" s="36"/>
-      <c r="X58" s="36"/>
+      <c r="W58" s="45"/>
+      <c r="X58" s="45"/>
       <c r="Y58" s="9"/>
       <c r="Z58" s="9"/>
       <c r="AA58" s="9"/>
@@ -7956,7 +8193,7 @@
       <c r="AF58" s="9"/>
       <c r="AG58" s="9"/>
     </row>
-    <row r="59" spans="1:33" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:33" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="9"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
@@ -7993,156 +8230,54 @@
     </row>
   </sheetData>
   <mergeCells count="222">
-    <mergeCell ref="D2:AF2"/>
-    <mergeCell ref="D3:AF3"/>
-    <mergeCell ref="D4:AF4"/>
-    <mergeCell ref="D5:AF5"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="Q7:R7"/>
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="W7:X7"/>
-    <mergeCell ref="Z7:AA7"/>
-    <mergeCell ref="AC7:AD7"/>
-    <mergeCell ref="AC10:AD10"/>
-    <mergeCell ref="B11:C12"/>
-    <mergeCell ref="E11:F12"/>
-    <mergeCell ref="H11:I12"/>
-    <mergeCell ref="K11:L12"/>
-    <mergeCell ref="N11:O12"/>
-    <mergeCell ref="Q11:R12"/>
-    <mergeCell ref="T11:U12"/>
-    <mergeCell ref="W11:X12"/>
-    <mergeCell ref="Z11:AA12"/>
-    <mergeCell ref="AC11:AD12"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="Q10:R10"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="W10:X10"/>
-    <mergeCell ref="Z10:AA10"/>
-    <mergeCell ref="AC13:AD13"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="T16:U16"/>
-    <mergeCell ref="W16:X16"/>
-    <mergeCell ref="Z16:AA16"/>
-    <mergeCell ref="AC16:AD16"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="T13:U13"/>
-    <mergeCell ref="W13:X13"/>
-    <mergeCell ref="Z13:AA13"/>
-    <mergeCell ref="AC17:AD18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="W19:X19"/>
-    <mergeCell ref="Z19:AA19"/>
-    <mergeCell ref="AC19:AD19"/>
-    <mergeCell ref="B17:C18"/>
-    <mergeCell ref="E17:F18"/>
-    <mergeCell ref="H17:I18"/>
-    <mergeCell ref="K17:L18"/>
-    <mergeCell ref="N17:O18"/>
-    <mergeCell ref="Q17:R18"/>
-    <mergeCell ref="T17:U18"/>
-    <mergeCell ref="W17:X18"/>
-    <mergeCell ref="Z17:AA18"/>
-    <mergeCell ref="AC22:AD22"/>
-    <mergeCell ref="B23:C24"/>
-    <mergeCell ref="E23:F24"/>
-    <mergeCell ref="H23:I24"/>
-    <mergeCell ref="K23:L24"/>
-    <mergeCell ref="N23:O24"/>
-    <mergeCell ref="Q23:R24"/>
-    <mergeCell ref="T23:U24"/>
-    <mergeCell ref="W23:X24"/>
-    <mergeCell ref="Z23:AA24"/>
-    <mergeCell ref="AC23:AD24"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="W22:X22"/>
-    <mergeCell ref="Z22:AA22"/>
-    <mergeCell ref="AC25:AD25"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="T28:U28"/>
-    <mergeCell ref="W28:X28"/>
-    <mergeCell ref="Z28:AA28"/>
-    <mergeCell ref="AC28:AD28"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="T25:U25"/>
-    <mergeCell ref="W25:X25"/>
-    <mergeCell ref="Z25:AA25"/>
-    <mergeCell ref="AC29:AD30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="T31:U31"/>
-    <mergeCell ref="W31:X31"/>
-    <mergeCell ref="Z31:AA31"/>
-    <mergeCell ref="AC31:AD31"/>
-    <mergeCell ref="B29:C30"/>
-    <mergeCell ref="E29:F30"/>
-    <mergeCell ref="H29:I30"/>
-    <mergeCell ref="K29:L30"/>
-    <mergeCell ref="N29:O30"/>
-    <mergeCell ref="Q29:R30"/>
-    <mergeCell ref="T29:U30"/>
-    <mergeCell ref="W29:X30"/>
-    <mergeCell ref="Z29:AA30"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="N34:O34"/>
-    <mergeCell ref="Q34:R34"/>
-    <mergeCell ref="T34:U34"/>
-    <mergeCell ref="W34:X34"/>
-    <mergeCell ref="Z34:AA34"/>
-    <mergeCell ref="E35:F36"/>
-    <mergeCell ref="H35:I36"/>
-    <mergeCell ref="K35:L36"/>
-    <mergeCell ref="N35:O36"/>
-    <mergeCell ref="Q35:R36"/>
-    <mergeCell ref="T35:U36"/>
-    <mergeCell ref="W35:X36"/>
-    <mergeCell ref="Z35:AA36"/>
+    <mergeCell ref="Z50:AA51"/>
+    <mergeCell ref="W55:X55"/>
+    <mergeCell ref="W56:X57"/>
+    <mergeCell ref="W58:X58"/>
+    <mergeCell ref="S39:W39"/>
+    <mergeCell ref="K58:L58"/>
+    <mergeCell ref="E50:F51"/>
+    <mergeCell ref="H50:I51"/>
+    <mergeCell ref="K50:L51"/>
+    <mergeCell ref="N50:O51"/>
+    <mergeCell ref="T56:U57"/>
+    <mergeCell ref="T44:U45"/>
+    <mergeCell ref="T49:U49"/>
+    <mergeCell ref="W43:X43"/>
+    <mergeCell ref="W49:X49"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="H56:I57"/>
+    <mergeCell ref="T52:U52"/>
+    <mergeCell ref="W46:X46"/>
+    <mergeCell ref="W52:X52"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="T50:U51"/>
+    <mergeCell ref="W44:X45"/>
+    <mergeCell ref="W50:X51"/>
+    <mergeCell ref="N58:O58"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="E44:F45"/>
+    <mergeCell ref="H44:I45"/>
+    <mergeCell ref="K44:L45"/>
+    <mergeCell ref="N44:O45"/>
+    <mergeCell ref="N56:O57"/>
+    <mergeCell ref="E56:F57"/>
+    <mergeCell ref="AD47:AE47"/>
+    <mergeCell ref="AD48:AE49"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="N49:O49"/>
+    <mergeCell ref="T55:U55"/>
+    <mergeCell ref="K55:L55"/>
+    <mergeCell ref="K56:L57"/>
+    <mergeCell ref="AD50:AE50"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="K52:L52"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="T58:U58"/>
+    <mergeCell ref="T46:U46"/>
     <mergeCell ref="W37:X37"/>
     <mergeCell ref="Z37:AA37"/>
     <mergeCell ref="E43:F43"/>
@@ -8167,54 +8302,156 @@
     <mergeCell ref="Z46:AA46"/>
     <mergeCell ref="Z52:AA52"/>
     <mergeCell ref="Z44:AA45"/>
-    <mergeCell ref="N58:O58"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="E44:F45"/>
-    <mergeCell ref="H44:I45"/>
-    <mergeCell ref="K44:L45"/>
-    <mergeCell ref="N44:O45"/>
-    <mergeCell ref="N56:O57"/>
-    <mergeCell ref="E56:F57"/>
-    <mergeCell ref="AD47:AE47"/>
-    <mergeCell ref="AD48:AE49"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="N49:O49"/>
-    <mergeCell ref="T55:U55"/>
-    <mergeCell ref="K55:L55"/>
-    <mergeCell ref="K56:L57"/>
-    <mergeCell ref="AD50:AE50"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="K52:L52"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="T58:U58"/>
-    <mergeCell ref="T46:U46"/>
-    <mergeCell ref="Z50:AA51"/>
-    <mergeCell ref="W55:X55"/>
-    <mergeCell ref="W56:X57"/>
-    <mergeCell ref="W58:X58"/>
-    <mergeCell ref="S39:W39"/>
-    <mergeCell ref="K58:L58"/>
-    <mergeCell ref="E50:F51"/>
-    <mergeCell ref="H50:I51"/>
-    <mergeCell ref="K50:L51"/>
-    <mergeCell ref="N50:O51"/>
-    <mergeCell ref="T56:U57"/>
-    <mergeCell ref="T44:U45"/>
-    <mergeCell ref="T49:U49"/>
-    <mergeCell ref="W43:X43"/>
-    <mergeCell ref="W49:X49"/>
-    <mergeCell ref="H55:I55"/>
-    <mergeCell ref="H56:I57"/>
-    <mergeCell ref="T52:U52"/>
-    <mergeCell ref="W46:X46"/>
-    <mergeCell ref="W52:X52"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="T50:U51"/>
-    <mergeCell ref="W44:X45"/>
-    <mergeCell ref="W50:X51"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="Q34:R34"/>
+    <mergeCell ref="T34:U34"/>
+    <mergeCell ref="W34:X34"/>
+    <mergeCell ref="Z34:AA34"/>
+    <mergeCell ref="E35:F36"/>
+    <mergeCell ref="H35:I36"/>
+    <mergeCell ref="K35:L36"/>
+    <mergeCell ref="N35:O36"/>
+    <mergeCell ref="Q35:R36"/>
+    <mergeCell ref="T35:U36"/>
+    <mergeCell ref="W35:X36"/>
+    <mergeCell ref="Z35:AA36"/>
+    <mergeCell ref="AC29:AD30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="T31:U31"/>
+    <mergeCell ref="W31:X31"/>
+    <mergeCell ref="Z31:AA31"/>
+    <mergeCell ref="AC31:AD31"/>
+    <mergeCell ref="B29:C30"/>
+    <mergeCell ref="E29:F30"/>
+    <mergeCell ref="H29:I30"/>
+    <mergeCell ref="K29:L30"/>
+    <mergeCell ref="N29:O30"/>
+    <mergeCell ref="Q29:R30"/>
+    <mergeCell ref="T29:U30"/>
+    <mergeCell ref="W29:X30"/>
+    <mergeCell ref="Z29:AA30"/>
+    <mergeCell ref="AC25:AD25"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="T28:U28"/>
+    <mergeCell ref="W28:X28"/>
+    <mergeCell ref="Z28:AA28"/>
+    <mergeCell ref="AC28:AD28"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="T25:U25"/>
+    <mergeCell ref="W25:X25"/>
+    <mergeCell ref="Z25:AA25"/>
+    <mergeCell ref="AC22:AD22"/>
+    <mergeCell ref="B23:C24"/>
+    <mergeCell ref="E23:F24"/>
+    <mergeCell ref="H23:I24"/>
+    <mergeCell ref="K23:L24"/>
+    <mergeCell ref="N23:O24"/>
+    <mergeCell ref="Q23:R24"/>
+    <mergeCell ref="T23:U24"/>
+    <mergeCell ref="W23:X24"/>
+    <mergeCell ref="Z23:AA24"/>
+    <mergeCell ref="AC23:AD24"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="W22:X22"/>
+    <mergeCell ref="Z22:AA22"/>
+    <mergeCell ref="AC17:AD18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="W19:X19"/>
+    <mergeCell ref="Z19:AA19"/>
+    <mergeCell ref="AC19:AD19"/>
+    <mergeCell ref="B17:C18"/>
+    <mergeCell ref="E17:F18"/>
+    <mergeCell ref="H17:I18"/>
+    <mergeCell ref="K17:L18"/>
+    <mergeCell ref="N17:O18"/>
+    <mergeCell ref="Q17:R18"/>
+    <mergeCell ref="T17:U18"/>
+    <mergeCell ref="W17:X18"/>
+    <mergeCell ref="Z17:AA18"/>
+    <mergeCell ref="AC13:AD13"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="W16:X16"/>
+    <mergeCell ref="Z16:AA16"/>
+    <mergeCell ref="AC16:AD16"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="T13:U13"/>
+    <mergeCell ref="W13:X13"/>
+    <mergeCell ref="Z13:AA13"/>
+    <mergeCell ref="AC10:AD10"/>
+    <mergeCell ref="B11:C12"/>
+    <mergeCell ref="E11:F12"/>
+    <mergeCell ref="H11:I12"/>
+    <mergeCell ref="K11:L12"/>
+    <mergeCell ref="N11:O12"/>
+    <mergeCell ref="Q11:R12"/>
+    <mergeCell ref="T11:U12"/>
+    <mergeCell ref="W11:X12"/>
+    <mergeCell ref="Z11:AA12"/>
+    <mergeCell ref="AC11:AD12"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="Q10:R10"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="W10:X10"/>
+    <mergeCell ref="Z10:AA10"/>
+    <mergeCell ref="D2:AF2"/>
+    <mergeCell ref="D3:AF3"/>
+    <mergeCell ref="D4:AF4"/>
+    <mergeCell ref="D5:AF5"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="W7:X7"/>
+    <mergeCell ref="Z7:AA7"/>
+    <mergeCell ref="AC7:AD7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/PensumOriginal1.xlsx
+++ b/PensumOriginal1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97FC5CE0-D682-4210-8912-4A1DEDB3FEE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A8992FA-41E6-471F-AFC1-ED10200571FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" tabRatio="404" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="404" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Actual" sheetId="11" r:id="rId1"/>
@@ -25,9 +25,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1017,7 +1014,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1076,19 +1073,24 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1102,35 +1104,29 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2832,15 +2828,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>110243</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>189058</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>182803</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>62619</xdr:colOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>33755</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>103333</xdr:rowOff>
+      <xdr:rowOff>93712</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2855,8 +2851,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5845087" y="5467496"/>
-          <a:ext cx="1043782" cy="886618"/>
+          <a:off x="5811212" y="5291667"/>
+          <a:ext cx="1322998" cy="1103939"/>
         </a:xfrm>
         <a:prstGeom prst="mathMultiply">
           <a:avLst/>
@@ -3328,16 +3324,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>98676</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>406553</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>131929</xdr:rowOff>
+      <xdr:rowOff>83822</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>51052</xdr:colOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>9619</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>46204</xdr:rowOff>
+      <xdr:rowOff>182802</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3352,8 +3348,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6036338" y="6208137"/>
-          <a:ext cx="1080532" cy="844509"/>
+          <a:off x="5755947" y="6597383"/>
+          <a:ext cx="1354127" cy="1080343"/>
         </a:xfrm>
         <a:prstGeom prst="mathMultiply">
           <a:avLst/>
@@ -3575,7 +3571,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="FFFF00">
+          <a:srgbClr val="00B050">
             <a:alpha val="58000"/>
           </a:srgbClr>
         </a:solidFill>
@@ -3640,7 +3636,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="FFFF00">
+          <a:srgbClr val="00B050">
             <a:alpha val="58000"/>
           </a:srgbClr>
         </a:solidFill>
@@ -3705,7 +3701,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="FFFF00">
+          <a:srgbClr val="00B050">
             <a:alpha val="58000"/>
           </a:srgbClr>
         </a:solidFill>
@@ -3770,7 +3766,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="FFFF00">
+          <a:srgbClr val="00B050">
             <a:alpha val="58000"/>
           </a:srgbClr>
         </a:solidFill>
@@ -3877,15 +3873,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>422060</xdr:colOff>
+      <xdr:colOff>460546</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>174539</xdr:rowOff>
+      <xdr:rowOff>184161</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>97436</xdr:colOff>
+      <xdr:colOff>135922</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>32075</xdr:rowOff>
+      <xdr:rowOff>41697</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3900,8 +3896,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9052876" y="2925126"/>
-          <a:ext cx="1415147" cy="1276566"/>
+          <a:off x="9148501" y="2906964"/>
+          <a:ext cx="1570754" cy="1262233"/>
         </a:xfrm>
         <a:prstGeom prst="mathMultiply">
           <a:avLst/>
@@ -4158,15 +4154,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>383366</xdr:colOff>
+      <xdr:colOff>404073</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>182441</xdr:rowOff>
+      <xdr:rowOff>172088</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>60490</xdr:colOff>
+      <xdr:colOff>81197</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>237329</xdr:rowOff>
+      <xdr:rowOff>226976</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4181,8 +4177,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2395279" y="8453640"/>
-          <a:ext cx="1416895" cy="1289250"/>
+          <a:off x="2407429" y="8314928"/>
+          <a:ext cx="1406119" cy="1281749"/>
         </a:xfrm>
         <a:prstGeom prst="mathMultiply">
           <a:avLst/>
@@ -4223,15 +4219,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>367888</xdr:colOff>
+      <xdr:colOff>383418</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>235349</xdr:rowOff>
+      <xdr:rowOff>214642</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>45012</xdr:colOff>
+      <xdr:colOff>60542</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>37533</xdr:rowOff>
+      <xdr:rowOff>16826</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4246,8 +4242,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4576383" y="8506548"/>
-          <a:ext cx="1416894" cy="1289250"/>
+          <a:off x="4571312" y="8357482"/>
+          <a:ext cx="1406119" cy="1287877"/>
         </a:xfrm>
         <a:prstGeom prst="mathMultiply">
           <a:avLst/>
@@ -4352,71 +4348,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>405740</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>118754</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>57148</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>174302</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="26" name="Signo de multiplicación 25">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2618BEE6-93A7-4AE0-BA7E-D721B8AD49A7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8124701" y="5997040"/>
-          <a:ext cx="1462395" cy="1183704"/>
-        </a:xfrm>
-        <a:prstGeom prst="mathMultiply">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFF00">
-            <a:alpha val="58000"/>
-          </a:srgbClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="es-ES" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>421501</xdr:colOff>
       <xdr:row>31</xdr:row>
@@ -4448,671 +4379,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-            <a:alpha val="58000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="es-ES" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>405667</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>124748</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>86764</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>35743</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="Signo de multiplicación 28">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FADB80A-04AD-46B3-AA8C-57E86C752DF6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9282472" y="1757605"/>
-          <a:ext cx="1462396" cy="1207385"/>
-        </a:xfrm>
-        <a:prstGeom prst="mathMultiply">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-            <a:alpha val="58000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="es-ES" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>419522</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>49537</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>100619</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>148558</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="41" name="Signo de multiplicación 40">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{380F3D2D-A694-470F-B354-4899A5346C07}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9296327" y="3899121"/>
-          <a:ext cx="1462396" cy="1207385"/>
-        </a:xfrm>
-        <a:prstGeom prst="mathMultiply">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-            <a:alpha val="58000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="es-ES" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>423480</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>23807</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>104577</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>112932</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="54" name="Signo de multiplicación 53">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9206D917-CB66-48D5-87B1-980CB1AA6D93}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9300285" y="4981755"/>
-          <a:ext cx="1462396" cy="1207385"/>
-        </a:xfrm>
-        <a:prstGeom prst="mathMultiply">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-            <a:alpha val="58000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="es-ES" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>377958</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>136622</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>59055</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>17929</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="55" name="Signo de multiplicación 54">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{131C6E6E-4C55-4BCB-A6D0-83B912D604C8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9254763" y="6014908"/>
-          <a:ext cx="1462396" cy="1207385"/>
-        </a:xfrm>
-        <a:prstGeom prst="mathMultiply">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-            <a:alpha val="58000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="es-ES" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>395136</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>226550</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>76234</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>49187</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="56" name="Signo de multiplicación 55">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD3F2C7C-0CB5-495B-8E16-405627E6415F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3505340" y="8497749"/>
-          <a:ext cx="1420868" cy="1309703"/>
-        </a:xfrm>
-        <a:prstGeom prst="mathMultiply">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-            <a:alpha val="58000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="es-ES" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>398918</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>181381</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>80015</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>182148</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="59" name="Signo de multiplicación 58">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A80F29B0-5E1C-4242-B7BD-36762DCF4C52}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2410831" y="9686942"/>
-          <a:ext cx="1420868" cy="1293446"/>
-        </a:xfrm>
-        <a:prstGeom prst="mathMultiply">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="tx2">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-            <a:alpha val="58000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="es-ES" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>419839</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>154117</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>100936</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>35424</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="60" name="Signo de multiplicación 59">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6F00A2D-2EBD-446F-ACF6-909294B7D78B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10148946" y="5315112"/>
-          <a:ext cx="1420868" cy="1300338"/>
-        </a:xfrm>
-        <a:prstGeom prst="mathMultiply">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="7030A0">
-            <a:alpha val="58000"/>
-          </a:srgbClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="es-ES" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>436168</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>160726</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>117265</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>42034</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="61" name="Signo de multiplicación 60">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59848488-7775-4955-BF22-D03D5C7E02F2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10165275" y="4116517"/>
-          <a:ext cx="1420868" cy="1300338"/>
-        </a:xfrm>
-        <a:prstGeom prst="mathMultiply">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="7030A0">
-            <a:alpha val="58000"/>
-          </a:srgbClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="es-ES" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>384461</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>206212</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>65558</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>87520</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="62" name="Signo de multiplicación 61">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F4E8883-DC01-43E4-8A63-21FB85581689}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10113568" y="2956799"/>
-          <a:ext cx="1420868" cy="1300338"/>
-        </a:xfrm>
-        <a:prstGeom prst="mathMultiply">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="7030A0">
-            <a:alpha val="58000"/>
-          </a:srgbClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="es-ES" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>361912</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>144785</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>43009</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>35812</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="63" name="Signo de multiplicación 62">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C45CF3F8-69ED-4C2E-9280-6A67CD84417F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10091019" y="1699887"/>
-          <a:ext cx="1420868" cy="1300338"/>
-        </a:xfrm>
-        <a:prstGeom prst="mathMultiply">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="7030A0">
+          <a:srgbClr val="00B050">
             <a:alpha val="58000"/>
           </a:srgbClr>
         </a:solidFill>
@@ -5148,9 +4415,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5188,9 +4455,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -5223,26 +4490,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -5275,26 +4525,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5486,11 +4719,13 @@
     <col min="20" max="20" width="6.85546875" customWidth="1"/>
     <col min="21" max="21" width="7.28515625" customWidth="1"/>
     <col min="22" max="22" width="2.7109375" customWidth="1"/>
-    <col min="23" max="24" width="6.85546875" customWidth="1"/>
+    <col min="23" max="23" width="6.85546875" customWidth="1"/>
+    <col min="24" max="24" width="9.140625" customWidth="1"/>
     <col min="25" max="25" width="2.7109375" customWidth="1"/>
     <col min="26" max="27" width="6.85546875" customWidth="1"/>
     <col min="28" max="28" width="2.7109375" customWidth="1"/>
-    <col min="29" max="30" width="6.85546875" customWidth="1"/>
+    <col min="29" max="29" width="6.85546875" customWidth="1"/>
+    <col min="30" max="30" width="8" customWidth="1"/>
     <col min="31" max="31" width="2.7109375" customWidth="1"/>
     <col min="32" max="32" width="7.7109375" customWidth="1"/>
     <col min="35" max="35" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -5535,111 +4770,111 @@
       <c r="A2" s="9"/>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
-      <c r="D2" s="34" t="s">
+      <c r="D2" s="49" t="s">
         <v>141</v>
       </c>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
-      <c r="N2" s="34"/>
-      <c r="O2" s="34"/>
-      <c r="P2" s="34"/>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
-      <c r="T2" s="34"/>
-      <c r="U2" s="34"/>
-      <c r="V2" s="34"/>
-      <c r="W2" s="34"/>
-      <c r="X2" s="34"/>
-      <c r="Y2" s="34"/>
-      <c r="Z2" s="34"/>
-      <c r="AA2" s="34"/>
-      <c r="AB2" s="34"/>
-      <c r="AC2" s="34"/>
-      <c r="AD2" s="34"/>
-      <c r="AE2" s="34"/>
-      <c r="AF2" s="34"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="49"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="49"/>
+      <c r="S2" s="49"/>
+      <c r="T2" s="49"/>
+      <c r="U2" s="49"/>
+      <c r="V2" s="49"/>
+      <c r="W2" s="49"/>
+      <c r="X2" s="49"/>
+      <c r="Y2" s="49"/>
+      <c r="Z2" s="49"/>
+      <c r="AA2" s="49"/>
+      <c r="AB2" s="49"/>
+      <c r="AC2" s="49"/>
+      <c r="AD2" s="49"/>
+      <c r="AE2" s="49"/>
+      <c r="AF2" s="49"/>
       <c r="AG2" s="9"/>
     </row>
     <row r="3" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
-      <c r="D3" s="34" t="s">
+      <c r="D3" s="49" t="s">
         <v>142</v>
       </c>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
-      <c r="M3" s="34"/>
-      <c r="N3" s="34"/>
-      <c r="O3" s="34"/>
-      <c r="P3" s="34"/>
-      <c r="Q3" s="34"/>
-      <c r="R3" s="34"/>
-      <c r="S3" s="34"/>
-      <c r="T3" s="34"/>
-      <c r="U3" s="34"/>
-      <c r="V3" s="34"/>
-      <c r="W3" s="34"/>
-      <c r="X3" s="34"/>
-      <c r="Y3" s="34"/>
-      <c r="Z3" s="34"/>
-      <c r="AA3" s="34"/>
-      <c r="AB3" s="34"/>
-      <c r="AC3" s="34"/>
-      <c r="AD3" s="34"/>
-      <c r="AE3" s="34"/>
-      <c r="AF3" s="34"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="49"/>
+      <c r="N3" s="49"/>
+      <c r="O3" s="49"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="49"/>
+      <c r="R3" s="49"/>
+      <c r="S3" s="49"/>
+      <c r="T3" s="49"/>
+      <c r="U3" s="49"/>
+      <c r="V3" s="49"/>
+      <c r="W3" s="49"/>
+      <c r="X3" s="49"/>
+      <c r="Y3" s="49"/>
+      <c r="Z3" s="49"/>
+      <c r="AA3" s="49"/>
+      <c r="AB3" s="49"/>
+      <c r="AC3" s="49"/>
+      <c r="AD3" s="49"/>
+      <c r="AE3" s="49"/>
+      <c r="AF3" s="49"/>
       <c r="AG3" s="9"/>
     </row>
     <row r="4" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="49" t="s">
         <v>143</v>
       </c>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="34"/>
-      <c r="K4" s="34"/>
-      <c r="L4" s="34"/>
-      <c r="M4" s="34"/>
-      <c r="N4" s="34"/>
-      <c r="O4" s="34"/>
-      <c r="P4" s="34"/>
-      <c r="Q4" s="34"/>
-      <c r="R4" s="34"/>
-      <c r="S4" s="34"/>
-      <c r="T4" s="34"/>
-      <c r="U4" s="34"/>
-      <c r="V4" s="34"/>
-      <c r="W4" s="34"/>
-      <c r="X4" s="34"/>
-      <c r="Y4" s="34"/>
-      <c r="Z4" s="34"/>
-      <c r="AA4" s="34"/>
-      <c r="AB4" s="34"/>
-      <c r="AC4" s="34"/>
-      <c r="AD4" s="34"/>
-      <c r="AE4" s="34"/>
-      <c r="AF4" s="34"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="49"/>
+      <c r="K4" s="49"/>
+      <c r="L4" s="49"/>
+      <c r="M4" s="49"/>
+      <c r="N4" s="49"/>
+      <c r="O4" s="49"/>
+      <c r="P4" s="49"/>
+      <c r="Q4" s="49"/>
+      <c r="R4" s="49"/>
+      <c r="S4" s="49"/>
+      <c r="T4" s="49"/>
+      <c r="U4" s="49"/>
+      <c r="V4" s="49"/>
+      <c r="W4" s="49"/>
+      <c r="X4" s="49"/>
+      <c r="Y4" s="49"/>
+      <c r="Z4" s="49"/>
+      <c r="AA4" s="49"/>
+      <c r="AB4" s="49"/>
+      <c r="AC4" s="49"/>
+      <c r="AD4" s="49"/>
+      <c r="AE4" s="49"/>
+      <c r="AF4" s="49"/>
       <c r="AG4" s="9"/>
       <c r="AI4" s="31"/>
     </row>
@@ -5647,37 +4882,37 @@
       <c r="A5" s="9"/>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
-      <c r="D5" s="34" t="s">
+      <c r="D5" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
-      <c r="K5" s="34"/>
-      <c r="L5" s="34"/>
-      <c r="M5" s="34"/>
-      <c r="N5" s="34"/>
-      <c r="O5" s="34"/>
-      <c r="P5" s="34"/>
-      <c r="Q5" s="34"/>
-      <c r="R5" s="34"/>
-      <c r="S5" s="34"/>
-      <c r="T5" s="34"/>
-      <c r="U5" s="34"/>
-      <c r="V5" s="34"/>
-      <c r="W5" s="34"/>
-      <c r="X5" s="34"/>
-      <c r="Y5" s="34"/>
-      <c r="Z5" s="34"/>
-      <c r="AA5" s="34"/>
-      <c r="AB5" s="34"/>
-      <c r="AC5" s="34"/>
-      <c r="AD5" s="34"/>
-      <c r="AE5" s="34"/>
-      <c r="AF5" s="34"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
+      <c r="K5" s="49"/>
+      <c r="L5" s="49"/>
+      <c r="M5" s="49"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
+      <c r="W5" s="49"/>
+      <c r="X5" s="49"/>
+      <c r="Y5" s="49"/>
+      <c r="Z5" s="49"/>
+      <c r="AA5" s="49"/>
+      <c r="AB5" s="49"/>
+      <c r="AC5" s="49"/>
+      <c r="AD5" s="49"/>
+      <c r="AE5" s="49"/>
+      <c r="AF5" s="49"/>
       <c r="AG5" s="9"/>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.25">
@@ -5717,64 +4952,60 @@
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" s="9"/>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="35"/>
+      <c r="C7" s="50"/>
       <c r="D7" s="9"/>
-      <c r="E7" s="35" t="s">
+      <c r="E7" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="35"/>
+      <c r="F7" s="50"/>
       <c r="G7" s="9"/>
-      <c r="H7" s="35" t="s">
+      <c r="H7" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="I7" s="35"/>
+      <c r="I7" s="50"/>
       <c r="J7" s="9"/>
-      <c r="K7" s="35" t="s">
+      <c r="K7" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="L7" s="35"/>
+      <c r="L7" s="50"/>
       <c r="M7" s="9"/>
-      <c r="N7" s="35" t="s">
+      <c r="N7" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="O7" s="35"/>
+      <c r="O7" s="50"/>
       <c r="P7" s="9"/>
-      <c r="Q7" s="35" t="s">
+      <c r="Q7" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="R7" s="35"/>
+      <c r="R7" s="50"/>
       <c r="S7" s="9"/>
-      <c r="T7" s="35" t="s">
+      <c r="T7" s="50" t="s">
         <v>70</v>
       </c>
-      <c r="U7" s="35"/>
+      <c r="U7" s="50"/>
       <c r="V7" s="9"/>
-      <c r="W7" s="35" t="s">
+      <c r="W7" s="50" t="s">
         <v>73</v>
       </c>
-      <c r="X7" s="35"/>
+      <c r="X7" s="50"/>
       <c r="Y7" s="9"/>
-      <c r="Z7" s="35" t="s">
+      <c r="Z7" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="AA7" s="35"/>
+      <c r="AA7" s="50"/>
       <c r="AB7" s="9"/>
-      <c r="AC7" s="35" t="s">
+      <c r="AC7" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="AD7" s="35"/>
+      <c r="AD7" s="50"/>
       <c r="AE7" s="9"/>
       <c r="AF7" s="24" t="s">
         <v>140</v>
       </c>
       <c r="AG7" s="9"/>
-      <c r="AI7">
-        <f>100/48</f>
-        <v>2.0833333333333335</v>
-      </c>
     </row>
     <row r="8" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
@@ -5810,6 +5041,10 @@
       <c r="AE8" s="9"/>
       <c r="AF8" s="9"/>
       <c r="AG8" s="9"/>
+      <c r="AH8">
+        <f>100/48</f>
+        <v>2.0833333333333335</v>
+      </c>
       <c r="AI8" s="32"/>
     </row>
     <row r="9" spans="1:35" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
@@ -5886,152 +5121,161 @@
       <c r="AE9" s="9"/>
       <c r="AF9" s="3"/>
       <c r="AG9" s="9"/>
-      <c r="AI9" s="33"/>
+      <c r="AH9">
+        <f>+AH8*34</f>
+        <v>70.833333333333343</v>
+      </c>
+      <c r="AI9" s="31"/>
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" s="9"/>
-      <c r="B10" s="36" t="s">
+      <c r="B10" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="37"/>
+      <c r="C10" s="48"/>
       <c r="D10" s="9"/>
-      <c r="E10" s="36" t="s">
+      <c r="E10" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="37"/>
+      <c r="F10" s="48"/>
       <c r="G10" s="9"/>
-      <c r="H10" s="36" t="s">
+      <c r="H10" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="I10" s="37"/>
+      <c r="I10" s="48"/>
       <c r="J10" s="9"/>
-      <c r="K10" s="36" t="s">
+      <c r="K10" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="L10" s="37"/>
+      <c r="L10" s="48"/>
       <c r="M10" s="9"/>
-      <c r="N10" s="36" t="s">
+      <c r="N10" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="O10" s="37"/>
+      <c r="O10" s="48"/>
       <c r="P10" s="9"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="37"/>
+      <c r="Q10" s="47"/>
+      <c r="R10" s="48"/>
       <c r="S10" s="9"/>
-      <c r="T10" s="36" t="s">
+      <c r="T10" s="47" t="s">
         <v>69</v>
       </c>
-      <c r="U10" s="37"/>
+      <c r="U10" s="48"/>
       <c r="V10" s="9"/>
-      <c r="W10" s="36" t="s">
+      <c r="W10" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="X10" s="37"/>
+      <c r="X10" s="48"/>
       <c r="Y10" s="9"/>
-      <c r="Z10" s="36" t="s">
+      <c r="Z10" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="AA10" s="37"/>
+      <c r="AA10" s="48"/>
       <c r="AB10" s="9"/>
-      <c r="AC10" s="36" t="s">
+      <c r="AC10" s="47" t="s">
         <v>91</v>
       </c>
-      <c r="AD10" s="37"/>
+      <c r="AD10" s="48"/>
       <c r="AE10" s="9"/>
       <c r="AF10" s="4" t="s">
         <v>107</v>
       </c>
       <c r="AG10" s="9"/>
-      <c r="AI10" s="32"/>
+      <c r="AI10" s="31"/>
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" s="9"/>
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="39"/>
+      <c r="C11" s="40"/>
       <c r="D11" s="9"/>
-      <c r="E11" s="38" t="s">
+      <c r="E11" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="39"/>
+      <c r="F11" s="40"/>
       <c r="G11" s="9"/>
-      <c r="H11" s="38" t="s">
+      <c r="H11" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="I11" s="39"/>
+      <c r="I11" s="40"/>
       <c r="J11" s="9"/>
-      <c r="K11" s="38" t="s">
+      <c r="K11" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="L11" s="39"/>
+      <c r="L11" s="40"/>
       <c r="M11" s="9"/>
-      <c r="N11" s="38" t="s">
+      <c r="N11" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="O11" s="39"/>
+      <c r="O11" s="40"/>
       <c r="P11" s="9"/>
-      <c r="Q11" s="38" t="s">
+      <c r="Q11" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="R11" s="39"/>
+      <c r="R11" s="40"/>
       <c r="S11" s="9"/>
-      <c r="T11" s="38" t="s">
+      <c r="T11" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="U11" s="39"/>
+      <c r="U11" s="40"/>
       <c r="V11" s="9"/>
-      <c r="W11" s="38" t="s">
+      <c r="W11" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="X11" s="39"/>
+      <c r="X11" s="40"/>
       <c r="Y11" s="9"/>
-      <c r="Z11" s="38" t="s">
+      <c r="Z11" s="39" t="s">
         <v>88</v>
       </c>
-      <c r="AA11" s="39"/>
+      <c r="AA11" s="40"/>
       <c r="AB11" s="9"/>
-      <c r="AC11" s="38" t="s">
+      <c r="AC11" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="AD11" s="39"/>
+      <c r="AD11" s="40"/>
       <c r="AE11" s="9"/>
       <c r="AF11" s="4" t="s">
         <v>108</v>
       </c>
       <c r="AG11" s="9"/>
+      <c r="AH11">
+        <f>+AH8*14</f>
+        <v>29.166666666666668</v>
+      </c>
+      <c r="AI11" s="31"/>
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
-      <c r="B12" s="40"/>
-      <c r="C12" s="41"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="42"/>
       <c r="D12" s="9"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="42"/>
       <c r="G12" s="9"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="41"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="42"/>
       <c r="J12" s="9"/>
-      <c r="K12" s="40"/>
-      <c r="L12" s="41"/>
+      <c r="K12" s="41"/>
+      <c r="L12" s="42"/>
       <c r="M12" s="9"/>
-      <c r="N12" s="40"/>
-      <c r="O12" s="41"/>
+      <c r="N12" s="41"/>
+      <c r="O12" s="42"/>
       <c r="P12" s="9"/>
-      <c r="Q12" s="40"/>
-      <c r="R12" s="41"/>
+      <c r="Q12" s="41"/>
+      <c r="R12" s="42"/>
       <c r="S12" s="9"/>
-      <c r="T12" s="40"/>
-      <c r="U12" s="41"/>
+      <c r="T12" s="41"/>
+      <c r="U12" s="42"/>
       <c r="V12" s="9"/>
-      <c r="W12" s="40"/>
-      <c r="X12" s="41"/>
+      <c r="W12" s="41"/>
+      <c r="X12" s="42"/>
       <c r="Y12" s="9"/>
-      <c r="Z12" s="40"/>
-      <c r="AA12" s="41"/>
+      <c r="Z12" s="41"/>
+      <c r="AA12" s="42"/>
       <c r="AB12" s="9"/>
-      <c r="AC12" s="40"/>
-      <c r="AD12" s="41"/>
+      <c r="AC12" s="41"/>
+      <c r="AD12" s="42"/>
       <c r="AE12" s="9"/>
       <c r="AF12" s="4" t="s">
         <v>109</v>
@@ -6040,53 +5284,53 @@
     </row>
     <row r="13" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9"/>
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="43"/>
+      <c r="C13" s="46"/>
       <c r="D13" s="9"/>
-      <c r="E13" s="42" t="s">
+      <c r="E13" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="43"/>
+      <c r="F13" s="46"/>
       <c r="G13" s="9"/>
-      <c r="H13" s="42" t="s">
+      <c r="H13" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="I13" s="43"/>
+      <c r="I13" s="46"/>
       <c r="J13" s="9"/>
-      <c r="K13" s="42">
+      <c r="K13" s="45">
         <v>10</v>
       </c>
-      <c r="L13" s="43"/>
+      <c r="L13" s="46"/>
       <c r="M13" s="9"/>
-      <c r="N13" s="42" t="s">
+      <c r="N13" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="O13" s="43"/>
+      <c r="O13" s="46"/>
       <c r="P13" s="9"/>
-      <c r="Q13" s="42"/>
-      <c r="R13" s="43"/>
+      <c r="Q13" s="45"/>
+      <c r="R13" s="46"/>
       <c r="S13" s="9"/>
-      <c r="T13" s="42">
+      <c r="T13" s="45">
         <v>26</v>
       </c>
-      <c r="U13" s="43"/>
+      <c r="U13" s="46"/>
       <c r="V13" s="9"/>
-      <c r="W13" s="42">
+      <c r="W13" s="45">
         <v>30</v>
       </c>
-      <c r="X13" s="43"/>
+      <c r="X13" s="46"/>
       <c r="Y13" s="9"/>
-      <c r="Z13" s="42" t="s">
+      <c r="Z13" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="AA13" s="43"/>
+      <c r="AA13" s="46"/>
       <c r="AB13" s="9"/>
-      <c r="AC13" s="42" t="s">
+      <c r="AC13" s="45" t="s">
         <v>90</v>
       </c>
-      <c r="AD13" s="43"/>
+      <c r="AD13" s="46"/>
       <c r="AE13" s="9"/>
       <c r="AF13" s="4" t="s">
         <v>110</v>
@@ -6129,6 +5373,10 @@
         <v>109</v>
       </c>
       <c r="AG14" s="9"/>
+      <c r="AH14">
+        <f>100/48</f>
+        <v>2.0833333333333335</v>
+      </c>
     </row>
     <row r="15" spans="1:35" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
@@ -6206,210 +5454,218 @@
         <v>111</v>
       </c>
       <c r="AG15" s="9"/>
+      <c r="AH15">
+        <f>+AH14*39</f>
+        <v>81.25</v>
+      </c>
     </row>
     <row r="16" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
-      <c r="B16" s="36" t="s">
+      <c r="B16" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="C16" s="37"/>
+      <c r="C16" s="48"/>
       <c r="D16" s="9"/>
-      <c r="E16" s="36" t="s">
+      <c r="E16" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="37"/>
+      <c r="F16" s="48"/>
       <c r="G16" s="9"/>
-      <c r="H16" s="36" t="s">
+      <c r="H16" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="37"/>
+      <c r="I16" s="48"/>
       <c r="J16" s="9"/>
-      <c r="K16" s="36" t="s">
+      <c r="K16" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="L16" s="37"/>
+      <c r="L16" s="48"/>
       <c r="M16" s="9"/>
-      <c r="N16" s="36" t="s">
+      <c r="N16" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="O16" s="37"/>
+      <c r="O16" s="48"/>
       <c r="P16" s="9"/>
-      <c r="Q16" s="36" t="s">
+      <c r="Q16" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="R16" s="37"/>
+      <c r="R16" s="48"/>
       <c r="S16" s="9"/>
-      <c r="T16" s="36"/>
-      <c r="U16" s="37"/>
+      <c r="T16" s="47"/>
+      <c r="U16" s="48"/>
       <c r="V16" s="9"/>
-      <c r="W16" s="36" t="s">
+      <c r="W16" s="47" t="s">
         <v>79</v>
       </c>
-      <c r="X16" s="37"/>
+      <c r="X16" s="48"/>
       <c r="Y16" s="9"/>
-      <c r="Z16" s="36" t="s">
+      <c r="Z16" s="47" t="s">
         <v>93</v>
       </c>
-      <c r="AA16" s="37"/>
+      <c r="AA16" s="48"/>
       <c r="AB16" s="9"/>
-      <c r="AC16" s="36" t="s">
+      <c r="AC16" s="47" t="s">
         <v>95</v>
       </c>
-      <c r="AD16" s="37"/>
+      <c r="AD16" s="48"/>
       <c r="AE16" s="9"/>
       <c r="AF16" s="4" t="s">
         <v>112</v>
       </c>
       <c r="AG16" s="9"/>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
-      <c r="B17" s="38" t="s">
+      <c r="B17" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="39"/>
+      <c r="C17" s="40"/>
       <c r="D17" s="9"/>
-      <c r="E17" s="38" t="s">
+      <c r="E17" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="39"/>
+      <c r="F17" s="40"/>
       <c r="G17" s="9"/>
-      <c r="H17" s="38" t="s">
+      <c r="H17" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="I17" s="39"/>
+      <c r="I17" s="40"/>
       <c r="J17" s="9"/>
-      <c r="K17" s="38" t="s">
+      <c r="K17" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="L17" s="39"/>
+      <c r="L17" s="40"/>
       <c r="M17" s="9"/>
-      <c r="N17" s="38" t="s">
+      <c r="N17" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="O17" s="39"/>
+      <c r="O17" s="40"/>
       <c r="P17" s="9"/>
-      <c r="Q17" s="38" t="s">
+      <c r="Q17" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="R17" s="39"/>
+      <c r="R17" s="40"/>
       <c r="S17" s="9"/>
-      <c r="T17" s="38" t="s">
+      <c r="T17" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="U17" s="39"/>
+      <c r="U17" s="40"/>
       <c r="V17" s="9"/>
-      <c r="W17" s="38" t="s">
+      <c r="W17" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="X17" s="39"/>
+      <c r="X17" s="40"/>
       <c r="Y17" s="9"/>
-      <c r="Z17" s="38" t="s">
+      <c r="Z17" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="AA17" s="39"/>
+      <c r="AA17" s="40"/>
       <c r="AB17" s="9"/>
-      <c r="AC17" s="38" t="s">
+      <c r="AC17" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="AD17" s="39"/>
+      <c r="AD17" s="40"/>
       <c r="AE17" s="9"/>
       <c r="AF17" s="4"/>
       <c r="AG17" s="9"/>
+      <c r="AH17">
+        <f>+AH14*9</f>
+        <v>18.75</v>
+      </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
-      <c r="B18" s="40"/>
-      <c r="C18" s="41"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="42"/>
       <c r="D18" s="9"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="42"/>
       <c r="G18" s="9"/>
-      <c r="H18" s="40"/>
-      <c r="I18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="42"/>
       <c r="J18" s="9"/>
-      <c r="K18" s="40"/>
-      <c r="L18" s="41"/>
+      <c r="K18" s="41"/>
+      <c r="L18" s="42"/>
       <c r="M18" s="9"/>
-      <c r="N18" s="40"/>
-      <c r="O18" s="41"/>
+      <c r="N18" s="41"/>
+      <c r="O18" s="42"/>
       <c r="P18" s="9"/>
-      <c r="Q18" s="40"/>
-      <c r="R18" s="41"/>
+      <c r="Q18" s="41"/>
+      <c r="R18" s="42"/>
       <c r="S18" s="9"/>
-      <c r="T18" s="40"/>
-      <c r="U18" s="41"/>
+      <c r="T18" s="41"/>
+      <c r="U18" s="42"/>
       <c r="V18" s="9"/>
-      <c r="W18" s="40"/>
-      <c r="X18" s="41"/>
+      <c r="W18" s="41"/>
+      <c r="X18" s="42"/>
       <c r="Y18" s="9"/>
-      <c r="Z18" s="40"/>
-      <c r="AA18" s="41"/>
+      <c r="Z18" s="41"/>
+      <c r="AA18" s="42"/>
       <c r="AB18" s="9"/>
-      <c r="AC18" s="40"/>
-      <c r="AD18" s="41"/>
+      <c r="AC18" s="41"/>
+      <c r="AD18" s="42"/>
       <c r="AE18" s="9"/>
       <c r="AF18" s="4" t="s">
         <v>113</v>
       </c>
       <c r="AG18" s="9"/>
     </row>
-    <row r="19" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9"/>
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="C19" s="43"/>
+      <c r="C19" s="46"/>
       <c r="D19" s="9"/>
-      <c r="E19" s="42">
+      <c r="E19" s="45">
         <v>2</v>
       </c>
-      <c r="F19" s="43"/>
+      <c r="F19" s="46"/>
       <c r="G19" s="9"/>
-      <c r="H19" s="42">
+      <c r="H19" s="45">
         <v>6</v>
       </c>
-      <c r="I19" s="43"/>
+      <c r="I19" s="46"/>
       <c r="J19" s="9"/>
-      <c r="K19" s="42">
+      <c r="K19" s="45">
         <v>11</v>
       </c>
-      <c r="L19" s="43"/>
+      <c r="L19" s="46"/>
       <c r="M19" s="9"/>
-      <c r="N19" s="42" t="s">
+      <c r="N19" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="O19" s="43"/>
+      <c r="O19" s="46"/>
       <c r="P19" s="9"/>
-      <c r="Q19" s="42" t="s">
+      <c r="Q19" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="R19" s="43"/>
+      <c r="R19" s="46"/>
       <c r="S19" s="9"/>
-      <c r="T19" s="42"/>
-      <c r="U19" s="43"/>
+      <c r="T19" s="45"/>
+      <c r="U19" s="46"/>
       <c r="V19" s="9"/>
-      <c r="W19" s="42">
+      <c r="W19" s="45">
         <v>30</v>
       </c>
-      <c r="X19" s="43"/>
+      <c r="X19" s="46"/>
       <c r="Y19" s="9"/>
-      <c r="Z19" s="42">
+      <c r="Z19" s="45">
         <v>32</v>
       </c>
-      <c r="AA19" s="43"/>
+      <c r="AA19" s="46"/>
       <c r="AB19" s="9"/>
-      <c r="AC19" s="42" t="s">
+      <c r="AC19" s="45" t="s">
         <v>97</v>
       </c>
-      <c r="AD19" s="43"/>
+      <c r="AD19" s="46"/>
       <c r="AE19" s="9"/>
       <c r="AF19" s="4" t="s">
         <v>114</v>
       </c>
       <c r="AG19" s="9"/>
     </row>
-    <row r="20" spans="1:33" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:34" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -6443,8 +5699,12 @@
       <c r="AE20" s="9"/>
       <c r="AF20" s="4"/>
       <c r="AG20" s="9"/>
+      <c r="AH20">
+        <f>100/48</f>
+        <v>2.0833333333333335</v>
+      </c>
     </row>
-    <row r="21" spans="1:33" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:34" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9"/>
       <c r="B21" s="1">
         <v>3</v>
@@ -6520,216 +5780,224 @@
         <v>115</v>
       </c>
       <c r="AG21" s="9"/>
+      <c r="AH21">
+        <f>+AH20*44</f>
+        <v>91.666666666666671</v>
+      </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A22" s="9"/>
-      <c r="B22" s="36" t="s">
+      <c r="B22" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="37"/>
+      <c r="C22" s="48"/>
       <c r="D22" s="9"/>
-      <c r="E22" s="36" t="s">
+      <c r="E22" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="F22" s="37"/>
+      <c r="F22" s="48"/>
       <c r="G22" s="9"/>
-      <c r="H22" s="36" t="s">
+      <c r="H22" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="I22" s="37"/>
+      <c r="I22" s="48"/>
       <c r="J22" s="9"/>
-      <c r="K22" s="36" t="s">
+      <c r="K22" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="L22" s="37"/>
+      <c r="L22" s="48"/>
       <c r="M22" s="9"/>
-      <c r="N22" s="36" t="s">
+      <c r="N22" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="O22" s="37"/>
+      <c r="O22" s="48"/>
       <c r="P22" s="9"/>
-      <c r="Q22" s="36" t="s">
+      <c r="Q22" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="R22" s="37"/>
+      <c r="R22" s="48"/>
       <c r="S22" s="9"/>
-      <c r="T22" s="36" t="s">
+      <c r="T22" s="47" t="s">
         <v>147</v>
       </c>
-      <c r="U22" s="37"/>
+      <c r="U22" s="48"/>
       <c r="V22" s="9"/>
-      <c r="W22" s="36" t="s">
+      <c r="W22" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="X22" s="37"/>
+      <c r="X22" s="48"/>
       <c r="Y22" s="9"/>
-      <c r="Z22" s="36" t="s">
+      <c r="Z22" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="AA22" s="37"/>
+      <c r="AA22" s="48"/>
       <c r="AB22" s="9"/>
-      <c r="AC22" s="36" t="s">
+      <c r="AC22" s="47" t="s">
         <v>148</v>
       </c>
-      <c r="AD22" s="37"/>
+      <c r="AD22" s="48"/>
       <c r="AE22" s="9"/>
       <c r="AF22" s="4" t="s">
         <v>108</v>
       </c>
       <c r="AG22" s="9"/>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A23" s="9"/>
-      <c r="B23" s="38" t="s">
+      <c r="B23" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="39"/>
+      <c r="C23" s="40"/>
       <c r="D23" s="9"/>
-      <c r="E23" s="38" t="s">
+      <c r="E23" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="F23" s="39"/>
+      <c r="F23" s="40"/>
       <c r="G23" s="9"/>
-      <c r="H23" s="38" t="s">
+      <c r="H23" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="I23" s="39"/>
+      <c r="I23" s="40"/>
       <c r="J23" s="9"/>
-      <c r="K23" s="38" t="s">
+      <c r="K23" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="L23" s="39"/>
+      <c r="L23" s="40"/>
       <c r="M23" s="9"/>
-      <c r="N23" s="38" t="s">
+      <c r="N23" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="O23" s="39"/>
+      <c r="O23" s="40"/>
       <c r="P23" s="9"/>
-      <c r="Q23" s="38" t="s">
+      <c r="Q23" s="39" t="s">
         <v>63</v>
       </c>
-      <c r="R23" s="39"/>
+      <c r="R23" s="40"/>
       <c r="S23" s="9"/>
-      <c r="T23" s="38" t="s">
+      <c r="T23" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="U23" s="39"/>
+      <c r="U23" s="40"/>
       <c r="V23" s="9"/>
-      <c r="W23" s="38" t="s">
+      <c r="W23" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="X23" s="39"/>
+      <c r="X23" s="40"/>
       <c r="Y23" s="9"/>
-      <c r="Z23" s="38" t="s">
+      <c r="Z23" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="AA23" s="39"/>
+      <c r="AA23" s="40"/>
       <c r="AB23" s="9"/>
-      <c r="AC23" s="38" t="s">
+      <c r="AC23" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="AD23" s="39"/>
+      <c r="AD23" s="40"/>
       <c r="AE23" s="9"/>
       <c r="AF23" s="4" t="s">
         <v>109</v>
       </c>
       <c r="AG23" s="9"/>
+      <c r="AH23">
+        <f>+AH20*4</f>
+        <v>8.3333333333333339</v>
+      </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A24" s="9"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="41"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="42"/>
       <c r="D24" s="9"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="42"/>
       <c r="G24" s="9"/>
-      <c r="H24" s="40"/>
-      <c r="I24" s="41"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="42"/>
       <c r="J24" s="9"/>
-      <c r="K24" s="40"/>
-      <c r="L24" s="41"/>
+      <c r="K24" s="41"/>
+      <c r="L24" s="42"/>
       <c r="M24" s="9"/>
-      <c r="N24" s="40"/>
-      <c r="O24" s="41"/>
+      <c r="N24" s="41"/>
+      <c r="O24" s="42"/>
       <c r="P24" s="9"/>
-      <c r="Q24" s="40"/>
-      <c r="R24" s="41"/>
+      <c r="Q24" s="41"/>
+      <c r="R24" s="42"/>
       <c r="S24" s="9"/>
-      <c r="T24" s="40"/>
-      <c r="U24" s="41"/>
+      <c r="T24" s="41"/>
+      <c r="U24" s="42"/>
       <c r="V24" s="9"/>
-      <c r="W24" s="40"/>
-      <c r="X24" s="41"/>
+      <c r="W24" s="41"/>
+      <c r="X24" s="42"/>
       <c r="Y24" s="9"/>
-      <c r="Z24" s="40"/>
-      <c r="AA24" s="41"/>
+      <c r="Z24" s="41"/>
+      <c r="AA24" s="42"/>
       <c r="AB24" s="9"/>
-      <c r="AC24" s="40"/>
-      <c r="AD24" s="41"/>
+      <c r="AC24" s="41"/>
+      <c r="AD24" s="42"/>
       <c r="AE24" s="9"/>
       <c r="AF24" s="4" t="s">
         <v>113</v>
       </c>
       <c r="AG24" s="9"/>
     </row>
-    <row r="25" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9"/>
-      <c r="B25" s="42" t="s">
+      <c r="B25" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="C25" s="43"/>
+      <c r="C25" s="46"/>
       <c r="D25" s="9"/>
-      <c r="E25" s="42">
+      <c r="E25" s="45">
         <v>3</v>
       </c>
-      <c r="F25" s="43"/>
+      <c r="F25" s="46"/>
       <c r="G25" s="9"/>
-      <c r="H25" s="42">
+      <c r="H25" s="45">
         <v>7</v>
       </c>
-      <c r="I25" s="43"/>
+      <c r="I25" s="46"/>
       <c r="J25" s="9"/>
-      <c r="K25" s="42">
+      <c r="K25" s="45">
         <v>12</v>
       </c>
-      <c r="L25" s="43"/>
+      <c r="L25" s="46"/>
       <c r="M25" s="9"/>
-      <c r="N25" s="42" t="s">
+      <c r="N25" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="O25" s="43"/>
+      <c r="O25" s="46"/>
       <c r="P25" s="9"/>
-      <c r="Q25" s="42">
+      <c r="Q25" s="45">
         <v>22</v>
       </c>
-      <c r="R25" s="43"/>
+      <c r="R25" s="46"/>
       <c r="S25" s="9"/>
-      <c r="T25" s="42">
+      <c r="T25" s="45">
         <v>27</v>
       </c>
-      <c r="U25" s="43"/>
+      <c r="U25" s="46"/>
       <c r="V25" s="9"/>
-      <c r="W25" s="42" t="s">
+      <c r="W25" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="X25" s="43"/>
+      <c r="X25" s="46"/>
       <c r="Y25" s="9"/>
-      <c r="Z25" s="42" t="s">
+      <c r="Z25" s="45" t="s">
         <v>100</v>
       </c>
-      <c r="AA25" s="43"/>
+      <c r="AA25" s="46"/>
       <c r="AB25" s="9"/>
-      <c r="AC25" s="42" t="s">
+      <c r="AC25" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="AD25" s="43"/>
+      <c r="AD25" s="46"/>
       <c r="AE25" s="9"/>
       <c r="AF25" s="4" t="s">
         <v>116</v>
       </c>
       <c r="AG25" s="9"/>
     </row>
-    <row r="26" spans="1:33" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:34" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -6766,7 +6034,7 @@
       </c>
       <c r="AG26" s="9"/>
     </row>
-    <row r="27" spans="1:33" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:34" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A27" s="9"/>
       <c r="B27" s="1">
         <v>4</v>
@@ -6843,211 +6111,211 @@
       </c>
       <c r="AG27" s="9"/>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A28" s="9"/>
-      <c r="B28" s="36" t="s">
+      <c r="B28" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="37"/>
+      <c r="C28" s="48"/>
       <c r="D28" s="9"/>
-      <c r="E28" s="36" t="s">
+      <c r="E28" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="F28" s="37"/>
+      <c r="F28" s="48"/>
       <c r="G28" s="9"/>
-      <c r="H28" s="36" t="s">
+      <c r="H28" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I28" s="37"/>
+      <c r="I28" s="48"/>
       <c r="J28" s="9"/>
-      <c r="K28" s="36" t="s">
+      <c r="K28" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="L28" s="37"/>
+      <c r="L28" s="48"/>
       <c r="M28" s="9"/>
-      <c r="N28" s="36" t="s">
+      <c r="N28" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="O28" s="37"/>
+      <c r="O28" s="48"/>
       <c r="P28" s="9"/>
-      <c r="Q28" s="36" t="s">
+      <c r="Q28" s="47" t="s">
         <v>64</v>
       </c>
-      <c r="R28" s="37"/>
+      <c r="R28" s="48"/>
       <c r="S28" s="9"/>
-      <c r="T28" s="36" t="s">
+      <c r="T28" s="47" t="s">
         <v>84</v>
       </c>
-      <c r="U28" s="37"/>
+      <c r="U28" s="48"/>
       <c r="V28" s="9"/>
-      <c r="W28" s="36" t="s">
+      <c r="W28" s="47" t="s">
         <v>84</v>
       </c>
-      <c r="X28" s="37"/>
+      <c r="X28" s="48"/>
       <c r="Y28" s="9"/>
-      <c r="Z28" s="36" t="s">
+      <c r="Z28" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="AA28" s="37"/>
+      <c r="AA28" s="48"/>
       <c r="AB28" s="9"/>
-      <c r="AC28" s="36"/>
-      <c r="AD28" s="37"/>
+      <c r="AC28" s="47"/>
+      <c r="AD28" s="48"/>
       <c r="AE28" s="9"/>
       <c r="AF28" s="4" t="s">
         <v>4</v>
       </c>
       <c r="AG28" s="9"/>
     </row>
-    <row r="29" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9"/>
-      <c r="B29" s="38" t="s">
+      <c r="B29" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="39"/>
+      <c r="C29" s="40"/>
       <c r="D29" s="9"/>
-      <c r="E29" s="38" t="s">
+      <c r="E29" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="F29" s="39"/>
+      <c r="F29" s="40"/>
       <c r="G29" s="9"/>
-      <c r="H29" s="38" t="s">
+      <c r="H29" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="I29" s="39"/>
+      <c r="I29" s="40"/>
       <c r="J29" s="9"/>
-      <c r="K29" s="38" t="s">
+      <c r="K29" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="39"/>
+      <c r="L29" s="40"/>
       <c r="M29" s="9"/>
-      <c r="N29" s="38" t="s">
+      <c r="N29" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="O29" s="39"/>
+      <c r="O29" s="40"/>
       <c r="P29" s="9"/>
-      <c r="Q29" s="38" t="s">
+      <c r="Q29" s="39" t="s">
         <v>146</v>
       </c>
-      <c r="R29" s="39"/>
+      <c r="R29" s="40"/>
       <c r="S29" s="9"/>
-      <c r="T29" s="38" t="s">
+      <c r="T29" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="U29" s="39"/>
+      <c r="U29" s="40"/>
       <c r="V29" s="9"/>
-      <c r="W29" s="38" t="s">
+      <c r="W29" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="X29" s="39"/>
+      <c r="X29" s="40"/>
       <c r="Y29" s="9"/>
-      <c r="Z29" s="38" t="s">
+      <c r="Z29" s="39" t="s">
         <v>102</v>
       </c>
-      <c r="AA29" s="39"/>
+      <c r="AA29" s="40"/>
       <c r="AB29" s="9"/>
-      <c r="AC29" s="38" t="s">
+      <c r="AC29" s="39" t="s">
         <v>149</v>
       </c>
-      <c r="AD29" s="39"/>
+      <c r="AD29" s="40"/>
       <c r="AE29" s="9"/>
       <c r="AF29" s="4" t="s">
         <v>119</v>
       </c>
       <c r="AG29" s="9"/>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A30" s="9"/>
-      <c r="B30" s="40"/>
-      <c r="C30" s="41"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="42"/>
       <c r="D30" s="9"/>
-      <c r="E30" s="40"/>
-      <c r="F30" s="41"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="42"/>
       <c r="G30" s="9"/>
-      <c r="H30" s="40"/>
-      <c r="I30" s="41"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="42"/>
       <c r="J30" s="9"/>
-      <c r="K30" s="40"/>
-      <c r="L30" s="41"/>
+      <c r="K30" s="41"/>
+      <c r="L30" s="42"/>
       <c r="M30" s="9"/>
-      <c r="N30" s="40"/>
-      <c r="O30" s="41"/>
+      <c r="N30" s="41"/>
+      <c r="O30" s="42"/>
       <c r="P30" s="9"/>
-      <c r="Q30" s="40"/>
-      <c r="R30" s="41"/>
+      <c r="Q30" s="41"/>
+      <c r="R30" s="42"/>
       <c r="S30" s="9"/>
-      <c r="T30" s="40"/>
-      <c r="U30" s="41"/>
+      <c r="T30" s="41"/>
+      <c r="U30" s="42"/>
       <c r="V30" s="9"/>
-      <c r="W30" s="40"/>
-      <c r="X30" s="41"/>
+      <c r="W30" s="41"/>
+      <c r="X30" s="42"/>
       <c r="Y30" s="9"/>
-      <c r="Z30" s="40"/>
-      <c r="AA30" s="41"/>
+      <c r="Z30" s="41"/>
+      <c r="AA30" s="42"/>
       <c r="AB30" s="9"/>
-      <c r="AC30" s="40"/>
-      <c r="AD30" s="41"/>
+      <c r="AC30" s="41"/>
+      <c r="AD30" s="42"/>
       <c r="AE30" s="9"/>
       <c r="AF30" s="4" t="s">
         <v>118</v>
       </c>
       <c r="AG30" s="9"/>
     </row>
-    <row r="31" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="9"/>
-      <c r="B31" s="42" t="s">
+      <c r="B31" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="C31" s="43"/>
+      <c r="C31" s="46"/>
       <c r="D31" s="9"/>
-      <c r="E31" s="42">
+      <c r="E31" s="45">
         <v>3</v>
       </c>
-      <c r="F31" s="43"/>
+      <c r="F31" s="46"/>
       <c r="G31" s="9"/>
-      <c r="H31" s="42">
+      <c r="H31" s="45">
         <v>6</v>
       </c>
-      <c r="I31" s="43"/>
+      <c r="I31" s="46"/>
       <c r="J31" s="9"/>
-      <c r="K31" s="42">
+      <c r="K31" s="45">
         <v>12</v>
       </c>
-      <c r="L31" s="43"/>
+      <c r="L31" s="46"/>
       <c r="M31" s="9"/>
-      <c r="N31" s="42">
+      <c r="N31" s="45">
         <v>18</v>
       </c>
-      <c r="O31" s="43"/>
+      <c r="O31" s="46"/>
       <c r="P31" s="9"/>
-      <c r="Q31" s="42">
+      <c r="Q31" s="45">
         <v>12</v>
       </c>
-      <c r="R31" s="43"/>
+      <c r="R31" s="46"/>
       <c r="S31" s="9"/>
-      <c r="T31" s="42" t="s">
+      <c r="T31" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="U31" s="43"/>
+      <c r="U31" s="46"/>
       <c r="V31" s="9"/>
-      <c r="W31" s="42">
+      <c r="W31" s="45">
         <v>33</v>
       </c>
-      <c r="X31" s="43"/>
+      <c r="X31" s="46"/>
       <c r="Y31" s="9"/>
-      <c r="Z31" s="42">
+      <c r="Z31" s="45">
         <v>38</v>
       </c>
-      <c r="AA31" s="43"/>
+      <c r="AA31" s="46"/>
       <c r="AB31" s="9"/>
-      <c r="AC31" s="42"/>
-      <c r="AD31" s="43"/>
+      <c r="AC31" s="45"/>
+      <c r="AD31" s="46"/>
       <c r="AE31" s="9"/>
       <c r="AF31" s="5" t="s">
         <v>162</v>
       </c>
       <c r="AG31" s="9"/>
     </row>
-    <row r="32" spans="1:33" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:34" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="9"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -7154,39 +6422,39 @@
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
-      <c r="E34" s="36" t="s">
+      <c r="E34" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="F34" s="37"/>
+      <c r="F34" s="48"/>
       <c r="G34" s="9"/>
-      <c r="H34" s="36" t="s">
+      <c r="H34" s="47" t="s">
         <v>144</v>
       </c>
-      <c r="I34" s="37"/>
+      <c r="I34" s="48"/>
       <c r="J34" s="9"/>
-      <c r="K34" s="36" t="s">
+      <c r="K34" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="L34" s="37"/>
+      <c r="L34" s="48"/>
       <c r="M34" s="9"/>
-      <c r="N34" s="36" t="s">
+      <c r="N34" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="O34" s="37"/>
+      <c r="O34" s="48"/>
       <c r="P34" s="9"/>
-      <c r="Q34" s="36" t="s">
+      <c r="Q34" s="47" t="s">
         <v>65</v>
       </c>
-      <c r="R34" s="37"/>
+      <c r="R34" s="48"/>
       <c r="S34" s="9"/>
-      <c r="T34" s="36"/>
-      <c r="U34" s="37"/>
+      <c r="T34" s="47"/>
+      <c r="U34" s="48"/>
       <c r="V34" s="9"/>
-      <c r="W34" s="36"/>
-      <c r="X34" s="37"/>
+      <c r="W34" s="47"/>
+      <c r="X34" s="48"/>
       <c r="Y34" s="9"/>
-      <c r="Z34" s="36"/>
-      <c r="AA34" s="37"/>
+      <c r="Z34" s="47"/>
+      <c r="AA34" s="48"/>
       <c r="AB34" s="9"/>
       <c r="AC34" s="11"/>
       <c r="AD34" s="9"/>
@@ -7199,45 +6467,45 @@
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
-      <c r="E35" s="38" t="s">
+      <c r="E35" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="F35" s="39"/>
+      <c r="F35" s="40"/>
       <c r="G35" s="9"/>
-      <c r="H35" s="38" t="s">
+      <c r="H35" s="39" t="s">
         <v>145</v>
       </c>
-      <c r="I35" s="39"/>
+      <c r="I35" s="40"/>
       <c r="J35" s="9"/>
-      <c r="K35" s="38" t="s">
+      <c r="K35" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="L35" s="39"/>
+      <c r="L35" s="40"/>
       <c r="M35" s="9"/>
-      <c r="N35" s="38" t="s">
+      <c r="N35" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="O35" s="39"/>
+      <c r="O35" s="40"/>
       <c r="P35" s="9"/>
-      <c r="Q35" s="38" t="s">
+      <c r="Q35" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="R35" s="39"/>
+      <c r="R35" s="40"/>
       <c r="S35" s="9"/>
-      <c r="T35" s="38" t="s">
+      <c r="T35" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="U35" s="39"/>
+      <c r="U35" s="40"/>
       <c r="V35" s="9"/>
-      <c r="W35" s="38" t="s">
+      <c r="W35" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="X35" s="39"/>
+      <c r="X35" s="40"/>
       <c r="Y35" s="9"/>
-      <c r="Z35" s="38" t="s">
+      <c r="Z35" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="AA35" s="39"/>
+      <c r="AA35" s="40"/>
       <c r="AB35" s="9"/>
       <c r="AC35" s="11"/>
       <c r="AD35" s="9"/>
@@ -7250,29 +6518,29 @@
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
-      <c r="E36" s="40"/>
-      <c r="F36" s="41"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="42"/>
       <c r="G36" s="9"/>
-      <c r="H36" s="40"/>
-      <c r="I36" s="41"/>
+      <c r="H36" s="41"/>
+      <c r="I36" s="42"/>
       <c r="J36" s="9"/>
-      <c r="K36" s="40"/>
-      <c r="L36" s="41"/>
+      <c r="K36" s="41"/>
+      <c r="L36" s="42"/>
       <c r="M36" s="9"/>
-      <c r="N36" s="40"/>
-      <c r="O36" s="41"/>
+      <c r="N36" s="41"/>
+      <c r="O36" s="42"/>
       <c r="P36" s="9"/>
-      <c r="Q36" s="40"/>
-      <c r="R36" s="41"/>
+      <c r="Q36" s="41"/>
+      <c r="R36" s="42"/>
       <c r="S36" s="9"/>
-      <c r="T36" s="40"/>
-      <c r="U36" s="41"/>
+      <c r="T36" s="41"/>
+      <c r="U36" s="42"/>
       <c r="V36" s="9"/>
-      <c r="W36" s="40"/>
-      <c r="X36" s="41"/>
+      <c r="W36" s="41"/>
+      <c r="X36" s="42"/>
       <c r="Y36" s="9"/>
-      <c r="Z36" s="40"/>
-      <c r="AA36" s="41"/>
+      <c r="Z36" s="41"/>
+      <c r="AA36" s="42"/>
       <c r="AB36" s="9"/>
       <c r="AC36" s="11"/>
       <c r="AD36" s="9"/>
@@ -7285,39 +6553,39 @@
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
-      <c r="E37" s="42">
+      <c r="E37" s="45">
         <v>4</v>
       </c>
-      <c r="F37" s="43"/>
+      <c r="F37" s="46"/>
       <c r="G37" s="9"/>
-      <c r="H37" s="42" t="s">
+      <c r="H37" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="I37" s="43"/>
+      <c r="I37" s="46"/>
       <c r="J37" s="9"/>
-      <c r="K37" s="42">
+      <c r="K37" s="45">
         <v>13</v>
       </c>
-      <c r="L37" s="43"/>
+      <c r="L37" s="46"/>
       <c r="M37" s="9"/>
-      <c r="N37" s="42">
+      <c r="N37" s="45">
         <v>19</v>
       </c>
-      <c r="O37" s="43"/>
+      <c r="O37" s="46"/>
       <c r="P37" s="9"/>
-      <c r="Q37" s="42">
+      <c r="Q37" s="45">
         <v>23</v>
       </c>
-      <c r="R37" s="43"/>
+      <c r="R37" s="46"/>
       <c r="S37" s="9"/>
-      <c r="T37" s="42"/>
-      <c r="U37" s="43"/>
+      <c r="T37" s="45"/>
+      <c r="U37" s="46"/>
       <c r="V37" s="9"/>
-      <c r="W37" s="42"/>
-      <c r="X37" s="43"/>
+      <c r="W37" s="45"/>
+      <c r="X37" s="46"/>
       <c r="Y37" s="9"/>
-      <c r="Z37" s="42"/>
-      <c r="AA37" s="43"/>
+      <c r="Z37" s="45"/>
+      <c r="AA37" s="46"/>
       <c r="AB37" s="9"/>
       <c r="AC37" s="11"/>
       <c r="AD37" s="9"/>
@@ -7381,11 +6649,11 @@
       <c r="P39" s="9"/>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
-      <c r="S39" s="49"/>
-      <c r="T39" s="49"/>
-      <c r="U39" s="49"/>
-      <c r="V39" s="49"/>
-      <c r="W39" s="49"/>
+      <c r="S39" s="36"/>
+      <c r="T39" s="36"/>
+      <c r="U39" s="36"/>
+      <c r="V39" s="36"/>
+      <c r="W39" s="36"/>
       <c r="X39" s="9"/>
       <c r="Y39" s="9"/>
       <c r="Z39" s="9"/>
@@ -7527,37 +6795,37 @@
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
       <c r="D43" s="15"/>
-      <c r="E43" s="36" t="s">
+      <c r="E43" s="47" t="s">
         <v>122</v>
       </c>
-      <c r="F43" s="37"/>
+      <c r="F43" s="48"/>
       <c r="G43" s="9"/>
-      <c r="H43" s="36" t="s">
+      <c r="H43" s="47" t="s">
         <v>130</v>
       </c>
-      <c r="I43" s="37"/>
+      <c r="I43" s="48"/>
       <c r="J43" s="9"/>
-      <c r="K43" s="36" t="s">
+      <c r="K43" s="47" t="s">
         <v>163</v>
       </c>
-      <c r="L43" s="37"/>
+      <c r="L43" s="48"/>
       <c r="M43" s="9"/>
-      <c r="N43" s="36" t="s">
+      <c r="N43" s="47" t="s">
         <v>124</v>
       </c>
-      <c r="O43" s="37"/>
+      <c r="O43" s="48"/>
       <c r="P43" s="9"/>
       <c r="Q43" s="17"/>
       <c r="R43" s="9"/>
       <c r="S43" s="9"/>
-      <c r="T43" s="44"/>
-      <c r="U43" s="44"/>
+      <c r="T43" s="34"/>
+      <c r="U43" s="34"/>
       <c r="V43" s="9"/>
-      <c r="W43" s="44"/>
-      <c r="X43" s="44"/>
+      <c r="W43" s="34"/>
+      <c r="X43" s="34"/>
       <c r="Y43" s="9"/>
-      <c r="Z43" s="44"/>
-      <c r="AA43" s="44"/>
+      <c r="Z43" s="34"/>
+      <c r="AA43" s="34"/>
       <c r="AB43" s="9"/>
       <c r="AC43" s="9"/>
       <c r="AD43" s="9"/>
@@ -7572,37 +6840,37 @@
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
       <c r="D44" s="15"/>
-      <c r="E44" s="38" t="s">
+      <c r="E44" s="39" t="s">
         <v>123</v>
       </c>
-      <c r="F44" s="39"/>
+      <c r="F44" s="40"/>
       <c r="G44" s="9"/>
-      <c r="H44" s="38" t="s">
+      <c r="H44" s="39" t="s">
         <v>131</v>
       </c>
-      <c r="I44" s="39"/>
+      <c r="I44" s="40"/>
       <c r="J44" s="9"/>
-      <c r="K44" s="38" t="s">
+      <c r="K44" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="L44" s="39"/>
+      <c r="L44" s="40"/>
       <c r="M44" s="9"/>
-      <c r="N44" s="38" t="s">
+      <c r="N44" s="39" t="s">
         <v>125</v>
       </c>
-      <c r="O44" s="39"/>
+      <c r="O44" s="40"/>
       <c r="P44" s="9"/>
       <c r="Q44" s="17"/>
       <c r="R44" s="9"/>
       <c r="S44" s="9"/>
-      <c r="T44" s="46"/>
-      <c r="U44" s="46"/>
+      <c r="T44" s="33"/>
+      <c r="U44" s="33"/>
       <c r="V44" s="9"/>
-      <c r="W44" s="46"/>
-      <c r="X44" s="46"/>
+      <c r="W44" s="33"/>
+      <c r="X44" s="33"/>
       <c r="Y44" s="9"/>
-      <c r="Z44" s="46"/>
-      <c r="AA44" s="46"/>
+      <c r="Z44" s="33"/>
+      <c r="AA44" s="33"/>
       <c r="AB44" s="11"/>
       <c r="AC44" s="9"/>
       <c r="AD44" s="9"/>
@@ -7617,29 +6885,29 @@
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
       <c r="D45" s="15"/>
-      <c r="E45" s="40"/>
-      <c r="F45" s="41"/>
+      <c r="E45" s="41"/>
+      <c r="F45" s="42"/>
       <c r="G45" s="9"/>
-      <c r="H45" s="40"/>
-      <c r="I45" s="41"/>
+      <c r="H45" s="41"/>
+      <c r="I45" s="42"/>
       <c r="J45" s="9"/>
-      <c r="K45" s="40"/>
-      <c r="L45" s="41"/>
+      <c r="K45" s="41"/>
+      <c r="L45" s="42"/>
       <c r="M45" s="9"/>
-      <c r="N45" s="40"/>
-      <c r="O45" s="41"/>
+      <c r="N45" s="41"/>
+      <c r="O45" s="42"/>
       <c r="P45" s="9"/>
       <c r="Q45" s="17"/>
       <c r="R45" s="9"/>
       <c r="S45" s="9"/>
-      <c r="T45" s="46"/>
-      <c r="U45" s="46"/>
+      <c r="T45" s="33"/>
+      <c r="U45" s="33"/>
       <c r="V45" s="9"/>
-      <c r="W45" s="46"/>
-      <c r="X45" s="46"/>
+      <c r="W45" s="33"/>
+      <c r="X45" s="33"/>
       <c r="Y45" s="9"/>
-      <c r="Z45" s="46"/>
-      <c r="AA45" s="46"/>
+      <c r="Z45" s="33"/>
+      <c r="AA45" s="33"/>
       <c r="AB45" s="28"/>
       <c r="AC45" s="9"/>
       <c r="AD45" s="9"/>
@@ -7654,37 +6922,37 @@
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
       <c r="D46" s="15"/>
-      <c r="E46" s="42" t="s">
+      <c r="E46" s="45" t="s">
         <v>152</v>
       </c>
-      <c r="F46" s="43"/>
+      <c r="F46" s="46"/>
       <c r="G46" s="9"/>
-      <c r="H46" s="42" t="s">
+      <c r="H46" s="45" t="s">
         <v>153</v>
       </c>
-      <c r="I46" s="43"/>
+      <c r="I46" s="46"/>
       <c r="J46" s="9"/>
-      <c r="K46" s="42" t="s">
+      <c r="K46" s="45" t="s">
         <v>154</v>
       </c>
-      <c r="L46" s="43"/>
+      <c r="L46" s="46"/>
       <c r="M46" s="9"/>
-      <c r="N46" s="42" t="s">
+      <c r="N46" s="45" t="s">
         <v>160</v>
       </c>
-      <c r="O46" s="43"/>
+      <c r="O46" s="46"/>
       <c r="P46" s="9"/>
       <c r="Q46" s="17"/>
       <c r="R46" s="9"/>
       <c r="S46" s="9"/>
-      <c r="T46" s="45"/>
-      <c r="U46" s="45"/>
+      <c r="T46" s="35"/>
+      <c r="U46" s="35"/>
       <c r="V46" s="9"/>
-      <c r="W46" s="45"/>
-      <c r="X46" s="45"/>
+      <c r="W46" s="35"/>
+      <c r="X46" s="35"/>
       <c r="Y46" s="9"/>
-      <c r="Z46" s="45"/>
-      <c r="AA46" s="45"/>
+      <c r="Z46" s="35"/>
+      <c r="AA46" s="35"/>
       <c r="AB46" s="27"/>
       <c r="AC46" s="9"/>
       <c r="AD46" s="9"/>
@@ -7724,8 +6992,8 @@
       <c r="AA47" s="27"/>
       <c r="AB47" s="27"/>
       <c r="AC47" s="9"/>
-      <c r="AD47" s="44"/>
-      <c r="AE47" s="44"/>
+      <c r="AD47" s="34"/>
+      <c r="AE47" s="34"/>
       <c r="AF47" s="9"/>
       <c r="AG47" s="9"/>
     </row>
@@ -7775,8 +7043,8 @@
       <c r="AA48" s="11"/>
       <c r="AB48" s="29"/>
       <c r="AC48" s="9"/>
-      <c r="AD48" s="46"/>
-      <c r="AE48" s="46"/>
+      <c r="AD48" s="33"/>
+      <c r="AE48" s="33"/>
       <c r="AF48" s="9"/>
       <c r="AG48" s="9"/>
     </row>
@@ -7785,41 +7053,41 @@
       <c r="B49" s="9"/>
       <c r="C49" s="9"/>
       <c r="D49" s="15"/>
-      <c r="E49" s="36" t="s">
+      <c r="E49" s="47" t="s">
         <v>126</v>
       </c>
-      <c r="F49" s="37"/>
+      <c r="F49" s="48"/>
       <c r="G49" s="9"/>
-      <c r="H49" s="36" t="s">
+      <c r="H49" s="47" t="s">
         <v>132</v>
       </c>
-      <c r="I49" s="37"/>
+      <c r="I49" s="48"/>
       <c r="J49" s="9"/>
-      <c r="K49" s="36" t="s">
+      <c r="K49" s="47" t="s">
         <v>135</v>
       </c>
-      <c r="L49" s="37"/>
+      <c r="L49" s="48"/>
       <c r="M49" s="9"/>
-      <c r="N49" s="36" t="s">
+      <c r="N49" s="47" t="s">
         <v>128</v>
       </c>
-      <c r="O49" s="37"/>
+      <c r="O49" s="48"/>
       <c r="P49" s="9"/>
       <c r="Q49" s="17"/>
       <c r="R49" s="9"/>
       <c r="S49" s="9"/>
-      <c r="T49" s="44"/>
-      <c r="U49" s="44"/>
+      <c r="T49" s="34"/>
+      <c r="U49" s="34"/>
       <c r="V49" s="9"/>
-      <c r="W49" s="44"/>
-      <c r="X49" s="44"/>
+      <c r="W49" s="34"/>
+      <c r="X49" s="34"/>
       <c r="Y49" s="9"/>
-      <c r="Z49" s="44"/>
-      <c r="AA49" s="44"/>
+      <c r="Z49" s="34"/>
+      <c r="AA49" s="34"/>
       <c r="AB49" s="9"/>
       <c r="AC49" s="9"/>
-      <c r="AD49" s="46"/>
-      <c r="AE49" s="46"/>
+      <c r="AD49" s="33"/>
+      <c r="AE49" s="33"/>
       <c r="AF49" s="9"/>
       <c r="AG49" s="9"/>
     </row>
@@ -7828,41 +7096,41 @@
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
       <c r="D50" s="15"/>
-      <c r="E50" s="38" t="s">
+      <c r="E50" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="F50" s="39"/>
+      <c r="F50" s="40"/>
       <c r="G50" s="9"/>
-      <c r="H50" s="38" t="s">
+      <c r="H50" s="39" t="s">
         <v>133</v>
       </c>
-      <c r="I50" s="39"/>
+      <c r="I50" s="40"/>
       <c r="J50" s="9"/>
-      <c r="K50" s="38" t="s">
+      <c r="K50" s="39" t="s">
         <v>136</v>
       </c>
-      <c r="L50" s="39"/>
+      <c r="L50" s="40"/>
       <c r="M50" s="9"/>
-      <c r="N50" s="38" t="s">
+      <c r="N50" s="39" t="s">
         <v>129</v>
       </c>
-      <c r="O50" s="39"/>
+      <c r="O50" s="40"/>
       <c r="P50" s="9"/>
       <c r="Q50" s="17"/>
       <c r="R50" s="9"/>
       <c r="S50" s="9"/>
-      <c r="T50" s="46"/>
-      <c r="U50" s="46"/>
+      <c r="T50" s="33"/>
+      <c r="U50" s="33"/>
       <c r="V50" s="9"/>
-      <c r="W50" s="46"/>
-      <c r="X50" s="46"/>
+      <c r="W50" s="33"/>
+      <c r="X50" s="33"/>
       <c r="Y50" s="9"/>
-      <c r="Z50" s="46"/>
-      <c r="AA50" s="46"/>
+      <c r="Z50" s="33"/>
+      <c r="AA50" s="33"/>
       <c r="AB50" s="11"/>
       <c r="AC50" s="9"/>
-      <c r="AD50" s="45"/>
-      <c r="AE50" s="45"/>
+      <c r="AD50" s="35"/>
+      <c r="AE50" s="35"/>
       <c r="AF50" s="9"/>
       <c r="AG50" s="9"/>
     </row>
@@ -7871,29 +7139,29 @@
       <c r="B51" s="9"/>
       <c r="C51" s="9"/>
       <c r="D51" s="15"/>
-      <c r="E51" s="40"/>
-      <c r="F51" s="41"/>
+      <c r="E51" s="41"/>
+      <c r="F51" s="42"/>
       <c r="G51" s="9"/>
-      <c r="H51" s="40"/>
-      <c r="I51" s="41"/>
+      <c r="H51" s="41"/>
+      <c r="I51" s="42"/>
       <c r="J51" s="9"/>
-      <c r="K51" s="40"/>
-      <c r="L51" s="41"/>
+      <c r="K51" s="41"/>
+      <c r="L51" s="42"/>
       <c r="M51" s="9"/>
-      <c r="N51" s="40"/>
-      <c r="O51" s="41"/>
+      <c r="N51" s="41"/>
+      <c r="O51" s="42"/>
       <c r="P51" s="9"/>
       <c r="Q51" s="17"/>
       <c r="R51" s="9"/>
       <c r="S51" s="9"/>
-      <c r="T51" s="46"/>
-      <c r="U51" s="46"/>
+      <c r="T51" s="33"/>
+      <c r="U51" s="33"/>
       <c r="V51" s="9"/>
-      <c r="W51" s="46"/>
-      <c r="X51" s="46"/>
+      <c r="W51" s="33"/>
+      <c r="X51" s="33"/>
       <c r="Y51" s="9"/>
-      <c r="Z51" s="46"/>
-      <c r="AA51" s="46"/>
+      <c r="Z51" s="33"/>
+      <c r="AA51" s="33"/>
       <c r="AB51" s="28"/>
       <c r="AC51" s="9"/>
       <c r="AD51" s="9"/>
@@ -7906,37 +7174,37 @@
       <c r="B52" s="9"/>
       <c r="C52" s="9"/>
       <c r="D52" s="15"/>
-      <c r="E52" s="42">
+      <c r="E52" s="45">
         <v>18</v>
       </c>
-      <c r="F52" s="43"/>
+      <c r="F52" s="46"/>
       <c r="G52" s="9"/>
-      <c r="H52" s="42">
+      <c r="H52" s="45">
         <v>35</v>
       </c>
-      <c r="I52" s="43"/>
+      <c r="I52" s="46"/>
       <c r="J52" s="9"/>
-      <c r="K52" s="42" t="s">
+      <c r="K52" s="45" t="s">
         <v>159</v>
       </c>
-      <c r="L52" s="43"/>
+      <c r="L52" s="46"/>
       <c r="M52" s="9"/>
-      <c r="N52" s="42">
+      <c r="N52" s="45">
         <v>42</v>
       </c>
-      <c r="O52" s="43"/>
+      <c r="O52" s="46"/>
       <c r="P52" s="9"/>
       <c r="Q52" s="17"/>
       <c r="R52" s="9"/>
       <c r="S52" s="9"/>
-      <c r="T52" s="45"/>
-      <c r="U52" s="45"/>
+      <c r="T52" s="35"/>
+      <c r="U52" s="35"/>
       <c r="V52" s="9"/>
-      <c r="W52" s="45"/>
-      <c r="X52" s="45"/>
+      <c r="W52" s="35"/>
+      <c r="X52" s="35"/>
       <c r="Y52" s="9"/>
-      <c r="Z52" s="45"/>
-      <c r="AA52" s="45"/>
+      <c r="Z52" s="35"/>
+      <c r="AA52" s="35"/>
       <c r="AB52" s="27"/>
       <c r="AC52" s="9"/>
       <c r="AD52" s="9"/>
@@ -8035,34 +7303,34 @@
       <c r="B55" s="9"/>
       <c r="C55" s="9"/>
       <c r="D55" s="15"/>
-      <c r="E55" s="36" t="s">
+      <c r="E55" s="47" t="s">
         <v>165</v>
       </c>
-      <c r="F55" s="37"/>
+      <c r="F55" s="48"/>
       <c r="G55" s="9"/>
-      <c r="H55" s="47" t="s">
+      <c r="H55" s="43" t="s">
         <v>167</v>
       </c>
-      <c r="I55" s="48"/>
+      <c r="I55" s="44"/>
       <c r="J55" s="9"/>
-      <c r="K55" s="47" t="s">
+      <c r="K55" s="43" t="s">
         <v>166</v>
       </c>
-      <c r="L55" s="48"/>
+      <c r="L55" s="44"/>
       <c r="M55" s="9"/>
-      <c r="N55" s="36" t="s">
+      <c r="N55" s="47" t="s">
         <v>164</v>
       </c>
-      <c r="O55" s="37"/>
+      <c r="O55" s="48"/>
       <c r="P55" s="9"/>
       <c r="Q55" s="17"/>
       <c r="R55" s="9"/>
       <c r="S55" s="9"/>
-      <c r="T55" s="44"/>
-      <c r="U55" s="44"/>
+      <c r="T55" s="34"/>
+      <c r="U55" s="34"/>
       <c r="V55" s="9"/>
-      <c r="W55" s="44"/>
-      <c r="X55" s="44"/>
+      <c r="W55" s="34"/>
+      <c r="X55" s="34"/>
       <c r="Y55" s="9"/>
       <c r="Z55" s="9"/>
       <c r="AA55" s="9"/>
@@ -8078,34 +7346,34 @@
       <c r="B56" s="9"/>
       <c r="C56" s="9"/>
       <c r="D56" s="15"/>
-      <c r="E56" s="38" t="s">
+      <c r="E56" s="39" t="s">
         <v>139</v>
       </c>
-      <c r="F56" s="39"/>
+      <c r="F56" s="40"/>
       <c r="G56" s="9"/>
-      <c r="H56" s="38" t="s">
+      <c r="H56" s="39" t="s">
         <v>168</v>
       </c>
-      <c r="I56" s="39"/>
+      <c r="I56" s="40"/>
       <c r="J56" s="9"/>
-      <c r="K56" s="38" t="s">
+      <c r="K56" s="39" t="s">
         <v>137</v>
       </c>
-      <c r="L56" s="39"/>
+      <c r="L56" s="40"/>
       <c r="M56" s="9"/>
-      <c r="N56" s="38" t="s">
+      <c r="N56" s="39" t="s">
         <v>138</v>
       </c>
-      <c r="O56" s="39"/>
+      <c r="O56" s="40"/>
       <c r="P56" s="9"/>
       <c r="Q56" s="17"/>
       <c r="R56" s="9"/>
       <c r="S56" s="9"/>
-      <c r="T56" s="46"/>
-      <c r="U56" s="46"/>
+      <c r="T56" s="33"/>
+      <c r="U56" s="33"/>
       <c r="V56" s="9"/>
-      <c r="W56" s="46"/>
-      <c r="X56" s="46"/>
+      <c r="W56" s="33"/>
+      <c r="X56" s="33"/>
       <c r="Y56" s="9"/>
       <c r="Z56" s="9"/>
       <c r="AA56" s="9"/>
@@ -8121,26 +7389,26 @@
       <c r="B57" s="9"/>
       <c r="C57" s="9"/>
       <c r="D57" s="15"/>
-      <c r="E57" s="40"/>
-      <c r="F57" s="41"/>
+      <c r="E57" s="41"/>
+      <c r="F57" s="42"/>
       <c r="G57" s="9"/>
-      <c r="H57" s="40"/>
-      <c r="I57" s="41"/>
+      <c r="H57" s="41"/>
+      <c r="I57" s="42"/>
       <c r="J57" s="9"/>
-      <c r="K57" s="40"/>
-      <c r="L57" s="41"/>
+      <c r="K57" s="41"/>
+      <c r="L57" s="42"/>
       <c r="M57" s="9"/>
-      <c r="N57" s="40"/>
-      <c r="O57" s="41"/>
+      <c r="N57" s="41"/>
+      <c r="O57" s="42"/>
       <c r="P57" s="9"/>
       <c r="Q57" s="17"/>
       <c r="R57" s="9"/>
       <c r="S57" s="9"/>
-      <c r="T57" s="46"/>
-      <c r="U57" s="46"/>
+      <c r="T57" s="33"/>
+      <c r="U57" s="33"/>
       <c r="V57" s="9"/>
-      <c r="W57" s="46"/>
-      <c r="X57" s="46"/>
+      <c r="W57" s="33"/>
+      <c r="X57" s="33"/>
       <c r="Y57" s="9"/>
       <c r="Z57" s="9"/>
       <c r="AA57" s="9"/>
@@ -8156,33 +7424,33 @@
       <c r="B58" s="9"/>
       <c r="C58" s="9"/>
       <c r="D58" s="15"/>
-      <c r="E58" s="42" t="s">
+      <c r="E58" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="F58" s="43"/>
+      <c r="F58" s="46"/>
       <c r="G58" s="9"/>
-      <c r="H58" s="50" t="s">
+      <c r="H58" s="37" t="s">
         <v>169</v>
       </c>
-      <c r="I58" s="51"/>
+      <c r="I58" s="38"/>
       <c r="J58" s="9"/>
-      <c r="K58" s="50">
+      <c r="K58" s="37">
         <v>43</v>
       </c>
-      <c r="L58" s="51"/>
+      <c r="L58" s="38"/>
       <c r="M58" s="9"/>
-      <c r="N58" s="42" t="s">
+      <c r="N58" s="45" t="s">
         <v>153</v>
       </c>
-      <c r="O58" s="43"/>
+      <c r="O58" s="46"/>
       <c r="P58" s="9"/>
       <c r="Q58" s="17"/>
       <c r="S58" s="9"/>
-      <c r="T58" s="45"/>
-      <c r="U58" s="45"/>
+      <c r="T58" s="35"/>
+      <c r="U58" s="35"/>
       <c r="V58" s="9"/>
-      <c r="W58" s="45"/>
-      <c r="X58" s="45"/>
+      <c r="W58" s="35"/>
+      <c r="X58" s="35"/>
       <c r="Y58" s="9"/>
       <c r="Z58" s="9"/>
       <c r="AA58" s="9"/>
@@ -8230,6 +7498,204 @@
     </row>
   </sheetData>
   <mergeCells count="222">
+    <mergeCell ref="D2:AF2"/>
+    <mergeCell ref="D3:AF3"/>
+    <mergeCell ref="D4:AF4"/>
+    <mergeCell ref="D5:AF5"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="W7:X7"/>
+    <mergeCell ref="Z7:AA7"/>
+    <mergeCell ref="AC7:AD7"/>
+    <mergeCell ref="AC10:AD10"/>
+    <mergeCell ref="B11:C12"/>
+    <mergeCell ref="E11:F12"/>
+    <mergeCell ref="H11:I12"/>
+    <mergeCell ref="K11:L12"/>
+    <mergeCell ref="N11:O12"/>
+    <mergeCell ref="Q11:R12"/>
+    <mergeCell ref="T11:U12"/>
+    <mergeCell ref="W11:X12"/>
+    <mergeCell ref="Z11:AA12"/>
+    <mergeCell ref="AC11:AD12"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="Q10:R10"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="W10:X10"/>
+    <mergeCell ref="Z10:AA10"/>
+    <mergeCell ref="AC13:AD13"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="W16:X16"/>
+    <mergeCell ref="Z16:AA16"/>
+    <mergeCell ref="AC16:AD16"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="T13:U13"/>
+    <mergeCell ref="W13:X13"/>
+    <mergeCell ref="Z13:AA13"/>
+    <mergeCell ref="AC17:AD18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="W19:X19"/>
+    <mergeCell ref="Z19:AA19"/>
+    <mergeCell ref="AC19:AD19"/>
+    <mergeCell ref="B17:C18"/>
+    <mergeCell ref="E17:F18"/>
+    <mergeCell ref="H17:I18"/>
+    <mergeCell ref="K17:L18"/>
+    <mergeCell ref="N17:O18"/>
+    <mergeCell ref="Q17:R18"/>
+    <mergeCell ref="T17:U18"/>
+    <mergeCell ref="W17:X18"/>
+    <mergeCell ref="Z17:AA18"/>
+    <mergeCell ref="AC22:AD22"/>
+    <mergeCell ref="B23:C24"/>
+    <mergeCell ref="E23:F24"/>
+    <mergeCell ref="H23:I24"/>
+    <mergeCell ref="K23:L24"/>
+    <mergeCell ref="N23:O24"/>
+    <mergeCell ref="Q23:R24"/>
+    <mergeCell ref="T23:U24"/>
+    <mergeCell ref="W23:X24"/>
+    <mergeCell ref="Z23:AA24"/>
+    <mergeCell ref="AC23:AD24"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="W22:X22"/>
+    <mergeCell ref="Z22:AA22"/>
+    <mergeCell ref="AC25:AD25"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="T28:U28"/>
+    <mergeCell ref="W28:X28"/>
+    <mergeCell ref="Z28:AA28"/>
+    <mergeCell ref="AC28:AD28"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="T25:U25"/>
+    <mergeCell ref="W25:X25"/>
+    <mergeCell ref="Z25:AA25"/>
+    <mergeCell ref="AC29:AD30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="T31:U31"/>
+    <mergeCell ref="W31:X31"/>
+    <mergeCell ref="Z31:AA31"/>
+    <mergeCell ref="AC31:AD31"/>
+    <mergeCell ref="B29:C30"/>
+    <mergeCell ref="E29:F30"/>
+    <mergeCell ref="H29:I30"/>
+    <mergeCell ref="K29:L30"/>
+    <mergeCell ref="N29:O30"/>
+    <mergeCell ref="Q29:R30"/>
+    <mergeCell ref="T29:U30"/>
+    <mergeCell ref="W29:X30"/>
+    <mergeCell ref="Z29:AA30"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="Q34:R34"/>
+    <mergeCell ref="T34:U34"/>
+    <mergeCell ref="W34:X34"/>
+    <mergeCell ref="Z34:AA34"/>
+    <mergeCell ref="E35:F36"/>
+    <mergeCell ref="H35:I36"/>
+    <mergeCell ref="K35:L36"/>
+    <mergeCell ref="N35:O36"/>
+    <mergeCell ref="Q35:R36"/>
+    <mergeCell ref="T35:U36"/>
+    <mergeCell ref="W35:X36"/>
+    <mergeCell ref="Z35:AA36"/>
+    <mergeCell ref="W37:X37"/>
+    <mergeCell ref="Z37:AA37"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="N43:O43"/>
+    <mergeCell ref="N55:O55"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="N37:O37"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="T37:U37"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="N46:O46"/>
+    <mergeCell ref="T43:U43"/>
+    <mergeCell ref="Z43:AA43"/>
+    <mergeCell ref="Z49:AA49"/>
+    <mergeCell ref="Z46:AA46"/>
+    <mergeCell ref="Z52:AA52"/>
+    <mergeCell ref="Z44:AA45"/>
+    <mergeCell ref="N58:O58"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="E44:F45"/>
+    <mergeCell ref="H44:I45"/>
+    <mergeCell ref="K44:L45"/>
+    <mergeCell ref="N44:O45"/>
+    <mergeCell ref="N56:O57"/>
+    <mergeCell ref="E56:F57"/>
+    <mergeCell ref="AD47:AE47"/>
+    <mergeCell ref="AD48:AE49"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="N49:O49"/>
+    <mergeCell ref="T55:U55"/>
+    <mergeCell ref="K55:L55"/>
+    <mergeCell ref="K56:L57"/>
+    <mergeCell ref="AD50:AE50"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="K52:L52"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="T58:U58"/>
+    <mergeCell ref="T46:U46"/>
     <mergeCell ref="Z50:AA51"/>
     <mergeCell ref="W55:X55"/>
     <mergeCell ref="W56:X57"/>
@@ -8254,204 +7720,6 @@
     <mergeCell ref="T50:U51"/>
     <mergeCell ref="W44:X45"/>
     <mergeCell ref="W50:X51"/>
-    <mergeCell ref="N58:O58"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="E44:F45"/>
-    <mergeCell ref="H44:I45"/>
-    <mergeCell ref="K44:L45"/>
-    <mergeCell ref="N44:O45"/>
-    <mergeCell ref="N56:O57"/>
-    <mergeCell ref="E56:F57"/>
-    <mergeCell ref="AD47:AE47"/>
-    <mergeCell ref="AD48:AE49"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="N49:O49"/>
-    <mergeCell ref="T55:U55"/>
-    <mergeCell ref="K55:L55"/>
-    <mergeCell ref="K56:L57"/>
-    <mergeCell ref="AD50:AE50"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="K52:L52"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="T58:U58"/>
-    <mergeCell ref="T46:U46"/>
-    <mergeCell ref="W37:X37"/>
-    <mergeCell ref="Z37:AA37"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="K43:L43"/>
-    <mergeCell ref="N43:O43"/>
-    <mergeCell ref="N55:O55"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="N37:O37"/>
-    <mergeCell ref="Q37:R37"/>
-    <mergeCell ref="T37:U37"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="K46:L46"/>
-    <mergeCell ref="N46:O46"/>
-    <mergeCell ref="T43:U43"/>
-    <mergeCell ref="Z43:AA43"/>
-    <mergeCell ref="Z49:AA49"/>
-    <mergeCell ref="Z46:AA46"/>
-    <mergeCell ref="Z52:AA52"/>
-    <mergeCell ref="Z44:AA45"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="N34:O34"/>
-    <mergeCell ref="Q34:R34"/>
-    <mergeCell ref="T34:U34"/>
-    <mergeCell ref="W34:X34"/>
-    <mergeCell ref="Z34:AA34"/>
-    <mergeCell ref="E35:F36"/>
-    <mergeCell ref="H35:I36"/>
-    <mergeCell ref="K35:L36"/>
-    <mergeCell ref="N35:O36"/>
-    <mergeCell ref="Q35:R36"/>
-    <mergeCell ref="T35:U36"/>
-    <mergeCell ref="W35:X36"/>
-    <mergeCell ref="Z35:AA36"/>
-    <mergeCell ref="AC29:AD30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="T31:U31"/>
-    <mergeCell ref="W31:X31"/>
-    <mergeCell ref="Z31:AA31"/>
-    <mergeCell ref="AC31:AD31"/>
-    <mergeCell ref="B29:C30"/>
-    <mergeCell ref="E29:F30"/>
-    <mergeCell ref="H29:I30"/>
-    <mergeCell ref="K29:L30"/>
-    <mergeCell ref="N29:O30"/>
-    <mergeCell ref="Q29:R30"/>
-    <mergeCell ref="T29:U30"/>
-    <mergeCell ref="W29:X30"/>
-    <mergeCell ref="Z29:AA30"/>
-    <mergeCell ref="AC25:AD25"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="T28:U28"/>
-    <mergeCell ref="W28:X28"/>
-    <mergeCell ref="Z28:AA28"/>
-    <mergeCell ref="AC28:AD28"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="T25:U25"/>
-    <mergeCell ref="W25:X25"/>
-    <mergeCell ref="Z25:AA25"/>
-    <mergeCell ref="AC22:AD22"/>
-    <mergeCell ref="B23:C24"/>
-    <mergeCell ref="E23:F24"/>
-    <mergeCell ref="H23:I24"/>
-    <mergeCell ref="K23:L24"/>
-    <mergeCell ref="N23:O24"/>
-    <mergeCell ref="Q23:R24"/>
-    <mergeCell ref="T23:U24"/>
-    <mergeCell ref="W23:X24"/>
-    <mergeCell ref="Z23:AA24"/>
-    <mergeCell ref="AC23:AD24"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="W22:X22"/>
-    <mergeCell ref="Z22:AA22"/>
-    <mergeCell ref="AC17:AD18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="W19:X19"/>
-    <mergeCell ref="Z19:AA19"/>
-    <mergeCell ref="AC19:AD19"/>
-    <mergeCell ref="B17:C18"/>
-    <mergeCell ref="E17:F18"/>
-    <mergeCell ref="H17:I18"/>
-    <mergeCell ref="K17:L18"/>
-    <mergeCell ref="N17:O18"/>
-    <mergeCell ref="Q17:R18"/>
-    <mergeCell ref="T17:U18"/>
-    <mergeCell ref="W17:X18"/>
-    <mergeCell ref="Z17:AA18"/>
-    <mergeCell ref="AC13:AD13"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="T16:U16"/>
-    <mergeCell ref="W16:X16"/>
-    <mergeCell ref="Z16:AA16"/>
-    <mergeCell ref="AC16:AD16"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="T13:U13"/>
-    <mergeCell ref="W13:X13"/>
-    <mergeCell ref="Z13:AA13"/>
-    <mergeCell ref="AC10:AD10"/>
-    <mergeCell ref="B11:C12"/>
-    <mergeCell ref="E11:F12"/>
-    <mergeCell ref="H11:I12"/>
-    <mergeCell ref="K11:L12"/>
-    <mergeCell ref="N11:O12"/>
-    <mergeCell ref="Q11:R12"/>
-    <mergeCell ref="T11:U12"/>
-    <mergeCell ref="W11:X12"/>
-    <mergeCell ref="Z11:AA12"/>
-    <mergeCell ref="AC11:AD12"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="Q10:R10"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="W10:X10"/>
-    <mergeCell ref="Z10:AA10"/>
-    <mergeCell ref="D2:AF2"/>
-    <mergeCell ref="D3:AF3"/>
-    <mergeCell ref="D4:AF4"/>
-    <mergeCell ref="D5:AF5"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="Q7:R7"/>
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="W7:X7"/>
-    <mergeCell ref="Z7:AA7"/>
-    <mergeCell ref="AC7:AD7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/PensumOriginal1.xlsx
+++ b/PensumOriginal1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A8992FA-41E6-471F-AFC1-ED10200571FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AA188EA-9CF0-467C-9953-FE3E81B45420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="404" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1074,23 +1074,17 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1104,29 +1098,35 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2547,15 +2547,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>405512</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>38860</xdr:rowOff>
+      <xdr:colOff>376649</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>221663</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>81662</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>60218</xdr:rowOff>
+      <xdr:colOff>52799</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>194915</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2570,14 +2570,14 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1319134" y="9797125"/>
-          <a:ext cx="1415921" cy="1275159"/>
+          <a:off x="1300285" y="9650451"/>
+          <a:ext cx="1427211" cy="1262494"/>
         </a:xfrm>
         <a:prstGeom prst="mathMultiply">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="FFFF00">
+          <a:srgbClr val="00B050">
             <a:alpha val="58000"/>
           </a:srgbClr>
         </a:solidFill>
@@ -4119,9 +4119,11 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="FFFF00">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
             <a:alpha val="58000"/>
-          </a:srgbClr>
+          </a:schemeClr>
         </a:solidFill>
       </xdr:spPr>
       <xdr:style>
@@ -4219,15 +4221,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>383418</xdr:colOff>
+      <xdr:colOff>402661</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>214642</xdr:rowOff>
+      <xdr:rowOff>128051</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>60542</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>16826</xdr:rowOff>
+      <xdr:colOff>79785</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>190008</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4242,8 +4244,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4571312" y="8357482"/>
-          <a:ext cx="1406119" cy="1287877"/>
+          <a:off x="4645616" y="8325324"/>
+          <a:ext cx="1428184" cy="1293472"/>
         </a:xfrm>
         <a:prstGeom prst="mathMultiply">
           <a:avLst/>
@@ -4314,9 +4316,11 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="FFFF00">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
             <a:alpha val="58000"/>
-          </a:srgbClr>
+          </a:schemeClr>
         </a:solidFill>
       </xdr:spPr>
       <xdr:style>
@@ -4770,111 +4774,111 @@
       <c r="A2" s="9"/>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
-      <c r="D2" s="49" t="s">
+      <c r="D2" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
-      <c r="M2" s="49"/>
-      <c r="N2" s="49"/>
-      <c r="O2" s="49"/>
-      <c r="P2" s="49"/>
-      <c r="Q2" s="49"/>
-      <c r="R2" s="49"/>
-      <c r="S2" s="49"/>
-      <c r="T2" s="49"/>
-      <c r="U2" s="49"/>
-      <c r="V2" s="49"/>
-      <c r="W2" s="49"/>
-      <c r="X2" s="49"/>
-      <c r="Y2" s="49"/>
-      <c r="Z2" s="49"/>
-      <c r="AA2" s="49"/>
-      <c r="AB2" s="49"/>
-      <c r="AC2" s="49"/>
-      <c r="AD2" s="49"/>
-      <c r="AE2" s="49"/>
-      <c r="AF2" s="49"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
+      <c r="T2" s="33"/>
+      <c r="U2" s="33"/>
+      <c r="V2" s="33"/>
+      <c r="W2" s="33"/>
+      <c r="X2" s="33"/>
+      <c r="Y2" s="33"/>
+      <c r="Z2" s="33"/>
+      <c r="AA2" s="33"/>
+      <c r="AB2" s="33"/>
+      <c r="AC2" s="33"/>
+      <c r="AD2" s="33"/>
+      <c r="AE2" s="33"/>
+      <c r="AF2" s="33"/>
       <c r="AG2" s="9"/>
     </row>
     <row r="3" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
-      <c r="D3" s="49" t="s">
+      <c r="D3" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
-      <c r="J3" s="49"/>
-      <c r="K3" s="49"/>
-      <c r="L3" s="49"/>
-      <c r="M3" s="49"/>
-      <c r="N3" s="49"/>
-      <c r="O3" s="49"/>
-      <c r="P3" s="49"/>
-      <c r="Q3" s="49"/>
-      <c r="R3" s="49"/>
-      <c r="S3" s="49"/>
-      <c r="T3" s="49"/>
-      <c r="U3" s="49"/>
-      <c r="V3" s="49"/>
-      <c r="W3" s="49"/>
-      <c r="X3" s="49"/>
-      <c r="Y3" s="49"/>
-      <c r="Z3" s="49"/>
-      <c r="AA3" s="49"/>
-      <c r="AB3" s="49"/>
-      <c r="AC3" s="49"/>
-      <c r="AD3" s="49"/>
-      <c r="AE3" s="49"/>
-      <c r="AF3" s="49"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="33"/>
+      <c r="M3" s="33"/>
+      <c r="N3" s="33"/>
+      <c r="O3" s="33"/>
+      <c r="P3" s="33"/>
+      <c r="Q3" s="33"/>
+      <c r="R3" s="33"/>
+      <c r="S3" s="33"/>
+      <c r="T3" s="33"/>
+      <c r="U3" s="33"/>
+      <c r="V3" s="33"/>
+      <c r="W3" s="33"/>
+      <c r="X3" s="33"/>
+      <c r="Y3" s="33"/>
+      <c r="Z3" s="33"/>
+      <c r="AA3" s="33"/>
+      <c r="AB3" s="33"/>
+      <c r="AC3" s="33"/>
+      <c r="AD3" s="33"/>
+      <c r="AE3" s="33"/>
+      <c r="AF3" s="33"/>
       <c r="AG3" s="9"/>
     </row>
     <row r="4" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
-      <c r="D4" s="49" t="s">
+      <c r="D4" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
-      <c r="K4" s="49"/>
-      <c r="L4" s="49"/>
-      <c r="M4" s="49"/>
-      <c r="N4" s="49"/>
-      <c r="O4" s="49"/>
-      <c r="P4" s="49"/>
-      <c r="Q4" s="49"/>
-      <c r="R4" s="49"/>
-      <c r="S4" s="49"/>
-      <c r="T4" s="49"/>
-      <c r="U4" s="49"/>
-      <c r="V4" s="49"/>
-      <c r="W4" s="49"/>
-      <c r="X4" s="49"/>
-      <c r="Y4" s="49"/>
-      <c r="Z4" s="49"/>
-      <c r="AA4" s="49"/>
-      <c r="AB4" s="49"/>
-      <c r="AC4" s="49"/>
-      <c r="AD4" s="49"/>
-      <c r="AE4" s="49"/>
-      <c r="AF4" s="49"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="33"/>
+      <c r="M4" s="33"/>
+      <c r="N4" s="33"/>
+      <c r="O4" s="33"/>
+      <c r="P4" s="33"/>
+      <c r="Q4" s="33"/>
+      <c r="R4" s="33"/>
+      <c r="S4" s="33"/>
+      <c r="T4" s="33"/>
+      <c r="U4" s="33"/>
+      <c r="V4" s="33"/>
+      <c r="W4" s="33"/>
+      <c r="X4" s="33"/>
+      <c r="Y4" s="33"/>
+      <c r="Z4" s="33"/>
+      <c r="AA4" s="33"/>
+      <c r="AB4" s="33"/>
+      <c r="AC4" s="33"/>
+      <c r="AD4" s="33"/>
+      <c r="AE4" s="33"/>
+      <c r="AF4" s="33"/>
       <c r="AG4" s="9"/>
       <c r="AI4" s="31"/>
     </row>
@@ -4882,37 +4886,37 @@
       <c r="A5" s="9"/>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
-      <c r="D5" s="49" t="s">
+      <c r="D5" s="33" t="s">
         <v>170</v>
       </c>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
-      <c r="K5" s="49"/>
-      <c r="L5" s="49"/>
-      <c r="M5" s="49"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
-      <c r="W5" s="49"/>
-      <c r="X5" s="49"/>
-      <c r="Y5" s="49"/>
-      <c r="Z5" s="49"/>
-      <c r="AA5" s="49"/>
-      <c r="AB5" s="49"/>
-      <c r="AC5" s="49"/>
-      <c r="AD5" s="49"/>
-      <c r="AE5" s="49"/>
-      <c r="AF5" s="49"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="33"/>
+      <c r="M5" s="33"/>
+      <c r="N5" s="33"/>
+      <c r="O5" s="33"/>
+      <c r="P5" s="33"/>
+      <c r="Q5" s="33"/>
+      <c r="R5" s="33"/>
+      <c r="S5" s="33"/>
+      <c r="T5" s="33"/>
+      <c r="U5" s="33"/>
+      <c r="V5" s="33"/>
+      <c r="W5" s="33"/>
+      <c r="X5" s="33"/>
+      <c r="Y5" s="33"/>
+      <c r="Z5" s="33"/>
+      <c r="AA5" s="33"/>
+      <c r="AB5" s="33"/>
+      <c r="AC5" s="33"/>
+      <c r="AD5" s="33"/>
+      <c r="AE5" s="33"/>
+      <c r="AF5" s="33"/>
       <c r="AG5" s="9"/>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.25">
@@ -4952,55 +4956,55 @@
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" s="9"/>
-      <c r="B7" s="50" t="s">
+      <c r="B7" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="50"/>
+      <c r="C7" s="34"/>
       <c r="D7" s="9"/>
-      <c r="E7" s="50" t="s">
+      <c r="E7" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="50"/>
+      <c r="F7" s="34"/>
       <c r="G7" s="9"/>
-      <c r="H7" s="50" t="s">
+      <c r="H7" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="I7" s="50"/>
+      <c r="I7" s="34"/>
       <c r="J7" s="9"/>
-      <c r="K7" s="50" t="s">
+      <c r="K7" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="L7" s="50"/>
+      <c r="L7" s="34"/>
       <c r="M7" s="9"/>
-      <c r="N7" s="50" t="s">
+      <c r="N7" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="O7" s="50"/>
+      <c r="O7" s="34"/>
       <c r="P7" s="9"/>
-      <c r="Q7" s="50" t="s">
+      <c r="Q7" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="R7" s="50"/>
+      <c r="R7" s="34"/>
       <c r="S7" s="9"/>
-      <c r="T7" s="50" t="s">
+      <c r="T7" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="U7" s="50"/>
+      <c r="U7" s="34"/>
       <c r="V7" s="9"/>
-      <c r="W7" s="50" t="s">
+      <c r="W7" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="X7" s="50"/>
+      <c r="X7" s="34"/>
       <c r="Y7" s="9"/>
-      <c r="Z7" s="50" t="s">
+      <c r="Z7" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="AA7" s="50"/>
+      <c r="AA7" s="34"/>
       <c r="AB7" s="9"/>
-      <c r="AC7" s="50" t="s">
+      <c r="AC7" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="AD7" s="50"/>
+      <c r="AD7" s="34"/>
       <c r="AE7" s="9"/>
       <c r="AF7" s="24" t="s">
         <v>140</v>
@@ -5129,53 +5133,53 @@
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" s="9"/>
-      <c r="B10" s="47" t="s">
+      <c r="B10" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="48"/>
+      <c r="C10" s="36"/>
       <c r="D10" s="9"/>
-      <c r="E10" s="47" t="s">
+      <c r="E10" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="48"/>
+      <c r="F10" s="36"/>
       <c r="G10" s="9"/>
-      <c r="H10" s="47" t="s">
+      <c r="H10" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="I10" s="48"/>
+      <c r="I10" s="36"/>
       <c r="J10" s="9"/>
-      <c r="K10" s="47" t="s">
+      <c r="K10" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="L10" s="48"/>
+      <c r="L10" s="36"/>
       <c r="M10" s="9"/>
-      <c r="N10" s="47" t="s">
+      <c r="N10" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="O10" s="48"/>
+      <c r="O10" s="36"/>
       <c r="P10" s="9"/>
-      <c r="Q10" s="47"/>
-      <c r="R10" s="48"/>
+      <c r="Q10" s="35"/>
+      <c r="R10" s="36"/>
       <c r="S10" s="9"/>
-      <c r="T10" s="47" t="s">
+      <c r="T10" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="U10" s="48"/>
+      <c r="U10" s="36"/>
       <c r="V10" s="9"/>
-      <c r="W10" s="47" t="s">
+      <c r="W10" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="X10" s="48"/>
+      <c r="X10" s="36"/>
       <c r="Y10" s="9"/>
-      <c r="Z10" s="47" t="s">
+      <c r="Z10" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="AA10" s="48"/>
+      <c r="AA10" s="36"/>
       <c r="AB10" s="9"/>
-      <c r="AC10" s="47" t="s">
+      <c r="AC10" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="AD10" s="48"/>
+      <c r="AD10" s="36"/>
       <c r="AE10" s="9"/>
       <c r="AF10" s="4" t="s">
         <v>107</v>
@@ -5185,55 +5189,55 @@
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" s="9"/>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="40"/>
+      <c r="C11" s="38"/>
       <c r="D11" s="9"/>
-      <c r="E11" s="39" t="s">
+      <c r="E11" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="40"/>
+      <c r="F11" s="38"/>
       <c r="G11" s="9"/>
-      <c r="H11" s="39" t="s">
+      <c r="H11" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I11" s="40"/>
+      <c r="I11" s="38"/>
       <c r="J11" s="9"/>
-      <c r="K11" s="39" t="s">
+      <c r="K11" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="L11" s="40"/>
+      <c r="L11" s="38"/>
       <c r="M11" s="9"/>
-      <c r="N11" s="39" t="s">
+      <c r="N11" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="O11" s="40"/>
+      <c r="O11" s="38"/>
       <c r="P11" s="9"/>
-      <c r="Q11" s="39" t="s">
+      <c r="Q11" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="R11" s="40"/>
+      <c r="R11" s="38"/>
       <c r="S11" s="9"/>
-      <c r="T11" s="39" t="s">
+      <c r="T11" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="U11" s="40"/>
+      <c r="U11" s="38"/>
       <c r="V11" s="9"/>
-      <c r="W11" s="39" t="s">
+      <c r="W11" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="X11" s="40"/>
+      <c r="X11" s="38"/>
       <c r="Y11" s="9"/>
-      <c r="Z11" s="39" t="s">
+      <c r="Z11" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="AA11" s="40"/>
+      <c r="AA11" s="38"/>
       <c r="AB11" s="9"/>
-      <c r="AC11" s="39" t="s">
+      <c r="AC11" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="AD11" s="40"/>
+      <c r="AD11" s="38"/>
       <c r="AE11" s="9"/>
       <c r="AF11" s="4" t="s">
         <v>108</v>
@@ -5247,35 +5251,35 @@
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
-      <c r="B12" s="41"/>
-      <c r="C12" s="42"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="40"/>
       <c r="D12" s="9"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="42"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="40"/>
       <c r="G12" s="9"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="42"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="40"/>
       <c r="J12" s="9"/>
-      <c r="K12" s="41"/>
-      <c r="L12" s="42"/>
+      <c r="K12" s="39"/>
+      <c r="L12" s="40"/>
       <c r="M12" s="9"/>
-      <c r="N12" s="41"/>
-      <c r="O12" s="42"/>
+      <c r="N12" s="39"/>
+      <c r="O12" s="40"/>
       <c r="P12" s="9"/>
-      <c r="Q12" s="41"/>
-      <c r="R12" s="42"/>
+      <c r="Q12" s="39"/>
+      <c r="R12" s="40"/>
       <c r="S12" s="9"/>
-      <c r="T12" s="41"/>
-      <c r="U12" s="42"/>
+      <c r="T12" s="39"/>
+      <c r="U12" s="40"/>
       <c r="V12" s="9"/>
-      <c r="W12" s="41"/>
-      <c r="X12" s="42"/>
+      <c r="W12" s="39"/>
+      <c r="X12" s="40"/>
       <c r="Y12" s="9"/>
-      <c r="Z12" s="41"/>
-      <c r="AA12" s="42"/>
+      <c r="Z12" s="39"/>
+      <c r="AA12" s="40"/>
       <c r="AB12" s="9"/>
-      <c r="AC12" s="41"/>
-      <c r="AD12" s="42"/>
+      <c r="AC12" s="39"/>
+      <c r="AD12" s="40"/>
       <c r="AE12" s="9"/>
       <c r="AF12" s="4" t="s">
         <v>109</v>
@@ -5284,53 +5288,53 @@
     </row>
     <row r="13" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9"/>
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="46"/>
+      <c r="C13" s="42"/>
       <c r="D13" s="9"/>
-      <c r="E13" s="45" t="s">
+      <c r="E13" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="46"/>
+      <c r="F13" s="42"/>
       <c r="G13" s="9"/>
-      <c r="H13" s="45" t="s">
+      <c r="H13" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="I13" s="46"/>
+      <c r="I13" s="42"/>
       <c r="J13" s="9"/>
-      <c r="K13" s="45">
+      <c r="K13" s="41">
         <v>10</v>
       </c>
-      <c r="L13" s="46"/>
+      <c r="L13" s="42"/>
       <c r="M13" s="9"/>
-      <c r="N13" s="45" t="s">
+      <c r="N13" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="O13" s="46"/>
+      <c r="O13" s="42"/>
       <c r="P13" s="9"/>
-      <c r="Q13" s="45"/>
-      <c r="R13" s="46"/>
+      <c r="Q13" s="41"/>
+      <c r="R13" s="42"/>
       <c r="S13" s="9"/>
-      <c r="T13" s="45">
+      <c r="T13" s="41">
         <v>26</v>
       </c>
-      <c r="U13" s="46"/>
+      <c r="U13" s="42"/>
       <c r="V13" s="9"/>
-      <c r="W13" s="45">
+      <c r="W13" s="41">
         <v>30</v>
       </c>
-      <c r="X13" s="46"/>
+      <c r="X13" s="42"/>
       <c r="Y13" s="9"/>
-      <c r="Z13" s="45" t="s">
+      <c r="Z13" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="AA13" s="46"/>
+      <c r="AA13" s="42"/>
       <c r="AB13" s="9"/>
-      <c r="AC13" s="45" t="s">
+      <c r="AC13" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="AD13" s="46"/>
+      <c r="AD13" s="42"/>
       <c r="AE13" s="9"/>
       <c r="AF13" s="4" t="s">
         <v>110</v>
@@ -5461,53 +5465,53 @@
     </row>
     <row r="16" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
-      <c r="B16" s="47" t="s">
+      <c r="B16" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="C16" s="48"/>
+      <c r="C16" s="36"/>
       <c r="D16" s="9"/>
-      <c r="E16" s="47" t="s">
+      <c r="E16" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="48"/>
+      <c r="F16" s="36"/>
       <c r="G16" s="9"/>
-      <c r="H16" s="47" t="s">
+      <c r="H16" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="48"/>
+      <c r="I16" s="36"/>
       <c r="J16" s="9"/>
-      <c r="K16" s="47" t="s">
+      <c r="K16" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="L16" s="48"/>
+      <c r="L16" s="36"/>
       <c r="M16" s="9"/>
-      <c r="N16" s="47" t="s">
+      <c r="N16" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="O16" s="48"/>
+      <c r="O16" s="36"/>
       <c r="P16" s="9"/>
-      <c r="Q16" s="47" t="s">
+      <c r="Q16" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="R16" s="48"/>
+      <c r="R16" s="36"/>
       <c r="S16" s="9"/>
-      <c r="T16" s="47"/>
-      <c r="U16" s="48"/>
+      <c r="T16" s="35"/>
+      <c r="U16" s="36"/>
       <c r="V16" s="9"/>
-      <c r="W16" s="47" t="s">
+      <c r="W16" s="35" t="s">
         <v>79</v>
       </c>
-      <c r="X16" s="48"/>
+      <c r="X16" s="36"/>
       <c r="Y16" s="9"/>
-      <c r="Z16" s="47" t="s">
+      <c r="Z16" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="AA16" s="48"/>
+      <c r="AA16" s="36"/>
       <c r="AB16" s="9"/>
-      <c r="AC16" s="47" t="s">
+      <c r="AC16" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="AD16" s="48"/>
+      <c r="AD16" s="36"/>
       <c r="AE16" s="9"/>
       <c r="AF16" s="4" t="s">
         <v>112</v>
@@ -5516,55 +5520,55 @@
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="40"/>
+      <c r="C17" s="38"/>
       <c r="D17" s="9"/>
-      <c r="E17" s="39" t="s">
+      <c r="E17" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="40"/>
+      <c r="F17" s="38"/>
       <c r="G17" s="9"/>
-      <c r="H17" s="39" t="s">
+      <c r="H17" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="I17" s="40"/>
+      <c r="I17" s="38"/>
       <c r="J17" s="9"/>
-      <c r="K17" s="39" t="s">
+      <c r="K17" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="L17" s="40"/>
+      <c r="L17" s="38"/>
       <c r="M17" s="9"/>
-      <c r="N17" s="39" t="s">
+      <c r="N17" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="O17" s="40"/>
+      <c r="O17" s="38"/>
       <c r="P17" s="9"/>
-      <c r="Q17" s="39" t="s">
+      <c r="Q17" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="R17" s="40"/>
+      <c r="R17" s="38"/>
       <c r="S17" s="9"/>
-      <c r="T17" s="39" t="s">
+      <c r="T17" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="U17" s="40"/>
+      <c r="U17" s="38"/>
       <c r="V17" s="9"/>
-      <c r="W17" s="39" t="s">
+      <c r="W17" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="X17" s="40"/>
+      <c r="X17" s="38"/>
       <c r="Y17" s="9"/>
-      <c r="Z17" s="39" t="s">
+      <c r="Z17" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="AA17" s="40"/>
+      <c r="AA17" s="38"/>
       <c r="AB17" s="9"/>
-      <c r="AC17" s="39" t="s">
+      <c r="AC17" s="37" t="s">
         <v>96</v>
       </c>
-      <c r="AD17" s="40"/>
+      <c r="AD17" s="38"/>
       <c r="AE17" s="9"/>
       <c r="AF17" s="4"/>
       <c r="AG17" s="9"/>
@@ -5575,35 +5579,35 @@
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
-      <c r="B18" s="41"/>
-      <c r="C18" s="42"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="40"/>
       <c r="D18" s="9"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="42"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="40"/>
       <c r="G18" s="9"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="42"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="40"/>
       <c r="J18" s="9"/>
-      <c r="K18" s="41"/>
-      <c r="L18" s="42"/>
+      <c r="K18" s="39"/>
+      <c r="L18" s="40"/>
       <c r="M18" s="9"/>
-      <c r="N18" s="41"/>
-      <c r="O18" s="42"/>
+      <c r="N18" s="39"/>
+      <c r="O18" s="40"/>
       <c r="P18" s="9"/>
-      <c r="Q18" s="41"/>
-      <c r="R18" s="42"/>
+      <c r="Q18" s="39"/>
+      <c r="R18" s="40"/>
       <c r="S18" s="9"/>
-      <c r="T18" s="41"/>
-      <c r="U18" s="42"/>
+      <c r="T18" s="39"/>
+      <c r="U18" s="40"/>
       <c r="V18" s="9"/>
-      <c r="W18" s="41"/>
-      <c r="X18" s="42"/>
+      <c r="W18" s="39"/>
+      <c r="X18" s="40"/>
       <c r="Y18" s="9"/>
-      <c r="Z18" s="41"/>
-      <c r="AA18" s="42"/>
+      <c r="Z18" s="39"/>
+      <c r="AA18" s="40"/>
       <c r="AB18" s="9"/>
-      <c r="AC18" s="41"/>
-      <c r="AD18" s="42"/>
+      <c r="AC18" s="39"/>
+      <c r="AD18" s="40"/>
       <c r="AE18" s="9"/>
       <c r="AF18" s="4" t="s">
         <v>113</v>
@@ -5612,53 +5616,53 @@
     </row>
     <row r="19" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9"/>
-      <c r="B19" s="45" t="s">
+      <c r="B19" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="C19" s="46"/>
+      <c r="C19" s="42"/>
       <c r="D19" s="9"/>
-      <c r="E19" s="45">
+      <c r="E19" s="41">
         <v>2</v>
       </c>
-      <c r="F19" s="46"/>
+      <c r="F19" s="42"/>
       <c r="G19" s="9"/>
-      <c r="H19" s="45">
+      <c r="H19" s="41">
         <v>6</v>
       </c>
-      <c r="I19" s="46"/>
+      <c r="I19" s="42"/>
       <c r="J19" s="9"/>
-      <c r="K19" s="45">
+      <c r="K19" s="41">
         <v>11</v>
       </c>
-      <c r="L19" s="46"/>
+      <c r="L19" s="42"/>
       <c r="M19" s="9"/>
-      <c r="N19" s="45" t="s">
+      <c r="N19" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="O19" s="46"/>
+      <c r="O19" s="42"/>
       <c r="P19" s="9"/>
-      <c r="Q19" s="45" t="s">
+      <c r="Q19" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="R19" s="46"/>
+      <c r="R19" s="42"/>
       <c r="S19" s="9"/>
-      <c r="T19" s="45"/>
-      <c r="U19" s="46"/>
+      <c r="T19" s="41"/>
+      <c r="U19" s="42"/>
       <c r="V19" s="9"/>
-      <c r="W19" s="45">
+      <c r="W19" s="41">
         <v>30</v>
       </c>
-      <c r="X19" s="46"/>
+      <c r="X19" s="42"/>
       <c r="Y19" s="9"/>
-      <c r="Z19" s="45">
+      <c r="Z19" s="41">
         <v>32</v>
       </c>
-      <c r="AA19" s="46"/>
+      <c r="AA19" s="42"/>
       <c r="AB19" s="9"/>
-      <c r="AC19" s="45" t="s">
+      <c r="AC19" s="41" t="s">
         <v>97</v>
       </c>
-      <c r="AD19" s="46"/>
+      <c r="AD19" s="42"/>
       <c r="AE19" s="9"/>
       <c r="AF19" s="4" t="s">
         <v>114</v>
@@ -5787,55 +5791,55 @@
     </row>
     <row r="22" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A22" s="9"/>
-      <c r="B22" s="47" t="s">
+      <c r="B22" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="48"/>
+      <c r="C22" s="36"/>
       <c r="D22" s="9"/>
-      <c r="E22" s="47" t="s">
+      <c r="E22" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="F22" s="48"/>
+      <c r="F22" s="36"/>
       <c r="G22" s="9"/>
-      <c r="H22" s="47" t="s">
+      <c r="H22" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="I22" s="48"/>
+      <c r="I22" s="36"/>
       <c r="J22" s="9"/>
-      <c r="K22" s="47" t="s">
+      <c r="K22" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="L22" s="48"/>
+      <c r="L22" s="36"/>
       <c r="M22" s="9"/>
-      <c r="N22" s="47" t="s">
+      <c r="N22" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="O22" s="48"/>
+      <c r="O22" s="36"/>
       <c r="P22" s="9"/>
-      <c r="Q22" s="47" t="s">
+      <c r="Q22" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="R22" s="48"/>
+      <c r="R22" s="36"/>
       <c r="S22" s="9"/>
-      <c r="T22" s="47" t="s">
+      <c r="T22" s="35" t="s">
         <v>147</v>
       </c>
-      <c r="U22" s="48"/>
+      <c r="U22" s="36"/>
       <c r="V22" s="9"/>
-      <c r="W22" s="47" t="s">
+      <c r="W22" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="X22" s="48"/>
+      <c r="X22" s="36"/>
       <c r="Y22" s="9"/>
-      <c r="Z22" s="47" t="s">
+      <c r="Z22" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="AA22" s="48"/>
+      <c r="AA22" s="36"/>
       <c r="AB22" s="9"/>
-      <c r="AC22" s="47" t="s">
+      <c r="AC22" s="35" t="s">
         <v>148</v>
       </c>
-      <c r="AD22" s="48"/>
+      <c r="AD22" s="36"/>
       <c r="AE22" s="9"/>
       <c r="AF22" s="4" t="s">
         <v>108</v>
@@ -5844,55 +5848,55 @@
     </row>
     <row r="23" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A23" s="9"/>
-      <c r="B23" s="39" t="s">
+      <c r="B23" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="40"/>
+      <c r="C23" s="38"/>
       <c r="D23" s="9"/>
-      <c r="E23" s="39" t="s">
+      <c r="E23" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="F23" s="40"/>
+      <c r="F23" s="38"/>
       <c r="G23" s="9"/>
-      <c r="H23" s="39" t="s">
+      <c r="H23" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="I23" s="40"/>
+      <c r="I23" s="38"/>
       <c r="J23" s="9"/>
-      <c r="K23" s="39" t="s">
+      <c r="K23" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="L23" s="40"/>
+      <c r="L23" s="38"/>
       <c r="M23" s="9"/>
-      <c r="N23" s="39" t="s">
+      <c r="N23" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="O23" s="40"/>
+      <c r="O23" s="38"/>
       <c r="P23" s="9"/>
-      <c r="Q23" s="39" t="s">
+      <c r="Q23" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="R23" s="40"/>
+      <c r="R23" s="38"/>
       <c r="S23" s="9"/>
-      <c r="T23" s="39" t="s">
+      <c r="T23" s="37" t="s">
         <v>74</v>
       </c>
-      <c r="U23" s="40"/>
+      <c r="U23" s="38"/>
       <c r="V23" s="9"/>
-      <c r="W23" s="39" t="s">
+      <c r="W23" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="X23" s="40"/>
+      <c r="X23" s="38"/>
       <c r="Y23" s="9"/>
-      <c r="Z23" s="39" t="s">
+      <c r="Z23" s="37" t="s">
         <v>99</v>
       </c>
-      <c r="AA23" s="40"/>
+      <c r="AA23" s="38"/>
       <c r="AB23" s="9"/>
-      <c r="AC23" s="39" t="s">
+      <c r="AC23" s="37" t="s">
         <v>104</v>
       </c>
-      <c r="AD23" s="40"/>
+      <c r="AD23" s="38"/>
       <c r="AE23" s="9"/>
       <c r="AF23" s="4" t="s">
         <v>109</v>
@@ -5905,35 +5909,35 @@
     </row>
     <row r="24" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A24" s="9"/>
-      <c r="B24" s="41"/>
-      <c r="C24" s="42"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="40"/>
       <c r="D24" s="9"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="42"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="40"/>
       <c r="G24" s="9"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="42"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="40"/>
       <c r="J24" s="9"/>
-      <c r="K24" s="41"/>
-      <c r="L24" s="42"/>
+      <c r="K24" s="39"/>
+      <c r="L24" s="40"/>
       <c r="M24" s="9"/>
-      <c r="N24" s="41"/>
-      <c r="O24" s="42"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="40"/>
       <c r="P24" s="9"/>
-      <c r="Q24" s="41"/>
-      <c r="R24" s="42"/>
+      <c r="Q24" s="39"/>
+      <c r="R24" s="40"/>
       <c r="S24" s="9"/>
-      <c r="T24" s="41"/>
-      <c r="U24" s="42"/>
+      <c r="T24" s="39"/>
+      <c r="U24" s="40"/>
       <c r="V24" s="9"/>
-      <c r="W24" s="41"/>
-      <c r="X24" s="42"/>
+      <c r="W24" s="39"/>
+      <c r="X24" s="40"/>
       <c r="Y24" s="9"/>
-      <c r="Z24" s="41"/>
-      <c r="AA24" s="42"/>
+      <c r="Z24" s="39"/>
+      <c r="AA24" s="40"/>
       <c r="AB24" s="9"/>
-      <c r="AC24" s="41"/>
-      <c r="AD24" s="42"/>
+      <c r="AC24" s="39"/>
+      <c r="AD24" s="40"/>
       <c r="AE24" s="9"/>
       <c r="AF24" s="4" t="s">
         <v>113</v>
@@ -5942,55 +5946,55 @@
     </row>
     <row r="25" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9"/>
-      <c r="B25" s="45" t="s">
+      <c r="B25" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="C25" s="46"/>
+      <c r="C25" s="42"/>
       <c r="D25" s="9"/>
-      <c r="E25" s="45">
+      <c r="E25" s="41">
         <v>3</v>
       </c>
-      <c r="F25" s="46"/>
+      <c r="F25" s="42"/>
       <c r="G25" s="9"/>
-      <c r="H25" s="45">
+      <c r="H25" s="41">
         <v>7</v>
       </c>
-      <c r="I25" s="46"/>
+      <c r="I25" s="42"/>
       <c r="J25" s="9"/>
-      <c r="K25" s="45">
+      <c r="K25" s="41">
         <v>12</v>
       </c>
-      <c r="L25" s="46"/>
+      <c r="L25" s="42"/>
       <c r="M25" s="9"/>
-      <c r="N25" s="45" t="s">
+      <c r="N25" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="O25" s="46"/>
+      <c r="O25" s="42"/>
       <c r="P25" s="9"/>
-      <c r="Q25" s="45">
+      <c r="Q25" s="41">
         <v>22</v>
       </c>
-      <c r="R25" s="46"/>
+      <c r="R25" s="42"/>
       <c r="S25" s="9"/>
-      <c r="T25" s="45">
+      <c r="T25" s="41">
         <v>27</v>
       </c>
-      <c r="U25" s="46"/>
+      <c r="U25" s="42"/>
       <c r="V25" s="9"/>
-      <c r="W25" s="45" t="s">
+      <c r="W25" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="X25" s="46"/>
+      <c r="X25" s="42"/>
       <c r="Y25" s="9"/>
-      <c r="Z25" s="45" t="s">
+      <c r="Z25" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="AA25" s="46"/>
+      <c r="AA25" s="42"/>
       <c r="AB25" s="9"/>
-      <c r="AC25" s="45" t="s">
+      <c r="AC25" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="AD25" s="46"/>
+      <c r="AD25" s="42"/>
       <c r="AE25" s="9"/>
       <c r="AF25" s="4" t="s">
         <v>116</v>
@@ -6113,53 +6117,53 @@
     </row>
     <row r="28" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A28" s="9"/>
-      <c r="B28" s="47" t="s">
+      <c r="B28" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="48"/>
+      <c r="C28" s="36"/>
       <c r="D28" s="9"/>
-      <c r="E28" s="47" t="s">
+      <c r="E28" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="F28" s="48"/>
+      <c r="F28" s="36"/>
       <c r="G28" s="9"/>
-      <c r="H28" s="47" t="s">
+      <c r="H28" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="I28" s="48"/>
+      <c r="I28" s="36"/>
       <c r="J28" s="9"/>
-      <c r="K28" s="47" t="s">
+      <c r="K28" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="L28" s="48"/>
+      <c r="L28" s="36"/>
       <c r="M28" s="9"/>
-      <c r="N28" s="47" t="s">
+      <c r="N28" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="O28" s="48"/>
+      <c r="O28" s="36"/>
       <c r="P28" s="9"/>
-      <c r="Q28" s="47" t="s">
+      <c r="Q28" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="R28" s="48"/>
+      <c r="R28" s="36"/>
       <c r="S28" s="9"/>
-      <c r="T28" s="47" t="s">
+      <c r="T28" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="U28" s="48"/>
+      <c r="U28" s="36"/>
       <c r="V28" s="9"/>
-      <c r="W28" s="47" t="s">
+      <c r="W28" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="X28" s="48"/>
+      <c r="X28" s="36"/>
       <c r="Y28" s="9"/>
-      <c r="Z28" s="47" t="s">
+      <c r="Z28" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="AA28" s="48"/>
+      <c r="AA28" s="36"/>
       <c r="AB28" s="9"/>
-      <c r="AC28" s="47"/>
-      <c r="AD28" s="48"/>
+      <c r="AC28" s="35"/>
+      <c r="AD28" s="36"/>
       <c r="AE28" s="9"/>
       <c r="AF28" s="4" t="s">
         <v>4</v>
@@ -6168,55 +6172,55 @@
     </row>
     <row r="29" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9"/>
-      <c r="B29" s="39" t="s">
+      <c r="B29" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="40"/>
+      <c r="C29" s="38"/>
       <c r="D29" s="9"/>
-      <c r="E29" s="39" t="s">
+      <c r="E29" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="F29" s="40"/>
+      <c r="F29" s="38"/>
       <c r="G29" s="9"/>
-      <c r="H29" s="39" t="s">
+      <c r="H29" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="I29" s="40"/>
+      <c r="I29" s="38"/>
       <c r="J29" s="9"/>
-      <c r="K29" s="39" t="s">
+      <c r="K29" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="40"/>
+      <c r="L29" s="38"/>
       <c r="M29" s="9"/>
-      <c r="N29" s="39" t="s">
+      <c r="N29" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="O29" s="40"/>
+      <c r="O29" s="38"/>
       <c r="P29" s="9"/>
-      <c r="Q29" s="39" t="s">
+      <c r="Q29" s="37" t="s">
         <v>146</v>
       </c>
-      <c r="R29" s="40"/>
+      <c r="R29" s="38"/>
       <c r="S29" s="9"/>
-      <c r="T29" s="39" t="s">
+      <c r="T29" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="U29" s="40"/>
+      <c r="U29" s="38"/>
       <c r="V29" s="9"/>
-      <c r="W29" s="39" t="s">
+      <c r="W29" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="X29" s="40"/>
+      <c r="X29" s="38"/>
       <c r="Y29" s="9"/>
-      <c r="Z29" s="39" t="s">
+      <c r="Z29" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="AA29" s="40"/>
+      <c r="AA29" s="38"/>
       <c r="AB29" s="9"/>
-      <c r="AC29" s="39" t="s">
+      <c r="AC29" s="37" t="s">
         <v>149</v>
       </c>
-      <c r="AD29" s="40"/>
+      <c r="AD29" s="38"/>
       <c r="AE29" s="9"/>
       <c r="AF29" s="4" t="s">
         <v>119</v>
@@ -6225,35 +6229,35 @@
     </row>
     <row r="30" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A30" s="9"/>
-      <c r="B30" s="41"/>
-      <c r="C30" s="42"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="40"/>
       <c r="D30" s="9"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="42"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="40"/>
       <c r="G30" s="9"/>
-      <c r="H30" s="41"/>
-      <c r="I30" s="42"/>
+      <c r="H30" s="39"/>
+      <c r="I30" s="40"/>
       <c r="J30" s="9"/>
-      <c r="K30" s="41"/>
-      <c r="L30" s="42"/>
+      <c r="K30" s="39"/>
+      <c r="L30" s="40"/>
       <c r="M30" s="9"/>
-      <c r="N30" s="41"/>
-      <c r="O30" s="42"/>
+      <c r="N30" s="39"/>
+      <c r="O30" s="40"/>
       <c r="P30" s="9"/>
-      <c r="Q30" s="41"/>
-      <c r="R30" s="42"/>
+      <c r="Q30" s="39"/>
+      <c r="R30" s="40"/>
       <c r="S30" s="9"/>
-      <c r="T30" s="41"/>
-      <c r="U30" s="42"/>
+      <c r="T30" s="39"/>
+      <c r="U30" s="40"/>
       <c r="V30" s="9"/>
-      <c r="W30" s="41"/>
-      <c r="X30" s="42"/>
+      <c r="W30" s="39"/>
+      <c r="X30" s="40"/>
       <c r="Y30" s="9"/>
-      <c r="Z30" s="41"/>
-      <c r="AA30" s="42"/>
+      <c r="Z30" s="39"/>
+      <c r="AA30" s="40"/>
       <c r="AB30" s="9"/>
-      <c r="AC30" s="41"/>
-      <c r="AD30" s="42"/>
+      <c r="AC30" s="39"/>
+      <c r="AD30" s="40"/>
       <c r="AE30" s="9"/>
       <c r="AF30" s="4" t="s">
         <v>118</v>
@@ -6262,53 +6266,53 @@
     </row>
     <row r="31" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="9"/>
-      <c r="B31" s="45" t="s">
+      <c r="B31" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="C31" s="46"/>
+      <c r="C31" s="42"/>
       <c r="D31" s="9"/>
-      <c r="E31" s="45">
+      <c r="E31" s="41">
         <v>3</v>
       </c>
-      <c r="F31" s="46"/>
+      <c r="F31" s="42"/>
       <c r="G31" s="9"/>
-      <c r="H31" s="45">
+      <c r="H31" s="41">
         <v>6</v>
       </c>
-      <c r="I31" s="46"/>
+      <c r="I31" s="42"/>
       <c r="J31" s="9"/>
-      <c r="K31" s="45">
+      <c r="K31" s="41">
         <v>12</v>
       </c>
-      <c r="L31" s="46"/>
+      <c r="L31" s="42"/>
       <c r="M31" s="9"/>
-      <c r="N31" s="45">
+      <c r="N31" s="41">
         <v>18</v>
       </c>
-      <c r="O31" s="46"/>
+      <c r="O31" s="42"/>
       <c r="P31" s="9"/>
-      <c r="Q31" s="45">
+      <c r="Q31" s="41">
         <v>12</v>
       </c>
-      <c r="R31" s="46"/>
+      <c r="R31" s="42"/>
       <c r="S31" s="9"/>
-      <c r="T31" s="45" t="s">
+      <c r="T31" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="U31" s="46"/>
+      <c r="U31" s="42"/>
       <c r="V31" s="9"/>
-      <c r="W31" s="45">
+      <c r="W31" s="41">
         <v>33</v>
       </c>
-      <c r="X31" s="46"/>
+      <c r="X31" s="42"/>
       <c r="Y31" s="9"/>
-      <c r="Z31" s="45">
+      <c r="Z31" s="41">
         <v>38</v>
       </c>
-      <c r="AA31" s="46"/>
+      <c r="AA31" s="42"/>
       <c r="AB31" s="9"/>
-      <c r="AC31" s="45"/>
-      <c r="AD31" s="46"/>
+      <c r="AC31" s="41"/>
+      <c r="AD31" s="42"/>
       <c r="AE31" s="9"/>
       <c r="AF31" s="5" t="s">
         <v>162</v>
@@ -6422,39 +6426,39 @@
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
-      <c r="E34" s="47" t="s">
+      <c r="E34" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="F34" s="48"/>
+      <c r="F34" s="36"/>
       <c r="G34" s="9"/>
-      <c r="H34" s="47" t="s">
+      <c r="H34" s="35" t="s">
         <v>144</v>
       </c>
-      <c r="I34" s="48"/>
+      <c r="I34" s="36"/>
       <c r="J34" s="9"/>
-      <c r="K34" s="47" t="s">
+      <c r="K34" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="L34" s="48"/>
+      <c r="L34" s="36"/>
       <c r="M34" s="9"/>
-      <c r="N34" s="47" t="s">
+      <c r="N34" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="O34" s="48"/>
+      <c r="O34" s="36"/>
       <c r="P34" s="9"/>
-      <c r="Q34" s="47" t="s">
+      <c r="Q34" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="R34" s="48"/>
+      <c r="R34" s="36"/>
       <c r="S34" s="9"/>
-      <c r="T34" s="47"/>
-      <c r="U34" s="48"/>
+      <c r="T34" s="35"/>
+      <c r="U34" s="36"/>
       <c r="V34" s="9"/>
-      <c r="W34" s="47"/>
-      <c r="X34" s="48"/>
+      <c r="W34" s="35"/>
+      <c r="X34" s="36"/>
       <c r="Y34" s="9"/>
-      <c r="Z34" s="47"/>
-      <c r="AA34" s="48"/>
+      <c r="Z34" s="35"/>
+      <c r="AA34" s="36"/>
       <c r="AB34" s="9"/>
       <c r="AC34" s="11"/>
       <c r="AD34" s="9"/>
@@ -6467,45 +6471,45 @@
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
-      <c r="E35" s="39" t="s">
+      <c r="E35" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="F35" s="40"/>
+      <c r="F35" s="38"/>
       <c r="G35" s="9"/>
-      <c r="H35" s="39" t="s">
+      <c r="H35" s="37" t="s">
         <v>145</v>
       </c>
-      <c r="I35" s="40"/>
+      <c r="I35" s="38"/>
       <c r="J35" s="9"/>
-      <c r="K35" s="39" t="s">
+      <c r="K35" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="L35" s="40"/>
+      <c r="L35" s="38"/>
       <c r="M35" s="9"/>
-      <c r="N35" s="39" t="s">
+      <c r="N35" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="O35" s="40"/>
+      <c r="O35" s="38"/>
       <c r="P35" s="9"/>
-      <c r="Q35" s="39" t="s">
+      <c r="Q35" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="R35" s="40"/>
+      <c r="R35" s="38"/>
       <c r="S35" s="9"/>
-      <c r="T35" s="39" t="s">
+      <c r="T35" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="U35" s="40"/>
+      <c r="U35" s="38"/>
       <c r="V35" s="9"/>
-      <c r="W35" s="39" t="s">
+      <c r="W35" s="37" t="s">
         <v>82</v>
       </c>
-      <c r="X35" s="40"/>
+      <c r="X35" s="38"/>
       <c r="Y35" s="9"/>
-      <c r="Z35" s="39" t="s">
+      <c r="Z35" s="37" t="s">
         <v>103</v>
       </c>
-      <c r="AA35" s="40"/>
+      <c r="AA35" s="38"/>
       <c r="AB35" s="9"/>
       <c r="AC35" s="11"/>
       <c r="AD35" s="9"/>
@@ -6518,29 +6522,29 @@
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
-      <c r="E36" s="41"/>
-      <c r="F36" s="42"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="40"/>
       <c r="G36" s="9"/>
-      <c r="H36" s="41"/>
-      <c r="I36" s="42"/>
+      <c r="H36" s="39"/>
+      <c r="I36" s="40"/>
       <c r="J36" s="9"/>
-      <c r="K36" s="41"/>
-      <c r="L36" s="42"/>
+      <c r="K36" s="39"/>
+      <c r="L36" s="40"/>
       <c r="M36" s="9"/>
-      <c r="N36" s="41"/>
-      <c r="O36" s="42"/>
+      <c r="N36" s="39"/>
+      <c r="O36" s="40"/>
       <c r="P36" s="9"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="42"/>
+      <c r="Q36" s="39"/>
+      <c r="R36" s="40"/>
       <c r="S36" s="9"/>
-      <c r="T36" s="41"/>
-      <c r="U36" s="42"/>
+      <c r="T36" s="39"/>
+      <c r="U36" s="40"/>
       <c r="V36" s="9"/>
-      <c r="W36" s="41"/>
-      <c r="X36" s="42"/>
+      <c r="W36" s="39"/>
+      <c r="X36" s="40"/>
       <c r="Y36" s="9"/>
-      <c r="Z36" s="41"/>
-      <c r="AA36" s="42"/>
+      <c r="Z36" s="39"/>
+      <c r="AA36" s="40"/>
       <c r="AB36" s="9"/>
       <c r="AC36" s="11"/>
       <c r="AD36" s="9"/>
@@ -6553,39 +6557,39 @@
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
-      <c r="E37" s="45">
+      <c r="E37" s="41">
         <v>4</v>
       </c>
-      <c r="F37" s="46"/>
+      <c r="F37" s="42"/>
       <c r="G37" s="9"/>
-      <c r="H37" s="45" t="s">
+      <c r="H37" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="I37" s="46"/>
+      <c r="I37" s="42"/>
       <c r="J37" s="9"/>
-      <c r="K37" s="45">
+      <c r="K37" s="41">
         <v>13</v>
       </c>
-      <c r="L37" s="46"/>
+      <c r="L37" s="42"/>
       <c r="M37" s="9"/>
-      <c r="N37" s="45">
+      <c r="N37" s="41">
         <v>19</v>
       </c>
-      <c r="O37" s="46"/>
+      <c r="O37" s="42"/>
       <c r="P37" s="9"/>
-      <c r="Q37" s="45">
+      <c r="Q37" s="41">
         <v>23</v>
       </c>
-      <c r="R37" s="46"/>
+      <c r="R37" s="42"/>
       <c r="S37" s="9"/>
-      <c r="T37" s="45"/>
-      <c r="U37" s="46"/>
+      <c r="T37" s="41"/>
+      <c r="U37" s="42"/>
       <c r="V37" s="9"/>
-      <c r="W37" s="45"/>
-      <c r="X37" s="46"/>
+      <c r="W37" s="41"/>
+      <c r="X37" s="42"/>
       <c r="Y37" s="9"/>
-      <c r="Z37" s="45"/>
-      <c r="AA37" s="46"/>
+      <c r="Z37" s="41"/>
+      <c r="AA37" s="42"/>
       <c r="AB37" s="9"/>
       <c r="AC37" s="11"/>
       <c r="AD37" s="9"/>
@@ -6649,11 +6653,11 @@
       <c r="P39" s="9"/>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
-      <c r="S39" s="36"/>
-      <c r="T39" s="36"/>
-      <c r="U39" s="36"/>
-      <c r="V39" s="36"/>
-      <c r="W39" s="36"/>
+      <c r="S39" s="48"/>
+      <c r="T39" s="48"/>
+      <c r="U39" s="48"/>
+      <c r="V39" s="48"/>
+      <c r="W39" s="48"/>
       <c r="X39" s="9"/>
       <c r="Y39" s="9"/>
       <c r="Z39" s="9"/>
@@ -6795,37 +6799,37 @@
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
       <c r="D43" s="15"/>
-      <c r="E43" s="47" t="s">
+      <c r="E43" s="35" t="s">
         <v>122</v>
       </c>
-      <c r="F43" s="48"/>
+      <c r="F43" s="36"/>
       <c r="G43" s="9"/>
-      <c r="H43" s="47" t="s">
+      <c r="H43" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="I43" s="48"/>
+      <c r="I43" s="36"/>
       <c r="J43" s="9"/>
-      <c r="K43" s="47" t="s">
+      <c r="K43" s="35" t="s">
         <v>163</v>
       </c>
-      <c r="L43" s="48"/>
+      <c r="L43" s="36"/>
       <c r="M43" s="9"/>
-      <c r="N43" s="47" t="s">
+      <c r="N43" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="O43" s="48"/>
+      <c r="O43" s="36"/>
       <c r="P43" s="9"/>
       <c r="Q43" s="17"/>
       <c r="R43" s="9"/>
       <c r="S43" s="9"/>
-      <c r="T43" s="34"/>
-      <c r="U43" s="34"/>
+      <c r="T43" s="43"/>
+      <c r="U43" s="43"/>
       <c r="V43" s="9"/>
-      <c r="W43" s="34"/>
-      <c r="X43" s="34"/>
+      <c r="W43" s="43"/>
+      <c r="X43" s="43"/>
       <c r="Y43" s="9"/>
-      <c r="Z43" s="34"/>
-      <c r="AA43" s="34"/>
+      <c r="Z43" s="43"/>
+      <c r="AA43" s="43"/>
       <c r="AB43" s="9"/>
       <c r="AC43" s="9"/>
       <c r="AD43" s="9"/>
@@ -6840,37 +6844,37 @@
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
       <c r="D44" s="15"/>
-      <c r="E44" s="39" t="s">
+      <c r="E44" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="F44" s="40"/>
+      <c r="F44" s="38"/>
       <c r="G44" s="9"/>
-      <c r="H44" s="39" t="s">
+      <c r="H44" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="I44" s="40"/>
+      <c r="I44" s="38"/>
       <c r="J44" s="9"/>
-      <c r="K44" s="39" t="s">
+      <c r="K44" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="L44" s="40"/>
+      <c r="L44" s="38"/>
       <c r="M44" s="9"/>
-      <c r="N44" s="39" t="s">
+      <c r="N44" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="O44" s="40"/>
+      <c r="O44" s="38"/>
       <c r="P44" s="9"/>
       <c r="Q44" s="17"/>
       <c r="R44" s="9"/>
       <c r="S44" s="9"/>
-      <c r="T44" s="33"/>
-      <c r="U44" s="33"/>
+      <c r="T44" s="45"/>
+      <c r="U44" s="45"/>
       <c r="V44" s="9"/>
-      <c r="W44" s="33"/>
-      <c r="X44" s="33"/>
+      <c r="W44" s="45"/>
+      <c r="X44" s="45"/>
       <c r="Y44" s="9"/>
-      <c r="Z44" s="33"/>
-      <c r="AA44" s="33"/>
+      <c r="Z44" s="45"/>
+      <c r="AA44" s="45"/>
       <c r="AB44" s="11"/>
       <c r="AC44" s="9"/>
       <c r="AD44" s="9"/>
@@ -6885,29 +6889,29 @@
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
       <c r="D45" s="15"/>
-      <c r="E45" s="41"/>
-      <c r="F45" s="42"/>
+      <c r="E45" s="39"/>
+      <c r="F45" s="40"/>
       <c r="G45" s="9"/>
-      <c r="H45" s="41"/>
-      <c r="I45" s="42"/>
+      <c r="H45" s="39"/>
+      <c r="I45" s="40"/>
       <c r="J45" s="9"/>
-      <c r="K45" s="41"/>
-      <c r="L45" s="42"/>
+      <c r="K45" s="39"/>
+      <c r="L45" s="40"/>
       <c r="M45" s="9"/>
-      <c r="N45" s="41"/>
-      <c r="O45" s="42"/>
+      <c r="N45" s="39"/>
+      <c r="O45" s="40"/>
       <c r="P45" s="9"/>
       <c r="Q45" s="17"/>
       <c r="R45" s="9"/>
       <c r="S45" s="9"/>
-      <c r="T45" s="33"/>
-      <c r="U45" s="33"/>
+      <c r="T45" s="45"/>
+      <c r="U45" s="45"/>
       <c r="V45" s="9"/>
-      <c r="W45" s="33"/>
-      <c r="X45" s="33"/>
+      <c r="W45" s="45"/>
+      <c r="X45" s="45"/>
       <c r="Y45" s="9"/>
-      <c r="Z45" s="33"/>
-      <c r="AA45" s="33"/>
+      <c r="Z45" s="45"/>
+      <c r="AA45" s="45"/>
       <c r="AB45" s="28"/>
       <c r="AC45" s="9"/>
       <c r="AD45" s="9"/>
@@ -6922,37 +6926,37 @@
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
       <c r="D46" s="15"/>
-      <c r="E46" s="45" t="s">
+      <c r="E46" s="41" t="s">
         <v>152</v>
       </c>
-      <c r="F46" s="46"/>
+      <c r="F46" s="42"/>
       <c r="G46" s="9"/>
-      <c r="H46" s="45" t="s">
+      <c r="H46" s="41" t="s">
         <v>153</v>
       </c>
-      <c r="I46" s="46"/>
+      <c r="I46" s="42"/>
       <c r="J46" s="9"/>
-      <c r="K46" s="45" t="s">
+      <c r="K46" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="L46" s="46"/>
+      <c r="L46" s="42"/>
       <c r="M46" s="9"/>
-      <c r="N46" s="45" t="s">
+      <c r="N46" s="41" t="s">
         <v>160</v>
       </c>
-      <c r="O46" s="46"/>
+      <c r="O46" s="42"/>
       <c r="P46" s="9"/>
       <c r="Q46" s="17"/>
       <c r="R46" s="9"/>
       <c r="S46" s="9"/>
-      <c r="T46" s="35"/>
-      <c r="U46" s="35"/>
+      <c r="T46" s="44"/>
+      <c r="U46" s="44"/>
       <c r="V46" s="9"/>
-      <c r="W46" s="35"/>
-      <c r="X46" s="35"/>
+      <c r="W46" s="44"/>
+      <c r="X46" s="44"/>
       <c r="Y46" s="9"/>
-      <c r="Z46" s="35"/>
-      <c r="AA46" s="35"/>
+      <c r="Z46" s="44"/>
+      <c r="AA46" s="44"/>
       <c r="AB46" s="27"/>
       <c r="AC46" s="9"/>
       <c r="AD46" s="9"/>
@@ -6992,8 +6996,8 @@
       <c r="AA47" s="27"/>
       <c r="AB47" s="27"/>
       <c r="AC47" s="9"/>
-      <c r="AD47" s="34"/>
-      <c r="AE47" s="34"/>
+      <c r="AD47" s="43"/>
+      <c r="AE47" s="43"/>
       <c r="AF47" s="9"/>
       <c r="AG47" s="9"/>
     </row>
@@ -7043,8 +7047,8 @@
       <c r="AA48" s="11"/>
       <c r="AB48" s="29"/>
       <c r="AC48" s="9"/>
-      <c r="AD48" s="33"/>
-      <c r="AE48" s="33"/>
+      <c r="AD48" s="45"/>
+      <c r="AE48" s="45"/>
       <c r="AF48" s="9"/>
       <c r="AG48" s="9"/>
     </row>
@@ -7053,41 +7057,41 @@
       <c r="B49" s="9"/>
       <c r="C49" s="9"/>
       <c r="D49" s="15"/>
-      <c r="E49" s="47" t="s">
+      <c r="E49" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="F49" s="48"/>
+      <c r="F49" s="36"/>
       <c r="G49" s="9"/>
-      <c r="H49" s="47" t="s">
+      <c r="H49" s="35" t="s">
         <v>132</v>
       </c>
-      <c r="I49" s="48"/>
+      <c r="I49" s="36"/>
       <c r="J49" s="9"/>
-      <c r="K49" s="47" t="s">
+      <c r="K49" s="35" t="s">
         <v>135</v>
       </c>
-      <c r="L49" s="48"/>
+      <c r="L49" s="36"/>
       <c r="M49" s="9"/>
-      <c r="N49" s="47" t="s">
+      <c r="N49" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="O49" s="48"/>
+      <c r="O49" s="36"/>
       <c r="P49" s="9"/>
       <c r="Q49" s="17"/>
       <c r="R49" s="9"/>
       <c r="S49" s="9"/>
-      <c r="T49" s="34"/>
-      <c r="U49" s="34"/>
+      <c r="T49" s="43"/>
+      <c r="U49" s="43"/>
       <c r="V49" s="9"/>
-      <c r="W49" s="34"/>
-      <c r="X49" s="34"/>
+      <c r="W49" s="43"/>
+      <c r="X49" s="43"/>
       <c r="Y49" s="9"/>
-      <c r="Z49" s="34"/>
-      <c r="AA49" s="34"/>
+      <c r="Z49" s="43"/>
+      <c r="AA49" s="43"/>
       <c r="AB49" s="9"/>
       <c r="AC49" s="9"/>
-      <c r="AD49" s="33"/>
-      <c r="AE49" s="33"/>
+      <c r="AD49" s="45"/>
+      <c r="AE49" s="45"/>
       <c r="AF49" s="9"/>
       <c r="AG49" s="9"/>
     </row>
@@ -7096,41 +7100,41 @@
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
       <c r="D50" s="15"/>
-      <c r="E50" s="39" t="s">
+      <c r="E50" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="F50" s="40"/>
+      <c r="F50" s="38"/>
       <c r="G50" s="9"/>
-      <c r="H50" s="39" t="s">
+      <c r="H50" s="37" t="s">
         <v>133</v>
       </c>
-      <c r="I50" s="40"/>
+      <c r="I50" s="38"/>
       <c r="J50" s="9"/>
-      <c r="K50" s="39" t="s">
+      <c r="K50" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="L50" s="40"/>
+      <c r="L50" s="38"/>
       <c r="M50" s="9"/>
-      <c r="N50" s="39" t="s">
+      <c r="N50" s="37" t="s">
         <v>129</v>
       </c>
-      <c r="O50" s="40"/>
+      <c r="O50" s="38"/>
       <c r="P50" s="9"/>
       <c r="Q50" s="17"/>
       <c r="R50" s="9"/>
       <c r="S50" s="9"/>
-      <c r="T50" s="33"/>
-      <c r="U50" s="33"/>
+      <c r="T50" s="45"/>
+      <c r="U50" s="45"/>
       <c r="V50" s="9"/>
-      <c r="W50" s="33"/>
-      <c r="X50" s="33"/>
+      <c r="W50" s="45"/>
+      <c r="X50" s="45"/>
       <c r="Y50" s="9"/>
-      <c r="Z50" s="33"/>
-      <c r="AA50" s="33"/>
+      <c r="Z50" s="45"/>
+      <c r="AA50" s="45"/>
       <c r="AB50" s="11"/>
       <c r="AC50" s="9"/>
-      <c r="AD50" s="35"/>
-      <c r="AE50" s="35"/>
+      <c r="AD50" s="44"/>
+      <c r="AE50" s="44"/>
       <c r="AF50" s="9"/>
       <c r="AG50" s="9"/>
     </row>
@@ -7139,29 +7143,29 @@
       <c r="B51" s="9"/>
       <c r="C51" s="9"/>
       <c r="D51" s="15"/>
-      <c r="E51" s="41"/>
-      <c r="F51" s="42"/>
+      <c r="E51" s="39"/>
+      <c r="F51" s="40"/>
       <c r="G51" s="9"/>
-      <c r="H51" s="41"/>
-      <c r="I51" s="42"/>
+      <c r="H51" s="39"/>
+      <c r="I51" s="40"/>
       <c r="J51" s="9"/>
-      <c r="K51" s="41"/>
-      <c r="L51" s="42"/>
+      <c r="K51" s="39"/>
+      <c r="L51" s="40"/>
       <c r="M51" s="9"/>
-      <c r="N51" s="41"/>
-      <c r="O51" s="42"/>
+      <c r="N51" s="39"/>
+      <c r="O51" s="40"/>
       <c r="P51" s="9"/>
       <c r="Q51" s="17"/>
       <c r="R51" s="9"/>
       <c r="S51" s="9"/>
-      <c r="T51" s="33"/>
-      <c r="U51" s="33"/>
+      <c r="T51" s="45"/>
+      <c r="U51" s="45"/>
       <c r="V51" s="9"/>
-      <c r="W51" s="33"/>
-      <c r="X51" s="33"/>
+      <c r="W51" s="45"/>
+      <c r="X51" s="45"/>
       <c r="Y51" s="9"/>
-      <c r="Z51" s="33"/>
-      <c r="AA51" s="33"/>
+      <c r="Z51" s="45"/>
+      <c r="AA51" s="45"/>
       <c r="AB51" s="28"/>
       <c r="AC51" s="9"/>
       <c r="AD51" s="9"/>
@@ -7174,37 +7178,37 @@
       <c r="B52" s="9"/>
       <c r="C52" s="9"/>
       <c r="D52" s="15"/>
-      <c r="E52" s="45">
+      <c r="E52" s="41">
         <v>18</v>
       </c>
-      <c r="F52" s="46"/>
+      <c r="F52" s="42"/>
       <c r="G52" s="9"/>
-      <c r="H52" s="45">
+      <c r="H52" s="41">
         <v>35</v>
       </c>
-      <c r="I52" s="46"/>
+      <c r="I52" s="42"/>
       <c r="J52" s="9"/>
-      <c r="K52" s="45" t="s">
+      <c r="K52" s="41" t="s">
         <v>159</v>
       </c>
-      <c r="L52" s="46"/>
+      <c r="L52" s="42"/>
       <c r="M52" s="9"/>
-      <c r="N52" s="45">
+      <c r="N52" s="41">
         <v>42</v>
       </c>
-      <c r="O52" s="46"/>
+      <c r="O52" s="42"/>
       <c r="P52" s="9"/>
       <c r="Q52" s="17"/>
       <c r="R52" s="9"/>
       <c r="S52" s="9"/>
-      <c r="T52" s="35"/>
-      <c r="U52" s="35"/>
+      <c r="T52" s="44"/>
+      <c r="U52" s="44"/>
       <c r="V52" s="9"/>
-      <c r="W52" s="35"/>
-      <c r="X52" s="35"/>
+      <c r="W52" s="44"/>
+      <c r="X52" s="44"/>
       <c r="Y52" s="9"/>
-      <c r="Z52" s="35"/>
-      <c r="AA52" s="35"/>
+      <c r="Z52" s="44"/>
+      <c r="AA52" s="44"/>
       <c r="AB52" s="27"/>
       <c r="AC52" s="9"/>
       <c r="AD52" s="9"/>
@@ -7303,34 +7307,34 @@
       <c r="B55" s="9"/>
       <c r="C55" s="9"/>
       <c r="D55" s="15"/>
-      <c r="E55" s="47" t="s">
+      <c r="E55" s="35" t="s">
         <v>165</v>
       </c>
-      <c r="F55" s="48"/>
+      <c r="F55" s="36"/>
       <c r="G55" s="9"/>
-      <c r="H55" s="43" t="s">
+      <c r="H55" s="46" t="s">
         <v>167</v>
       </c>
-      <c r="I55" s="44"/>
+      <c r="I55" s="47"/>
       <c r="J55" s="9"/>
-      <c r="K55" s="43" t="s">
+      <c r="K55" s="46" t="s">
         <v>166</v>
       </c>
-      <c r="L55" s="44"/>
+      <c r="L55" s="47"/>
       <c r="M55" s="9"/>
-      <c r="N55" s="47" t="s">
+      <c r="N55" s="35" t="s">
         <v>164</v>
       </c>
-      <c r="O55" s="48"/>
+      <c r="O55" s="36"/>
       <c r="P55" s="9"/>
       <c r="Q55" s="17"/>
       <c r="R55" s="9"/>
       <c r="S55" s="9"/>
-      <c r="T55" s="34"/>
-      <c r="U55" s="34"/>
+      <c r="T55" s="43"/>
+      <c r="U55" s="43"/>
       <c r="V55" s="9"/>
-      <c r="W55" s="34"/>
-      <c r="X55" s="34"/>
+      <c r="W55" s="43"/>
+      <c r="X55" s="43"/>
       <c r="Y55" s="9"/>
       <c r="Z55" s="9"/>
       <c r="AA55" s="9"/>
@@ -7346,34 +7350,34 @@
       <c r="B56" s="9"/>
       <c r="C56" s="9"/>
       <c r="D56" s="15"/>
-      <c r="E56" s="39" t="s">
+      <c r="E56" s="37" t="s">
         <v>139</v>
       </c>
-      <c r="F56" s="40"/>
+      <c r="F56" s="38"/>
       <c r="G56" s="9"/>
-      <c r="H56" s="39" t="s">
+      <c r="H56" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="I56" s="40"/>
+      <c r="I56" s="38"/>
       <c r="J56" s="9"/>
-      <c r="K56" s="39" t="s">
+      <c r="K56" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="L56" s="40"/>
+      <c r="L56" s="38"/>
       <c r="M56" s="9"/>
-      <c r="N56" s="39" t="s">
+      <c r="N56" s="37" t="s">
         <v>138</v>
       </c>
-      <c r="O56" s="40"/>
+      <c r="O56" s="38"/>
       <c r="P56" s="9"/>
       <c r="Q56" s="17"/>
       <c r="R56" s="9"/>
       <c r="S56" s="9"/>
-      <c r="T56" s="33"/>
-      <c r="U56" s="33"/>
+      <c r="T56" s="45"/>
+      <c r="U56" s="45"/>
       <c r="V56" s="9"/>
-      <c r="W56" s="33"/>
-      <c r="X56" s="33"/>
+      <c r="W56" s="45"/>
+      <c r="X56" s="45"/>
       <c r="Y56" s="9"/>
       <c r="Z56" s="9"/>
       <c r="AA56" s="9"/>
@@ -7389,26 +7393,26 @@
       <c r="B57" s="9"/>
       <c r="C57" s="9"/>
       <c r="D57" s="15"/>
-      <c r="E57" s="41"/>
-      <c r="F57" s="42"/>
+      <c r="E57" s="39"/>
+      <c r="F57" s="40"/>
       <c r="G57" s="9"/>
-      <c r="H57" s="41"/>
-      <c r="I57" s="42"/>
+      <c r="H57" s="39"/>
+      <c r="I57" s="40"/>
       <c r="J57" s="9"/>
-      <c r="K57" s="41"/>
-      <c r="L57" s="42"/>
+      <c r="K57" s="39"/>
+      <c r="L57" s="40"/>
       <c r="M57" s="9"/>
-      <c r="N57" s="41"/>
-      <c r="O57" s="42"/>
+      <c r="N57" s="39"/>
+      <c r="O57" s="40"/>
       <c r="P57" s="9"/>
       <c r="Q57" s="17"/>
       <c r="R57" s="9"/>
       <c r="S57" s="9"/>
-      <c r="T57" s="33"/>
-      <c r="U57" s="33"/>
+      <c r="T57" s="45"/>
+      <c r="U57" s="45"/>
       <c r="V57" s="9"/>
-      <c r="W57" s="33"/>
-      <c r="X57" s="33"/>
+      <c r="W57" s="45"/>
+      <c r="X57" s="45"/>
       <c r="Y57" s="9"/>
       <c r="Z57" s="9"/>
       <c r="AA57" s="9"/>
@@ -7424,33 +7428,33 @@
       <c r="B58" s="9"/>
       <c r="C58" s="9"/>
       <c r="D58" s="15"/>
-      <c r="E58" s="45" t="s">
+      <c r="E58" s="41" t="s">
         <v>161</v>
       </c>
-      <c r="F58" s="46"/>
+      <c r="F58" s="42"/>
       <c r="G58" s="9"/>
-      <c r="H58" s="37" t="s">
+      <c r="H58" s="49" t="s">
         <v>169</v>
       </c>
-      <c r="I58" s="38"/>
+      <c r="I58" s="50"/>
       <c r="J58" s="9"/>
-      <c r="K58" s="37">
+      <c r="K58" s="49">
         <v>43</v>
       </c>
-      <c r="L58" s="38"/>
+      <c r="L58" s="50"/>
       <c r="M58" s="9"/>
-      <c r="N58" s="45" t="s">
+      <c r="N58" s="41" t="s">
         <v>153</v>
       </c>
-      <c r="O58" s="46"/>
+      <c r="O58" s="42"/>
       <c r="P58" s="9"/>
       <c r="Q58" s="17"/>
       <c r="S58" s="9"/>
-      <c r="T58" s="35"/>
-      <c r="U58" s="35"/>
+      <c r="T58" s="44"/>
+      <c r="U58" s="44"/>
       <c r="V58" s="9"/>
-      <c r="W58" s="35"/>
-      <c r="X58" s="35"/>
+      <c r="W58" s="44"/>
+      <c r="X58" s="44"/>
       <c r="Y58" s="9"/>
       <c r="Z58" s="9"/>
       <c r="AA58" s="9"/>
@@ -7498,156 +7502,54 @@
     </row>
   </sheetData>
   <mergeCells count="222">
-    <mergeCell ref="D2:AF2"/>
-    <mergeCell ref="D3:AF3"/>
-    <mergeCell ref="D4:AF4"/>
-    <mergeCell ref="D5:AF5"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="Q7:R7"/>
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="W7:X7"/>
-    <mergeCell ref="Z7:AA7"/>
-    <mergeCell ref="AC7:AD7"/>
-    <mergeCell ref="AC10:AD10"/>
-    <mergeCell ref="B11:C12"/>
-    <mergeCell ref="E11:F12"/>
-    <mergeCell ref="H11:I12"/>
-    <mergeCell ref="K11:L12"/>
-    <mergeCell ref="N11:O12"/>
-    <mergeCell ref="Q11:R12"/>
-    <mergeCell ref="T11:U12"/>
-    <mergeCell ref="W11:X12"/>
-    <mergeCell ref="Z11:AA12"/>
-    <mergeCell ref="AC11:AD12"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="Q10:R10"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="W10:X10"/>
-    <mergeCell ref="Z10:AA10"/>
-    <mergeCell ref="AC13:AD13"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="T16:U16"/>
-    <mergeCell ref="W16:X16"/>
-    <mergeCell ref="Z16:AA16"/>
-    <mergeCell ref="AC16:AD16"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="T13:U13"/>
-    <mergeCell ref="W13:X13"/>
-    <mergeCell ref="Z13:AA13"/>
-    <mergeCell ref="AC17:AD18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="W19:X19"/>
-    <mergeCell ref="Z19:AA19"/>
-    <mergeCell ref="AC19:AD19"/>
-    <mergeCell ref="B17:C18"/>
-    <mergeCell ref="E17:F18"/>
-    <mergeCell ref="H17:I18"/>
-    <mergeCell ref="K17:L18"/>
-    <mergeCell ref="N17:O18"/>
-    <mergeCell ref="Q17:R18"/>
-    <mergeCell ref="T17:U18"/>
-    <mergeCell ref="W17:X18"/>
-    <mergeCell ref="Z17:AA18"/>
-    <mergeCell ref="AC22:AD22"/>
-    <mergeCell ref="B23:C24"/>
-    <mergeCell ref="E23:F24"/>
-    <mergeCell ref="H23:I24"/>
-    <mergeCell ref="K23:L24"/>
-    <mergeCell ref="N23:O24"/>
-    <mergeCell ref="Q23:R24"/>
-    <mergeCell ref="T23:U24"/>
-    <mergeCell ref="W23:X24"/>
-    <mergeCell ref="Z23:AA24"/>
-    <mergeCell ref="AC23:AD24"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="W22:X22"/>
-    <mergeCell ref="Z22:AA22"/>
-    <mergeCell ref="AC25:AD25"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="T28:U28"/>
-    <mergeCell ref="W28:X28"/>
-    <mergeCell ref="Z28:AA28"/>
-    <mergeCell ref="AC28:AD28"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="T25:U25"/>
-    <mergeCell ref="W25:X25"/>
-    <mergeCell ref="Z25:AA25"/>
-    <mergeCell ref="AC29:AD30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="T31:U31"/>
-    <mergeCell ref="W31:X31"/>
-    <mergeCell ref="Z31:AA31"/>
-    <mergeCell ref="AC31:AD31"/>
-    <mergeCell ref="B29:C30"/>
-    <mergeCell ref="E29:F30"/>
-    <mergeCell ref="H29:I30"/>
-    <mergeCell ref="K29:L30"/>
-    <mergeCell ref="N29:O30"/>
-    <mergeCell ref="Q29:R30"/>
-    <mergeCell ref="T29:U30"/>
-    <mergeCell ref="W29:X30"/>
-    <mergeCell ref="Z29:AA30"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="N34:O34"/>
-    <mergeCell ref="Q34:R34"/>
-    <mergeCell ref="T34:U34"/>
-    <mergeCell ref="W34:X34"/>
-    <mergeCell ref="Z34:AA34"/>
-    <mergeCell ref="E35:F36"/>
-    <mergeCell ref="H35:I36"/>
-    <mergeCell ref="K35:L36"/>
-    <mergeCell ref="N35:O36"/>
-    <mergeCell ref="Q35:R36"/>
-    <mergeCell ref="T35:U36"/>
-    <mergeCell ref="W35:X36"/>
-    <mergeCell ref="Z35:AA36"/>
+    <mergeCell ref="Z50:AA51"/>
+    <mergeCell ref="W55:X55"/>
+    <mergeCell ref="W56:X57"/>
+    <mergeCell ref="W58:X58"/>
+    <mergeCell ref="S39:W39"/>
+    <mergeCell ref="K58:L58"/>
+    <mergeCell ref="E50:F51"/>
+    <mergeCell ref="H50:I51"/>
+    <mergeCell ref="K50:L51"/>
+    <mergeCell ref="N50:O51"/>
+    <mergeCell ref="T56:U57"/>
+    <mergeCell ref="T44:U45"/>
+    <mergeCell ref="T49:U49"/>
+    <mergeCell ref="W43:X43"/>
+    <mergeCell ref="W49:X49"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="H56:I57"/>
+    <mergeCell ref="T52:U52"/>
+    <mergeCell ref="W46:X46"/>
+    <mergeCell ref="W52:X52"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="T50:U51"/>
+    <mergeCell ref="W44:X45"/>
+    <mergeCell ref="W50:X51"/>
+    <mergeCell ref="N58:O58"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="E44:F45"/>
+    <mergeCell ref="H44:I45"/>
+    <mergeCell ref="K44:L45"/>
+    <mergeCell ref="N44:O45"/>
+    <mergeCell ref="N56:O57"/>
+    <mergeCell ref="E56:F57"/>
+    <mergeCell ref="AD47:AE47"/>
+    <mergeCell ref="AD48:AE49"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="N49:O49"/>
+    <mergeCell ref="T55:U55"/>
+    <mergeCell ref="K55:L55"/>
+    <mergeCell ref="K56:L57"/>
+    <mergeCell ref="AD50:AE50"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="K52:L52"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="T58:U58"/>
+    <mergeCell ref="T46:U46"/>
     <mergeCell ref="W37:X37"/>
     <mergeCell ref="Z37:AA37"/>
     <mergeCell ref="E43:F43"/>
@@ -7672,54 +7574,156 @@
     <mergeCell ref="Z46:AA46"/>
     <mergeCell ref="Z52:AA52"/>
     <mergeCell ref="Z44:AA45"/>
-    <mergeCell ref="N58:O58"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="E44:F45"/>
-    <mergeCell ref="H44:I45"/>
-    <mergeCell ref="K44:L45"/>
-    <mergeCell ref="N44:O45"/>
-    <mergeCell ref="N56:O57"/>
-    <mergeCell ref="E56:F57"/>
-    <mergeCell ref="AD47:AE47"/>
-    <mergeCell ref="AD48:AE49"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="N49:O49"/>
-    <mergeCell ref="T55:U55"/>
-    <mergeCell ref="K55:L55"/>
-    <mergeCell ref="K56:L57"/>
-    <mergeCell ref="AD50:AE50"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="K52:L52"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="T58:U58"/>
-    <mergeCell ref="T46:U46"/>
-    <mergeCell ref="Z50:AA51"/>
-    <mergeCell ref="W55:X55"/>
-    <mergeCell ref="W56:X57"/>
-    <mergeCell ref="W58:X58"/>
-    <mergeCell ref="S39:W39"/>
-    <mergeCell ref="K58:L58"/>
-    <mergeCell ref="E50:F51"/>
-    <mergeCell ref="H50:I51"/>
-    <mergeCell ref="K50:L51"/>
-    <mergeCell ref="N50:O51"/>
-    <mergeCell ref="T56:U57"/>
-    <mergeCell ref="T44:U45"/>
-    <mergeCell ref="T49:U49"/>
-    <mergeCell ref="W43:X43"/>
-    <mergeCell ref="W49:X49"/>
-    <mergeCell ref="H55:I55"/>
-    <mergeCell ref="H56:I57"/>
-    <mergeCell ref="T52:U52"/>
-    <mergeCell ref="W46:X46"/>
-    <mergeCell ref="W52:X52"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="T50:U51"/>
-    <mergeCell ref="W44:X45"/>
-    <mergeCell ref="W50:X51"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="Q34:R34"/>
+    <mergeCell ref="T34:U34"/>
+    <mergeCell ref="W34:X34"/>
+    <mergeCell ref="Z34:AA34"/>
+    <mergeCell ref="E35:F36"/>
+    <mergeCell ref="H35:I36"/>
+    <mergeCell ref="K35:L36"/>
+    <mergeCell ref="N35:O36"/>
+    <mergeCell ref="Q35:R36"/>
+    <mergeCell ref="T35:U36"/>
+    <mergeCell ref="W35:X36"/>
+    <mergeCell ref="Z35:AA36"/>
+    <mergeCell ref="AC29:AD30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="T31:U31"/>
+    <mergeCell ref="W31:X31"/>
+    <mergeCell ref="Z31:AA31"/>
+    <mergeCell ref="AC31:AD31"/>
+    <mergeCell ref="B29:C30"/>
+    <mergeCell ref="E29:F30"/>
+    <mergeCell ref="H29:I30"/>
+    <mergeCell ref="K29:L30"/>
+    <mergeCell ref="N29:O30"/>
+    <mergeCell ref="Q29:R30"/>
+    <mergeCell ref="T29:U30"/>
+    <mergeCell ref="W29:X30"/>
+    <mergeCell ref="Z29:AA30"/>
+    <mergeCell ref="AC25:AD25"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="T28:U28"/>
+    <mergeCell ref="W28:X28"/>
+    <mergeCell ref="Z28:AA28"/>
+    <mergeCell ref="AC28:AD28"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="T25:U25"/>
+    <mergeCell ref="W25:X25"/>
+    <mergeCell ref="Z25:AA25"/>
+    <mergeCell ref="AC22:AD22"/>
+    <mergeCell ref="B23:C24"/>
+    <mergeCell ref="E23:F24"/>
+    <mergeCell ref="H23:I24"/>
+    <mergeCell ref="K23:L24"/>
+    <mergeCell ref="N23:O24"/>
+    <mergeCell ref="Q23:R24"/>
+    <mergeCell ref="T23:U24"/>
+    <mergeCell ref="W23:X24"/>
+    <mergeCell ref="Z23:AA24"/>
+    <mergeCell ref="AC23:AD24"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="W22:X22"/>
+    <mergeCell ref="Z22:AA22"/>
+    <mergeCell ref="AC17:AD18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="W19:X19"/>
+    <mergeCell ref="Z19:AA19"/>
+    <mergeCell ref="AC19:AD19"/>
+    <mergeCell ref="B17:C18"/>
+    <mergeCell ref="E17:F18"/>
+    <mergeCell ref="H17:I18"/>
+    <mergeCell ref="K17:L18"/>
+    <mergeCell ref="N17:O18"/>
+    <mergeCell ref="Q17:R18"/>
+    <mergeCell ref="T17:U18"/>
+    <mergeCell ref="W17:X18"/>
+    <mergeCell ref="Z17:AA18"/>
+    <mergeCell ref="AC13:AD13"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="W16:X16"/>
+    <mergeCell ref="Z16:AA16"/>
+    <mergeCell ref="AC16:AD16"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="T13:U13"/>
+    <mergeCell ref="W13:X13"/>
+    <mergeCell ref="Z13:AA13"/>
+    <mergeCell ref="AC10:AD10"/>
+    <mergeCell ref="B11:C12"/>
+    <mergeCell ref="E11:F12"/>
+    <mergeCell ref="H11:I12"/>
+    <mergeCell ref="K11:L12"/>
+    <mergeCell ref="N11:O12"/>
+    <mergeCell ref="Q11:R12"/>
+    <mergeCell ref="T11:U12"/>
+    <mergeCell ref="W11:X12"/>
+    <mergeCell ref="Z11:AA12"/>
+    <mergeCell ref="AC11:AD12"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="Q10:R10"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="W10:X10"/>
+    <mergeCell ref="Z10:AA10"/>
+    <mergeCell ref="D2:AF2"/>
+    <mergeCell ref="D3:AF3"/>
+    <mergeCell ref="D4:AF4"/>
+    <mergeCell ref="D5:AF5"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="W7:X7"/>
+    <mergeCell ref="Z7:AA7"/>
+    <mergeCell ref="AC7:AD7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/PensumOriginal1.xlsx
+++ b/PensumOriginal1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AA188EA-9CF0-467C-9953-FE3E81B45420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C00C715F-4CBE-4B62-8B27-7DA2388D77E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="404" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" tabRatio="404" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Actual" sheetId="11" r:id="rId1"/>
@@ -25,6 +25,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1074,17 +1077,23 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1098,35 +1107,29 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2577,9 +2580,11 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="00B050">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
             <a:alpha val="58000"/>
-          </a:srgbClr>
+          </a:schemeClr>
         </a:solidFill>
       </xdr:spPr>
       <xdr:style>
@@ -4316,11 +4321,9 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent1">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
+          <a:srgbClr val="00B050">
             <a:alpha val="58000"/>
-          </a:schemeClr>
+          </a:srgbClr>
         </a:solidFill>
       </xdr:spPr>
       <xdr:style>
@@ -4343,8 +4346,15 @@
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="es-ES" sz="1100"/>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -4419,9 +4429,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4459,9 +4469,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4494,9 +4504,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4529,9 +4556,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4774,111 +4818,111 @@
       <c r="A2" s="9"/>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="49" t="s">
         <v>141</v>
       </c>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
-      <c r="T2" s="33"/>
-      <c r="U2" s="33"/>
-      <c r="V2" s="33"/>
-      <c r="W2" s="33"/>
-      <c r="X2" s="33"/>
-      <c r="Y2" s="33"/>
-      <c r="Z2" s="33"/>
-      <c r="AA2" s="33"/>
-      <c r="AB2" s="33"/>
-      <c r="AC2" s="33"/>
-      <c r="AD2" s="33"/>
-      <c r="AE2" s="33"/>
-      <c r="AF2" s="33"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="49"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="49"/>
+      <c r="S2" s="49"/>
+      <c r="T2" s="49"/>
+      <c r="U2" s="49"/>
+      <c r="V2" s="49"/>
+      <c r="W2" s="49"/>
+      <c r="X2" s="49"/>
+      <c r="Y2" s="49"/>
+      <c r="Z2" s="49"/>
+      <c r="AA2" s="49"/>
+      <c r="AB2" s="49"/>
+      <c r="AC2" s="49"/>
+      <c r="AD2" s="49"/>
+      <c r="AE2" s="49"/>
+      <c r="AF2" s="49"/>
       <c r="AG2" s="9"/>
     </row>
     <row r="3" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="49" t="s">
         <v>142</v>
       </c>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="33"/>
-      <c r="L3" s="33"/>
-      <c r="M3" s="33"/>
-      <c r="N3" s="33"/>
-      <c r="O3" s="33"/>
-      <c r="P3" s="33"/>
-      <c r="Q3" s="33"/>
-      <c r="R3" s="33"/>
-      <c r="S3" s="33"/>
-      <c r="T3" s="33"/>
-      <c r="U3" s="33"/>
-      <c r="V3" s="33"/>
-      <c r="W3" s="33"/>
-      <c r="X3" s="33"/>
-      <c r="Y3" s="33"/>
-      <c r="Z3" s="33"/>
-      <c r="AA3" s="33"/>
-      <c r="AB3" s="33"/>
-      <c r="AC3" s="33"/>
-      <c r="AD3" s="33"/>
-      <c r="AE3" s="33"/>
-      <c r="AF3" s="33"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="49"/>
+      <c r="N3" s="49"/>
+      <c r="O3" s="49"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="49"/>
+      <c r="R3" s="49"/>
+      <c r="S3" s="49"/>
+      <c r="T3" s="49"/>
+      <c r="U3" s="49"/>
+      <c r="V3" s="49"/>
+      <c r="W3" s="49"/>
+      <c r="X3" s="49"/>
+      <c r="Y3" s="49"/>
+      <c r="Z3" s="49"/>
+      <c r="AA3" s="49"/>
+      <c r="AB3" s="49"/>
+      <c r="AC3" s="49"/>
+      <c r="AD3" s="49"/>
+      <c r="AE3" s="49"/>
+      <c r="AF3" s="49"/>
       <c r="AG3" s="9"/>
     </row>
     <row r="4" spans="1:35" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="49" t="s">
         <v>143</v>
       </c>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="33"/>
-      <c r="O4" s="33"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="33"/>
-      <c r="R4" s="33"/>
-      <c r="S4" s="33"/>
-      <c r="T4" s="33"/>
-      <c r="U4" s="33"/>
-      <c r="V4" s="33"/>
-      <c r="W4" s="33"/>
-      <c r="X4" s="33"/>
-      <c r="Y4" s="33"/>
-      <c r="Z4" s="33"/>
-      <c r="AA4" s="33"/>
-      <c r="AB4" s="33"/>
-      <c r="AC4" s="33"/>
-      <c r="AD4" s="33"/>
-      <c r="AE4" s="33"/>
-      <c r="AF4" s="33"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="49"/>
+      <c r="K4" s="49"/>
+      <c r="L4" s="49"/>
+      <c r="M4" s="49"/>
+      <c r="N4" s="49"/>
+      <c r="O4" s="49"/>
+      <c r="P4" s="49"/>
+      <c r="Q4" s="49"/>
+      <c r="R4" s="49"/>
+      <c r="S4" s="49"/>
+      <c r="T4" s="49"/>
+      <c r="U4" s="49"/>
+      <c r="V4" s="49"/>
+      <c r="W4" s="49"/>
+      <c r="X4" s="49"/>
+      <c r="Y4" s="49"/>
+      <c r="Z4" s="49"/>
+      <c r="AA4" s="49"/>
+      <c r="AB4" s="49"/>
+      <c r="AC4" s="49"/>
+      <c r="AD4" s="49"/>
+      <c r="AE4" s="49"/>
+      <c r="AF4" s="49"/>
       <c r="AG4" s="9"/>
       <c r="AI4" s="31"/>
     </row>
@@ -4886,37 +4930,37 @@
       <c r="A5" s="9"/>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="33"/>
-      <c r="M5" s="33"/>
-      <c r="N5" s="33"/>
-      <c r="O5" s="33"/>
-      <c r="P5" s="33"/>
-      <c r="Q5" s="33"/>
-      <c r="R5" s="33"/>
-      <c r="S5" s="33"/>
-      <c r="T5" s="33"/>
-      <c r="U5" s="33"/>
-      <c r="V5" s="33"/>
-      <c r="W5" s="33"/>
-      <c r="X5" s="33"/>
-      <c r="Y5" s="33"/>
-      <c r="Z5" s="33"/>
-      <c r="AA5" s="33"/>
-      <c r="AB5" s="33"/>
-      <c r="AC5" s="33"/>
-      <c r="AD5" s="33"/>
-      <c r="AE5" s="33"/>
-      <c r="AF5" s="33"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
+      <c r="K5" s="49"/>
+      <c r="L5" s="49"/>
+      <c r="M5" s="49"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
+      <c r="W5" s="49"/>
+      <c r="X5" s="49"/>
+      <c r="Y5" s="49"/>
+      <c r="Z5" s="49"/>
+      <c r="AA5" s="49"/>
+      <c r="AB5" s="49"/>
+      <c r="AC5" s="49"/>
+      <c r="AD5" s="49"/>
+      <c r="AE5" s="49"/>
+      <c r="AF5" s="49"/>
       <c r="AG5" s="9"/>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.25">
@@ -4956,55 +5000,55 @@
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" s="9"/>
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="34"/>
+      <c r="C7" s="50"/>
       <c r="D7" s="9"/>
-      <c r="E7" s="34" t="s">
+      <c r="E7" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="34"/>
+      <c r="F7" s="50"/>
       <c r="G7" s="9"/>
-      <c r="H7" s="34" t="s">
+      <c r="H7" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="I7" s="34"/>
+      <c r="I7" s="50"/>
       <c r="J7" s="9"/>
-      <c r="K7" s="34" t="s">
+      <c r="K7" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="L7" s="34"/>
+      <c r="L7" s="50"/>
       <c r="M7" s="9"/>
-      <c r="N7" s="34" t="s">
+      <c r="N7" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="O7" s="34"/>
+      <c r="O7" s="50"/>
       <c r="P7" s="9"/>
-      <c r="Q7" s="34" t="s">
+      <c r="Q7" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="R7" s="34"/>
+      <c r="R7" s="50"/>
       <c r="S7" s="9"/>
-      <c r="T7" s="34" t="s">
+      <c r="T7" s="50" t="s">
         <v>70</v>
       </c>
-      <c r="U7" s="34"/>
+      <c r="U7" s="50"/>
       <c r="V7" s="9"/>
-      <c r="W7" s="34" t="s">
+      <c r="W7" s="50" t="s">
         <v>73</v>
       </c>
-      <c r="X7" s="34"/>
+      <c r="X7" s="50"/>
       <c r="Y7" s="9"/>
-      <c r="Z7" s="34" t="s">
+      <c r="Z7" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="AA7" s="34"/>
+      <c r="AA7" s="50"/>
       <c r="AB7" s="9"/>
-      <c r="AC7" s="34" t="s">
+      <c r="AC7" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="AD7" s="34"/>
+      <c r="AD7" s="50"/>
       <c r="AE7" s="9"/>
       <c r="AF7" s="24" t="s">
         <v>140</v>
@@ -5133,53 +5177,53 @@
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" s="9"/>
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="36"/>
+      <c r="C10" s="48"/>
       <c r="D10" s="9"/>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="36"/>
+      <c r="F10" s="48"/>
       <c r="G10" s="9"/>
-      <c r="H10" s="35" t="s">
+      <c r="H10" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="I10" s="36"/>
+      <c r="I10" s="48"/>
       <c r="J10" s="9"/>
-      <c r="K10" s="35" t="s">
+      <c r="K10" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="L10" s="36"/>
+      <c r="L10" s="48"/>
       <c r="M10" s="9"/>
-      <c r="N10" s="35" t="s">
+      <c r="N10" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="O10" s="36"/>
+      <c r="O10" s="48"/>
       <c r="P10" s="9"/>
-      <c r="Q10" s="35"/>
-      <c r="R10" s="36"/>
+      <c r="Q10" s="47"/>
+      <c r="R10" s="48"/>
       <c r="S10" s="9"/>
-      <c r="T10" s="35" t="s">
+      <c r="T10" s="47" t="s">
         <v>69</v>
       </c>
-      <c r="U10" s="36"/>
+      <c r="U10" s="48"/>
       <c r="V10" s="9"/>
-      <c r="W10" s="35" t="s">
+      <c r="W10" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="X10" s="36"/>
+      <c r="X10" s="48"/>
       <c r="Y10" s="9"/>
-      <c r="Z10" s="35" t="s">
+      <c r="Z10" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="AA10" s="36"/>
+      <c r="AA10" s="48"/>
       <c r="AB10" s="9"/>
-      <c r="AC10" s="35" t="s">
+      <c r="AC10" s="47" t="s">
         <v>91</v>
       </c>
-      <c r="AD10" s="36"/>
+      <c r="AD10" s="48"/>
       <c r="AE10" s="9"/>
       <c r="AF10" s="4" t="s">
         <v>107</v>
@@ -5189,55 +5233,55 @@
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" s="9"/>
-      <c r="B11" s="37" t="s">
+      <c r="B11" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="38"/>
+      <c r="C11" s="40"/>
       <c r="D11" s="9"/>
-      <c r="E11" s="37" t="s">
+      <c r="E11" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="38"/>
+      <c r="F11" s="40"/>
       <c r="G11" s="9"/>
-      <c r="H11" s="37" t="s">
+      <c r="H11" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="I11" s="38"/>
+      <c r="I11" s="40"/>
       <c r="J11" s="9"/>
-      <c r="K11" s="37" t="s">
+      <c r="K11" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="L11" s="38"/>
+      <c r="L11" s="40"/>
       <c r="M11" s="9"/>
-      <c r="N11" s="37" t="s">
+      <c r="N11" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="O11" s="38"/>
+      <c r="O11" s="40"/>
       <c r="P11" s="9"/>
-      <c r="Q11" s="37" t="s">
+      <c r="Q11" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="R11" s="38"/>
+      <c r="R11" s="40"/>
       <c r="S11" s="9"/>
-      <c r="T11" s="37" t="s">
+      <c r="T11" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="U11" s="38"/>
+      <c r="U11" s="40"/>
       <c r="V11" s="9"/>
-      <c r="W11" s="37" t="s">
+      <c r="W11" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="X11" s="38"/>
+      <c r="X11" s="40"/>
       <c r="Y11" s="9"/>
-      <c r="Z11" s="37" t="s">
+      <c r="Z11" s="39" t="s">
         <v>88</v>
       </c>
-      <c r="AA11" s="38"/>
+      <c r="AA11" s="40"/>
       <c r="AB11" s="9"/>
-      <c r="AC11" s="37" t="s">
+      <c r="AC11" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="AD11" s="38"/>
+      <c r="AD11" s="40"/>
       <c r="AE11" s="9"/>
       <c r="AF11" s="4" t="s">
         <v>108</v>
@@ -5251,35 +5295,35 @@
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
-      <c r="B12" s="39"/>
-      <c r="C12" s="40"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="42"/>
       <c r="D12" s="9"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="40"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="42"/>
       <c r="G12" s="9"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="40"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="42"/>
       <c r="J12" s="9"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="40"/>
+      <c r="K12" s="41"/>
+      <c r="L12" s="42"/>
       <c r="M12" s="9"/>
-      <c r="N12" s="39"/>
-      <c r="O12" s="40"/>
+      <c r="N12" s="41"/>
+      <c r="O12" s="42"/>
       <c r="P12" s="9"/>
-      <c r="Q12" s="39"/>
-      <c r="R12" s="40"/>
+      <c r="Q12" s="41"/>
+      <c r="R12" s="42"/>
       <c r="S12" s="9"/>
-      <c r="T12" s="39"/>
-      <c r="U12" s="40"/>
+      <c r="T12" s="41"/>
+      <c r="U12" s="42"/>
       <c r="V12" s="9"/>
-      <c r="W12" s="39"/>
-      <c r="X12" s="40"/>
+      <c r="W12" s="41"/>
+      <c r="X12" s="42"/>
       <c r="Y12" s="9"/>
-      <c r="Z12" s="39"/>
-      <c r="AA12" s="40"/>
+      <c r="Z12" s="41"/>
+      <c r="AA12" s="42"/>
       <c r="AB12" s="9"/>
-      <c r="AC12" s="39"/>
-      <c r="AD12" s="40"/>
+      <c r="AC12" s="41"/>
+      <c r="AD12" s="42"/>
       <c r="AE12" s="9"/>
       <c r="AF12" s="4" t="s">
         <v>109</v>
@@ -5288,53 +5332,53 @@
     </row>
     <row r="13" spans="1:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9"/>
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="42"/>
+      <c r="C13" s="46"/>
       <c r="D13" s="9"/>
-      <c r="E13" s="41" t="s">
+      <c r="E13" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="42"/>
+      <c r="F13" s="46"/>
       <c r="G13" s="9"/>
-      <c r="H13" s="41" t="s">
+      <c r="H13" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="I13" s="42"/>
+      <c r="I13" s="46"/>
       <c r="J13" s="9"/>
-      <c r="K13" s="41">
+      <c r="K13" s="45">
         <v>10</v>
       </c>
-      <c r="L13" s="42"/>
+      <c r="L13" s="46"/>
       <c r="M13" s="9"/>
-      <c r="N13" s="41" t="s">
+      <c r="N13" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="O13" s="42"/>
+      <c r="O13" s="46"/>
       <c r="P13" s="9"/>
-      <c r="Q13" s="41"/>
-      <c r="R13" s="42"/>
+      <c r="Q13" s="45"/>
+      <c r="R13" s="46"/>
       <c r="S13" s="9"/>
-      <c r="T13" s="41">
+      <c r="T13" s="45">
         <v>26</v>
       </c>
-      <c r="U13" s="42"/>
+      <c r="U13" s="46"/>
       <c r="V13" s="9"/>
-      <c r="W13" s="41">
+      <c r="W13" s="45">
         <v>30</v>
       </c>
-      <c r="X13" s="42"/>
+      <c r="X13" s="46"/>
       <c r="Y13" s="9"/>
-      <c r="Z13" s="41" t="s">
+      <c r="Z13" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="AA13" s="42"/>
+      <c r="AA13" s="46"/>
       <c r="AB13" s="9"/>
-      <c r="AC13" s="41" t="s">
+      <c r="AC13" s="45" t="s">
         <v>90</v>
       </c>
-      <c r="AD13" s="42"/>
+      <c r="AD13" s="46"/>
       <c r="AE13" s="9"/>
       <c r="AF13" s="4" t="s">
         <v>110</v>
@@ -5465,53 +5509,53 @@
     </row>
     <row r="16" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
-      <c r="B16" s="35" t="s">
+      <c r="B16" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="C16" s="36"/>
+      <c r="C16" s="48"/>
       <c r="D16" s="9"/>
-      <c r="E16" s="35" t="s">
+      <c r="E16" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="36"/>
+      <c r="F16" s="48"/>
       <c r="G16" s="9"/>
-      <c r="H16" s="35" t="s">
+      <c r="H16" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="36"/>
+      <c r="I16" s="48"/>
       <c r="J16" s="9"/>
-      <c r="K16" s="35" t="s">
+      <c r="K16" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="L16" s="36"/>
+      <c r="L16" s="48"/>
       <c r="M16" s="9"/>
-      <c r="N16" s="35" t="s">
+      <c r="N16" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="O16" s="36"/>
+      <c r="O16" s="48"/>
       <c r="P16" s="9"/>
-      <c r="Q16" s="35" t="s">
+      <c r="Q16" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="R16" s="36"/>
+      <c r="R16" s="48"/>
       <c r="S16" s="9"/>
-      <c r="T16" s="35"/>
-      <c r="U16" s="36"/>
+      <c r="T16" s="47"/>
+      <c r="U16" s="48"/>
       <c r="V16" s="9"/>
-      <c r="W16" s="35" t="s">
+      <c r="W16" s="47" t="s">
         <v>79</v>
       </c>
-      <c r="X16" s="36"/>
+      <c r="X16" s="48"/>
       <c r="Y16" s="9"/>
-      <c r="Z16" s="35" t="s">
+      <c r="Z16" s="47" t="s">
         <v>93</v>
       </c>
-      <c r="AA16" s="36"/>
+      <c r="AA16" s="48"/>
       <c r="AB16" s="9"/>
-      <c r="AC16" s="35" t="s">
+      <c r="AC16" s="47" t="s">
         <v>95</v>
       </c>
-      <c r="AD16" s="36"/>
+      <c r="AD16" s="48"/>
       <c r="AE16" s="9"/>
       <c r="AF16" s="4" t="s">
         <v>112</v>
@@ -5520,55 +5564,55 @@
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
-      <c r="B17" s="37" t="s">
+      <c r="B17" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="38"/>
+      <c r="C17" s="40"/>
       <c r="D17" s="9"/>
-      <c r="E17" s="37" t="s">
+      <c r="E17" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="38"/>
+      <c r="F17" s="40"/>
       <c r="G17" s="9"/>
-      <c r="H17" s="37" t="s">
+      <c r="H17" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="I17" s="38"/>
+      <c r="I17" s="40"/>
       <c r="J17" s="9"/>
-      <c r="K17" s="37" t="s">
+      <c r="K17" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="L17" s="38"/>
+      <c r="L17" s="40"/>
       <c r="M17" s="9"/>
-      <c r="N17" s="37" t="s">
+      <c r="N17" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="O17" s="38"/>
+      <c r="O17" s="40"/>
       <c r="P17" s="9"/>
-      <c r="Q17" s="37" t="s">
+      <c r="Q17" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="R17" s="38"/>
+      <c r="R17" s="40"/>
       <c r="S17" s="9"/>
-      <c r="T17" s="37" t="s">
+      <c r="T17" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="U17" s="38"/>
+      <c r="U17" s="40"/>
       <c r="V17" s="9"/>
-      <c r="W17" s="37" t="s">
+      <c r="W17" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="X17" s="38"/>
+      <c r="X17" s="40"/>
       <c r="Y17" s="9"/>
-      <c r="Z17" s="37" t="s">
+      <c r="Z17" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="AA17" s="38"/>
+      <c r="AA17" s="40"/>
       <c r="AB17" s="9"/>
-      <c r="AC17" s="37" t="s">
+      <c r="AC17" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="AD17" s="38"/>
+      <c r="AD17" s="40"/>
       <c r="AE17" s="9"/>
       <c r="AF17" s="4"/>
       <c r="AG17" s="9"/>
@@ -5579,35 +5623,35 @@
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
-      <c r="B18" s="39"/>
-      <c r="C18" s="40"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="42"/>
       <c r="D18" s="9"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="40"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="42"/>
       <c r="G18" s="9"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="40"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="42"/>
       <c r="J18" s="9"/>
-      <c r="K18" s="39"/>
-      <c r="L18" s="40"/>
+      <c r="K18" s="41"/>
+      <c r="L18" s="42"/>
       <c r="M18" s="9"/>
-      <c r="N18" s="39"/>
-      <c r="O18" s="40"/>
+      <c r="N18" s="41"/>
+      <c r="O18" s="42"/>
       <c r="P18" s="9"/>
-      <c r="Q18" s="39"/>
-      <c r="R18" s="40"/>
+      <c r="Q18" s="41"/>
+      <c r="R18" s="42"/>
       <c r="S18" s="9"/>
-      <c r="T18" s="39"/>
-      <c r="U18" s="40"/>
+      <c r="T18" s="41"/>
+      <c r="U18" s="42"/>
       <c r="V18" s="9"/>
-      <c r="W18" s="39"/>
-      <c r="X18" s="40"/>
+      <c r="W18" s="41"/>
+      <c r="X18" s="42"/>
       <c r="Y18" s="9"/>
-      <c r="Z18" s="39"/>
-      <c r="AA18" s="40"/>
+      <c r="Z18" s="41"/>
+      <c r="AA18" s="42"/>
       <c r="AB18" s="9"/>
-      <c r="AC18" s="39"/>
-      <c r="AD18" s="40"/>
+      <c r="AC18" s="41"/>
+      <c r="AD18" s="42"/>
       <c r="AE18" s="9"/>
       <c r="AF18" s="4" t="s">
         <v>113</v>
@@ -5616,53 +5660,53 @@
     </row>
     <row r="19" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9"/>
-      <c r="B19" s="41" t="s">
+      <c r="B19" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="C19" s="42"/>
+      <c r="C19" s="46"/>
       <c r="D19" s="9"/>
-      <c r="E19" s="41">
+      <c r="E19" s="45">
         <v>2</v>
       </c>
-      <c r="F19" s="42"/>
+      <c r="F19" s="46"/>
       <c r="G19" s="9"/>
-      <c r="H19" s="41">
+      <c r="H19" s="45">
         <v>6</v>
       </c>
-      <c r="I19" s="42"/>
+      <c r="I19" s="46"/>
       <c r="J19" s="9"/>
-      <c r="K19" s="41">
+      <c r="K19" s="45">
         <v>11</v>
       </c>
-      <c r="L19" s="42"/>
+      <c r="L19" s="46"/>
       <c r="M19" s="9"/>
-      <c r="N19" s="41" t="s">
+      <c r="N19" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="O19" s="42"/>
+      <c r="O19" s="46"/>
       <c r="P19" s="9"/>
-      <c r="Q19" s="41" t="s">
+      <c r="Q19" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="R19" s="42"/>
+      <c r="R19" s="46"/>
       <c r="S19" s="9"/>
-      <c r="T19" s="41"/>
-      <c r="U19" s="42"/>
+      <c r="T19" s="45"/>
+      <c r="U19" s="46"/>
       <c r="V19" s="9"/>
-      <c r="W19" s="41">
+      <c r="W19" s="45">
         <v>30</v>
       </c>
-      <c r="X19" s="42"/>
+      <c r="X19" s="46"/>
       <c r="Y19" s="9"/>
-      <c r="Z19" s="41">
+      <c r="Z19" s="45">
         <v>32</v>
       </c>
-      <c r="AA19" s="42"/>
+      <c r="AA19" s="46"/>
       <c r="AB19" s="9"/>
-      <c r="AC19" s="41" t="s">
+      <c r="AC19" s="45" t="s">
         <v>97</v>
       </c>
-      <c r="AD19" s="42"/>
+      <c r="AD19" s="46"/>
       <c r="AE19" s="9"/>
       <c r="AF19" s="4" t="s">
         <v>114</v>
@@ -5791,55 +5835,55 @@
     </row>
     <row r="22" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A22" s="9"/>
-      <c r="B22" s="35" t="s">
+      <c r="B22" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="36"/>
+      <c r="C22" s="48"/>
       <c r="D22" s="9"/>
-      <c r="E22" s="35" t="s">
+      <c r="E22" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="F22" s="36"/>
+      <c r="F22" s="48"/>
       <c r="G22" s="9"/>
-      <c r="H22" s="35" t="s">
+      <c r="H22" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="I22" s="36"/>
+      <c r="I22" s="48"/>
       <c r="J22" s="9"/>
-      <c r="K22" s="35" t="s">
+      <c r="K22" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="L22" s="36"/>
+      <c r="L22" s="48"/>
       <c r="M22" s="9"/>
-      <c r="N22" s="35" t="s">
+      <c r="N22" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="O22" s="36"/>
+      <c r="O22" s="48"/>
       <c r="P22" s="9"/>
-      <c r="Q22" s="35" t="s">
+      <c r="Q22" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="R22" s="36"/>
+      <c r="R22" s="48"/>
       <c r="S22" s="9"/>
-      <c r="T22" s="35" t="s">
+      <c r="T22" s="47" t="s">
         <v>147</v>
       </c>
-      <c r="U22" s="36"/>
+      <c r="U22" s="48"/>
       <c r="V22" s="9"/>
-      <c r="W22" s="35" t="s">
+      <c r="W22" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="X22" s="36"/>
+      <c r="X22" s="48"/>
       <c r="Y22" s="9"/>
-      <c r="Z22" s="35" t="s">
+      <c r="Z22" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="AA22" s="36"/>
+      <c r="AA22" s="48"/>
       <c r="AB22" s="9"/>
-      <c r="AC22" s="35" t="s">
+      <c r="AC22" s="47" t="s">
         <v>148</v>
       </c>
-      <c r="AD22" s="36"/>
+      <c r="AD22" s="48"/>
       <c r="AE22" s="9"/>
       <c r="AF22" s="4" t="s">
         <v>108</v>
@@ -5848,55 +5892,55 @@
     </row>
     <row r="23" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A23" s="9"/>
-      <c r="B23" s="37" t="s">
+      <c r="B23" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="38"/>
+      <c r="C23" s="40"/>
       <c r="D23" s="9"/>
-      <c r="E23" s="37" t="s">
+      <c r="E23" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="F23" s="38"/>
+      <c r="F23" s="40"/>
       <c r="G23" s="9"/>
-      <c r="H23" s="37" t="s">
+      <c r="H23" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="I23" s="38"/>
+      <c r="I23" s="40"/>
       <c r="J23" s="9"/>
-      <c r="K23" s="37" t="s">
+      <c r="K23" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="L23" s="38"/>
+      <c r="L23" s="40"/>
       <c r="M23" s="9"/>
-      <c r="N23" s="37" t="s">
+      <c r="N23" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="O23" s="38"/>
+      <c r="O23" s="40"/>
       <c r="P23" s="9"/>
-      <c r="Q23" s="37" t="s">
+      <c r="Q23" s="39" t="s">
         <v>63</v>
       </c>
-      <c r="R23" s="38"/>
+      <c r="R23" s="40"/>
       <c r="S23" s="9"/>
-      <c r="T23" s="37" t="s">
+      <c r="T23" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="U23" s="38"/>
+      <c r="U23" s="40"/>
       <c r="V23" s="9"/>
-      <c r="W23" s="37" t="s">
+      <c r="W23" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="X23" s="38"/>
+      <c r="X23" s="40"/>
       <c r="Y23" s="9"/>
-      <c r="Z23" s="37" t="s">
+      <c r="Z23" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="AA23" s="38"/>
+      <c r="AA23" s="40"/>
       <c r="AB23" s="9"/>
-      <c r="AC23" s="37" t="s">
+      <c r="AC23" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="AD23" s="38"/>
+      <c r="AD23" s="40"/>
       <c r="AE23" s="9"/>
       <c r="AF23" s="4" t="s">
         <v>109</v>
@@ -5909,35 +5953,35 @@
     </row>
     <row r="24" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A24" s="9"/>
-      <c r="B24" s="39"/>
-      <c r="C24" s="40"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="42"/>
       <c r="D24" s="9"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="40"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="42"/>
       <c r="G24" s="9"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="40"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="42"/>
       <c r="J24" s="9"/>
-      <c r="K24" s="39"/>
-      <c r="L24" s="40"/>
+      <c r="K24" s="41"/>
+      <c r="L24" s="42"/>
       <c r="M24" s="9"/>
-      <c r="N24" s="39"/>
-      <c r="O24" s="40"/>
+      <c r="N24" s="41"/>
+      <c r="O24" s="42"/>
       <c r="P24" s="9"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="40"/>
+      <c r="Q24" s="41"/>
+      <c r="R24" s="42"/>
       <c r="S24" s="9"/>
-      <c r="T24" s="39"/>
-      <c r="U24" s="40"/>
+      <c r="T24" s="41"/>
+      <c r="U24" s="42"/>
       <c r="V24" s="9"/>
-      <c r="W24" s="39"/>
-      <c r="X24" s="40"/>
+      <c r="W24" s="41"/>
+      <c r="X24" s="42"/>
       <c r="Y24" s="9"/>
-      <c r="Z24" s="39"/>
-      <c r="AA24" s="40"/>
+      <c r="Z24" s="41"/>
+      <c r="AA24" s="42"/>
       <c r="AB24" s="9"/>
-      <c r="AC24" s="39"/>
-      <c r="AD24" s="40"/>
+      <c r="AC24" s="41"/>
+      <c r="AD24" s="42"/>
       <c r="AE24" s="9"/>
       <c r="AF24" s="4" t="s">
         <v>113</v>
@@ -5946,55 +5990,55 @@
     </row>
     <row r="25" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9"/>
-      <c r="B25" s="41" t="s">
+      <c r="B25" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="C25" s="42"/>
+      <c r="C25" s="46"/>
       <c r="D25" s="9"/>
-      <c r="E25" s="41">
+      <c r="E25" s="45">
         <v>3</v>
       </c>
-      <c r="F25" s="42"/>
+      <c r="F25" s="46"/>
       <c r="G25" s="9"/>
-      <c r="H25" s="41">
+      <c r="H25" s="45">
         <v>7</v>
       </c>
-      <c r="I25" s="42"/>
+      <c r="I25" s="46"/>
       <c r="J25" s="9"/>
-      <c r="K25" s="41">
+      <c r="K25" s="45">
         <v>12</v>
       </c>
-      <c r="L25" s="42"/>
+      <c r="L25" s="46"/>
       <c r="M25" s="9"/>
-      <c r="N25" s="41" t="s">
+      <c r="N25" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="O25" s="42"/>
+      <c r="O25" s="46"/>
       <c r="P25" s="9"/>
-      <c r="Q25" s="41">
+      <c r="Q25" s="45">
         <v>22</v>
       </c>
-      <c r="R25" s="42"/>
+      <c r="R25" s="46"/>
       <c r="S25" s="9"/>
-      <c r="T25" s="41">
+      <c r="T25" s="45">
         <v>27</v>
       </c>
-      <c r="U25" s="42"/>
+      <c r="U25" s="46"/>
       <c r="V25" s="9"/>
-      <c r="W25" s="41" t="s">
+      <c r="W25" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="X25" s="42"/>
+      <c r="X25" s="46"/>
       <c r="Y25" s="9"/>
-      <c r="Z25" s="41" t="s">
+      <c r="Z25" s="45" t="s">
         <v>100</v>
       </c>
-      <c r="AA25" s="42"/>
+      <c r="AA25" s="46"/>
       <c r="AB25" s="9"/>
-      <c r="AC25" s="41" t="s">
+      <c r="AC25" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="AD25" s="42"/>
+      <c r="AD25" s="46"/>
       <c r="AE25" s="9"/>
       <c r="AF25" s="4" t="s">
         <v>116</v>
@@ -6117,53 +6161,53 @@
     </row>
     <row r="28" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A28" s="9"/>
-      <c r="B28" s="35" t="s">
+      <c r="B28" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="36"/>
+      <c r="C28" s="48"/>
       <c r="D28" s="9"/>
-      <c r="E28" s="35" t="s">
+      <c r="E28" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="F28" s="36"/>
+      <c r="F28" s="48"/>
       <c r="G28" s="9"/>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="I28" s="36"/>
+      <c r="I28" s="48"/>
       <c r="J28" s="9"/>
-      <c r="K28" s="35" t="s">
+      <c r="K28" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="L28" s="36"/>
+      <c r="L28" s="48"/>
       <c r="M28" s="9"/>
-      <c r="N28" s="35" t="s">
+      <c r="N28" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="O28" s="36"/>
+      <c r="O28" s="48"/>
       <c r="P28" s="9"/>
-      <c r="Q28" s="35" t="s">
+      <c r="Q28" s="47" t="s">
         <v>64</v>
       </c>
-      <c r="R28" s="36"/>
+      <c r="R28" s="48"/>
       <c r="S28" s="9"/>
-      <c r="T28" s="35" t="s">
+      <c r="T28" s="47" t="s">
         <v>84</v>
       </c>
-      <c r="U28" s="36"/>
+      <c r="U28" s="48"/>
       <c r="V28" s="9"/>
-      <c r="W28" s="35" t="s">
+      <c r="W28" s="47" t="s">
         <v>84</v>
       </c>
-      <c r="X28" s="36"/>
+      <c r="X28" s="48"/>
       <c r="Y28" s="9"/>
-      <c r="Z28" s="35" t="s">
+      <c r="Z28" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="AA28" s="36"/>
+      <c r="AA28" s="48"/>
       <c r="AB28" s="9"/>
-      <c r="AC28" s="35"/>
-      <c r="AD28" s="36"/>
+      <c r="AC28" s="47"/>
+      <c r="AD28" s="48"/>
       <c r="AE28" s="9"/>
       <c r="AF28" s="4" t="s">
         <v>4</v>
@@ -6172,55 +6216,55 @@
     </row>
     <row r="29" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9"/>
-      <c r="B29" s="37" t="s">
+      <c r="B29" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="38"/>
+      <c r="C29" s="40"/>
       <c r="D29" s="9"/>
-      <c r="E29" s="37" t="s">
+      <c r="E29" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="F29" s="38"/>
+      <c r="F29" s="40"/>
       <c r="G29" s="9"/>
-      <c r="H29" s="37" t="s">
+      <c r="H29" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="I29" s="38"/>
+      <c r="I29" s="40"/>
       <c r="J29" s="9"/>
-      <c r="K29" s="37" t="s">
+      <c r="K29" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="38"/>
+      <c r="L29" s="40"/>
       <c r="M29" s="9"/>
-      <c r="N29" s="37" t="s">
+      <c r="N29" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="O29" s="38"/>
+      <c r="O29" s="40"/>
       <c r="P29" s="9"/>
-      <c r="Q29" s="37" t="s">
+      <c r="Q29" s="39" t="s">
         <v>146</v>
       </c>
-      <c r="R29" s="38"/>
+      <c r="R29" s="40"/>
       <c r="S29" s="9"/>
-      <c r="T29" s="37" t="s">
+      <c r="T29" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="U29" s="38"/>
+      <c r="U29" s="40"/>
       <c r="V29" s="9"/>
-      <c r="W29" s="37" t="s">
+      <c r="W29" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="X29" s="38"/>
+      <c r="X29" s="40"/>
       <c r="Y29" s="9"/>
-      <c r="Z29" s="37" t="s">
+      <c r="Z29" s="39" t="s">
         <v>102</v>
       </c>
-      <c r="AA29" s="38"/>
+      <c r="AA29" s="40"/>
       <c r="AB29" s="9"/>
-      <c r="AC29" s="37" t="s">
+      <c r="AC29" s="39" t="s">
         <v>149</v>
       </c>
-      <c r="AD29" s="38"/>
+      <c r="AD29" s="40"/>
       <c r="AE29" s="9"/>
       <c r="AF29" s="4" t="s">
         <v>119</v>
@@ -6229,35 +6273,35 @@
     </row>
     <row r="30" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A30" s="9"/>
-      <c r="B30" s="39"/>
-      <c r="C30" s="40"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="42"/>
       <c r="D30" s="9"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="40"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="42"/>
       <c r="G30" s="9"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="40"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="42"/>
       <c r="J30" s="9"/>
-      <c r="K30" s="39"/>
-      <c r="L30" s="40"/>
+      <c r="K30" s="41"/>
+      <c r="L30" s="42"/>
       <c r="M30" s="9"/>
-      <c r="N30" s="39"/>
-      <c r="O30" s="40"/>
+      <c r="N30" s="41"/>
+      <c r="O30" s="42"/>
       <c r="P30" s="9"/>
-      <c r="Q30" s="39"/>
-      <c r="R30" s="40"/>
+      <c r="Q30" s="41"/>
+      <c r="R30" s="42"/>
       <c r="S30" s="9"/>
-      <c r="T30" s="39"/>
-      <c r="U30" s="40"/>
+      <c r="T30" s="41"/>
+      <c r="U30" s="42"/>
       <c r="V30" s="9"/>
-      <c r="W30" s="39"/>
-      <c r="X30" s="40"/>
+      <c r="W30" s="41"/>
+      <c r="X30" s="42"/>
       <c r="Y30" s="9"/>
-      <c r="Z30" s="39"/>
-      <c r="AA30" s="40"/>
+      <c r="Z30" s="41"/>
+      <c r="AA30" s="42"/>
       <c r="AB30" s="9"/>
-      <c r="AC30" s="39"/>
-      <c r="AD30" s="40"/>
+      <c r="AC30" s="41"/>
+      <c r="AD30" s="42"/>
       <c r="AE30" s="9"/>
       <c r="AF30" s="4" t="s">
         <v>118</v>
@@ -6266,53 +6310,53 @@
     </row>
     <row r="31" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="9"/>
-      <c r="B31" s="41" t="s">
+      <c r="B31" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="C31" s="42"/>
+      <c r="C31" s="46"/>
       <c r="D31" s="9"/>
-      <c r="E31" s="41">
+      <c r="E31" s="45">
         <v>3</v>
       </c>
-      <c r="F31" s="42"/>
+      <c r="F31" s="46"/>
       <c r="G31" s="9"/>
-      <c r="H31" s="41">
+      <c r="H31" s="45">
         <v>6</v>
       </c>
-      <c r="I31" s="42"/>
+      <c r="I31" s="46"/>
       <c r="J31" s="9"/>
-      <c r="K31" s="41">
+      <c r="K31" s="45">
         <v>12</v>
       </c>
-      <c r="L31" s="42"/>
+      <c r="L31" s="46"/>
       <c r="M31" s="9"/>
-      <c r="N31" s="41">
+      <c r="N31" s="45">
         <v>18</v>
       </c>
-      <c r="O31" s="42"/>
+      <c r="O31" s="46"/>
       <c r="P31" s="9"/>
-      <c r="Q31" s="41">
+      <c r="Q31" s="45">
         <v>12</v>
       </c>
-      <c r="R31" s="42"/>
+      <c r="R31" s="46"/>
       <c r="S31" s="9"/>
-      <c r="T31" s="41" t="s">
+      <c r="T31" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="U31" s="42"/>
+      <c r="U31" s="46"/>
       <c r="V31" s="9"/>
-      <c r="W31" s="41">
+      <c r="W31" s="45">
         <v>33</v>
       </c>
-      <c r="X31" s="42"/>
+      <c r="X31" s="46"/>
       <c r="Y31" s="9"/>
-      <c r="Z31" s="41">
+      <c r="Z31" s="45">
         <v>38</v>
       </c>
-      <c r="AA31" s="42"/>
+      <c r="AA31" s="46"/>
       <c r="AB31" s="9"/>
-      <c r="AC31" s="41"/>
-      <c r="AD31" s="42"/>
+      <c r="AC31" s="45"/>
+      <c r="AD31" s="46"/>
       <c r="AE31" s="9"/>
       <c r="AF31" s="5" t="s">
         <v>162</v>
@@ -6426,39 +6470,39 @@
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
-      <c r="E34" s="35" t="s">
+      <c r="E34" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="F34" s="36"/>
+      <c r="F34" s="48"/>
       <c r="G34" s="9"/>
-      <c r="H34" s="35" t="s">
+      <c r="H34" s="47" t="s">
         <v>144</v>
       </c>
-      <c r="I34" s="36"/>
+      <c r="I34" s="48"/>
       <c r="J34" s="9"/>
-      <c r="K34" s="35" t="s">
+      <c r="K34" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="L34" s="36"/>
+      <c r="L34" s="48"/>
       <c r="M34" s="9"/>
-      <c r="N34" s="35" t="s">
+      <c r="N34" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="O34" s="36"/>
+      <c r="O34" s="48"/>
       <c r="P34" s="9"/>
-      <c r="Q34" s="35" t="s">
+      <c r="Q34" s="47" t="s">
         <v>65</v>
       </c>
-      <c r="R34" s="36"/>
+      <c r="R34" s="48"/>
       <c r="S34" s="9"/>
-      <c r="T34" s="35"/>
-      <c r="U34" s="36"/>
+      <c r="T34" s="47"/>
+      <c r="U34" s="48"/>
       <c r="V34" s="9"/>
-      <c r="W34" s="35"/>
-      <c r="X34" s="36"/>
+      <c r="W34" s="47"/>
+      <c r="X34" s="48"/>
       <c r="Y34" s="9"/>
-      <c r="Z34" s="35"/>
-      <c r="AA34" s="36"/>
+      <c r="Z34" s="47"/>
+      <c r="AA34" s="48"/>
       <c r="AB34" s="9"/>
       <c r="AC34" s="11"/>
       <c r="AD34" s="9"/>
@@ -6471,45 +6515,45 @@
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
-      <c r="E35" s="37" t="s">
+      <c r="E35" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="F35" s="38"/>
+      <c r="F35" s="40"/>
       <c r="G35" s="9"/>
-      <c r="H35" s="37" t="s">
+      <c r="H35" s="39" t="s">
         <v>145</v>
       </c>
-      <c r="I35" s="38"/>
+      <c r="I35" s="40"/>
       <c r="J35" s="9"/>
-      <c r="K35" s="37" t="s">
+      <c r="K35" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="L35" s="38"/>
+      <c r="L35" s="40"/>
       <c r="M35" s="9"/>
-      <c r="N35" s="37" t="s">
+      <c r="N35" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="O35" s="38"/>
+      <c r="O35" s="40"/>
       <c r="P35" s="9"/>
-      <c r="Q35" s="37" t="s">
+      <c r="Q35" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="R35" s="38"/>
+      <c r="R35" s="40"/>
       <c r="S35" s="9"/>
-      <c r="T35" s="37" t="s">
+      <c r="T35" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="U35" s="38"/>
+      <c r="U35" s="40"/>
       <c r="V35" s="9"/>
-      <c r="W35" s="37" t="s">
+      <c r="W35" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="X35" s="38"/>
+      <c r="X35" s="40"/>
       <c r="Y35" s="9"/>
-      <c r="Z35" s="37" t="s">
+      <c r="Z35" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="AA35" s="38"/>
+      <c r="AA35" s="40"/>
       <c r="AB35" s="9"/>
       <c r="AC35" s="11"/>
       <c r="AD35" s="9"/>
@@ -6522,29 +6566,29 @@
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
-      <c r="E36" s="39"/>
-      <c r="F36" s="40"/>
+      <c r="E36" s="41"/>
+      <c r="F36" s="42"/>
       <c r="G36" s="9"/>
-      <c r="H36" s="39"/>
-      <c r="I36" s="40"/>
+      <c r="H36" s="41"/>
+      <c r="I36" s="42"/>
       <c r="J36" s="9"/>
-      <c r="K36" s="39"/>
-      <c r="L36" s="40"/>
+      <c r="K36" s="41"/>
+      <c r="L36" s="42"/>
       <c r="M36" s="9"/>
-      <c r="N36" s="39"/>
-      <c r="O36" s="40"/>
+      <c r="N36" s="41"/>
+      <c r="O36" s="42"/>
       <c r="P36" s="9"/>
-      <c r="Q36" s="39"/>
-      <c r="R36" s="40"/>
+      <c r="Q36" s="41"/>
+      <c r="R36" s="42"/>
       <c r="S36" s="9"/>
-      <c r="T36" s="39"/>
-      <c r="U36" s="40"/>
+      <c r="T36" s="41"/>
+      <c r="U36" s="42"/>
       <c r="V36" s="9"/>
-      <c r="W36" s="39"/>
-      <c r="X36" s="40"/>
+      <c r="W36" s="41"/>
+      <c r="X36" s="42"/>
       <c r="Y36" s="9"/>
-      <c r="Z36" s="39"/>
-      <c r="AA36" s="40"/>
+      <c r="Z36" s="41"/>
+      <c r="AA36" s="42"/>
       <c r="AB36" s="9"/>
       <c r="AC36" s="11"/>
       <c r="AD36" s="9"/>
@@ -6557,39 +6601,39 @@
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
-      <c r="E37" s="41">
+      <c r="E37" s="45">
         <v>4</v>
       </c>
-      <c r="F37" s="42"/>
+      <c r="F37" s="46"/>
       <c r="G37" s="9"/>
-      <c r="H37" s="41" t="s">
+      <c r="H37" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="I37" s="42"/>
+      <c r="I37" s="46"/>
       <c r="J37" s="9"/>
-      <c r="K37" s="41">
+      <c r="K37" s="45">
         <v>13</v>
       </c>
-      <c r="L37" s="42"/>
+      <c r="L37" s="46"/>
       <c r="M37" s="9"/>
-      <c r="N37" s="41">
+      <c r="N37" s="45">
         <v>19</v>
       </c>
-      <c r="O37" s="42"/>
+      <c r="O37" s="46"/>
       <c r="P37" s="9"/>
-      <c r="Q37" s="41">
+      <c r="Q37" s="45">
         <v>23</v>
       </c>
-      <c r="R37" s="42"/>
+      <c r="R37" s="46"/>
       <c r="S37" s="9"/>
-      <c r="T37" s="41"/>
-      <c r="U37" s="42"/>
+      <c r="T37" s="45"/>
+      <c r="U37" s="46"/>
       <c r="V37" s="9"/>
-      <c r="W37" s="41"/>
-      <c r="X37" s="42"/>
+      <c r="W37" s="45"/>
+      <c r="X37" s="46"/>
       <c r="Y37" s="9"/>
-      <c r="Z37" s="41"/>
-      <c r="AA37" s="42"/>
+      <c r="Z37" s="45"/>
+      <c r="AA37" s="46"/>
       <c r="AB37" s="9"/>
       <c r="AC37" s="11"/>
       <c r="AD37" s="9"/>
@@ -6653,11 +6697,11 @@
       <c r="P39" s="9"/>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
-      <c r="S39" s="48"/>
-      <c r="T39" s="48"/>
-      <c r="U39" s="48"/>
-      <c r="V39" s="48"/>
-      <c r="W39" s="48"/>
+      <c r="S39" s="36"/>
+      <c r="T39" s="36"/>
+      <c r="U39" s="36"/>
+      <c r="V39" s="36"/>
+      <c r="W39" s="36"/>
       <c r="X39" s="9"/>
       <c r="Y39" s="9"/>
       <c r="Z39" s="9"/>
@@ -6799,37 +6843,37 @@
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
       <c r="D43" s="15"/>
-      <c r="E43" s="35" t="s">
+      <c r="E43" s="47" t="s">
         <v>122</v>
       </c>
-      <c r="F43" s="36"/>
+      <c r="F43" s="48"/>
       <c r="G43" s="9"/>
-      <c r="H43" s="35" t="s">
+      <c r="H43" s="47" t="s">
         <v>130</v>
       </c>
-      <c r="I43" s="36"/>
+      <c r="I43" s="48"/>
       <c r="J43" s="9"/>
-      <c r="K43" s="35" t="s">
+      <c r="K43" s="47" t="s">
         <v>163</v>
       </c>
-      <c r="L43" s="36"/>
+      <c r="L43" s="48"/>
       <c r="M43" s="9"/>
-      <c r="N43" s="35" t="s">
+      <c r="N43" s="47" t="s">
         <v>124</v>
       </c>
-      <c r="O43" s="36"/>
+      <c r="O43" s="48"/>
       <c r="P43" s="9"/>
       <c r="Q43" s="17"/>
       <c r="R43" s="9"/>
       <c r="S43" s="9"/>
-      <c r="T43" s="43"/>
-      <c r="U43" s="43"/>
+      <c r="T43" s="34"/>
+      <c r="U43" s="34"/>
       <c r="V43" s="9"/>
-      <c r="W43" s="43"/>
-      <c r="X43" s="43"/>
+      <c r="W43" s="34"/>
+      <c r="X43" s="34"/>
       <c r="Y43" s="9"/>
-      <c r="Z43" s="43"/>
-      <c r="AA43" s="43"/>
+      <c r="Z43" s="34"/>
+      <c r="AA43" s="34"/>
       <c r="AB43" s="9"/>
       <c r="AC43" s="9"/>
       <c r="AD43" s="9"/>
@@ -6844,37 +6888,37 @@
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
       <c r="D44" s="15"/>
-      <c r="E44" s="37" t="s">
+      <c r="E44" s="39" t="s">
         <v>123</v>
       </c>
-      <c r="F44" s="38"/>
+      <c r="F44" s="40"/>
       <c r="G44" s="9"/>
-      <c r="H44" s="37" t="s">
+      <c r="H44" s="39" t="s">
         <v>131</v>
       </c>
-      <c r="I44" s="38"/>
+      <c r="I44" s="40"/>
       <c r="J44" s="9"/>
-      <c r="K44" s="37" t="s">
+      <c r="K44" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="L44" s="38"/>
+      <c r="L44" s="40"/>
       <c r="M44" s="9"/>
-      <c r="N44" s="37" t="s">
+      <c r="N44" s="39" t="s">
         <v>125</v>
       </c>
-      <c r="O44" s="38"/>
+      <c r="O44" s="40"/>
       <c r="P44" s="9"/>
       <c r="Q44" s="17"/>
       <c r="R44" s="9"/>
       <c r="S44" s="9"/>
-      <c r="T44" s="45"/>
-      <c r="U44" s="45"/>
+      <c r="T44" s="33"/>
+      <c r="U44" s="33"/>
       <c r="V44" s="9"/>
-      <c r="W44" s="45"/>
-      <c r="X44" s="45"/>
+      <c r="W44" s="33"/>
+      <c r="X44" s="33"/>
       <c r="Y44" s="9"/>
-      <c r="Z44" s="45"/>
-      <c r="AA44" s="45"/>
+      <c r="Z44" s="33"/>
+      <c r="AA44" s="33"/>
       <c r="AB44" s="11"/>
       <c r="AC44" s="9"/>
       <c r="AD44" s="9"/>
@@ -6889,29 +6933,29 @@
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
       <c r="D45" s="15"/>
-      <c r="E45" s="39"/>
-      <c r="F45" s="40"/>
+      <c r="E45" s="41"/>
+      <c r="F45" s="42"/>
       <c r="G45" s="9"/>
-      <c r="H45" s="39"/>
-      <c r="I45" s="40"/>
+      <c r="H45" s="41"/>
+      <c r="I45" s="42"/>
       <c r="J45" s="9"/>
-      <c r="K45" s="39"/>
-      <c r="L45" s="40"/>
+      <c r="K45" s="41"/>
+      <c r="L45" s="42"/>
       <c r="M45" s="9"/>
-      <c r="N45" s="39"/>
-      <c r="O45" s="40"/>
+      <c r="N45" s="41"/>
+      <c r="O45" s="42"/>
       <c r="P45" s="9"/>
       <c r="Q45" s="17"/>
       <c r="R45" s="9"/>
       <c r="S45" s="9"/>
-      <c r="T45" s="45"/>
-      <c r="U45" s="45"/>
+      <c r="T45" s="33"/>
+      <c r="U45" s="33"/>
       <c r="V45" s="9"/>
-      <c r="W45" s="45"/>
-      <c r="X45" s="45"/>
+      <c r="W45" s="33"/>
+      <c r="X45" s="33"/>
       <c r="Y45" s="9"/>
-      <c r="Z45" s="45"/>
-      <c r="AA45" s="45"/>
+      <c r="Z45" s="33"/>
+      <c r="AA45" s="33"/>
       <c r="AB45" s="28"/>
       <c r="AC45" s="9"/>
       <c r="AD45" s="9"/>
@@ -6926,37 +6970,37 @@
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
       <c r="D46" s="15"/>
-      <c r="E46" s="41" t="s">
+      <c r="E46" s="45" t="s">
         <v>152</v>
       </c>
-      <c r="F46" s="42"/>
+      <c r="F46" s="46"/>
       <c r="G46" s="9"/>
-      <c r="H46" s="41" t="s">
+      <c r="H46" s="45" t="s">
         <v>153</v>
       </c>
-      <c r="I46" s="42"/>
+      <c r="I46" s="46"/>
       <c r="J46" s="9"/>
-      <c r="K46" s="41" t="s">
+      <c r="K46" s="45" t="s">
         <v>154</v>
       </c>
-      <c r="L46" s="42"/>
+      <c r="L46" s="46"/>
       <c r="M46" s="9"/>
-      <c r="N46" s="41" t="s">
+      <c r="N46" s="45" t="s">
         <v>160</v>
       </c>
-      <c r="O46" s="42"/>
+      <c r="O46" s="46"/>
       <c r="P46" s="9"/>
       <c r="Q46" s="17"/>
       <c r="R46" s="9"/>
       <c r="S46" s="9"/>
-      <c r="T46" s="44"/>
-      <c r="U46" s="44"/>
+      <c r="T46" s="35"/>
+      <c r="U46" s="35"/>
       <c r="V46" s="9"/>
-      <c r="W46" s="44"/>
-      <c r="X46" s="44"/>
+      <c r="W46" s="35"/>
+      <c r="X46" s="35"/>
       <c r="Y46" s="9"/>
-      <c r="Z46" s="44"/>
-      <c r="AA46" s="44"/>
+      <c r="Z46" s="35"/>
+      <c r="AA46" s="35"/>
       <c r="AB46" s="27"/>
       <c r="AC46" s="9"/>
       <c r="AD46" s="9"/>
@@ -6996,8 +7040,8 @@
       <c r="AA47" s="27"/>
       <c r="AB47" s="27"/>
       <c r="AC47" s="9"/>
-      <c r="AD47" s="43"/>
-      <c r="AE47" s="43"/>
+      <c r="AD47" s="34"/>
+      <c r="AE47" s="34"/>
       <c r="AF47" s="9"/>
       <c r="AG47" s="9"/>
     </row>
@@ -7047,8 +7091,8 @@
       <c r="AA48" s="11"/>
       <c r="AB48" s="29"/>
       <c r="AC48" s="9"/>
-      <c r="AD48" s="45"/>
-      <c r="AE48" s="45"/>
+      <c r="AD48" s="33"/>
+      <c r="AE48" s="33"/>
       <c r="AF48" s="9"/>
       <c r="AG48" s="9"/>
     </row>
@@ -7057,41 +7101,41 @@
       <c r="B49" s="9"/>
       <c r="C49" s="9"/>
       <c r="D49" s="15"/>
-      <c r="E49" s="35" t="s">
+      <c r="E49" s="47" t="s">
         <v>126</v>
       </c>
-      <c r="F49" s="36"/>
+      <c r="F49" s="48"/>
       <c r="G49" s="9"/>
-      <c r="H49" s="35" t="s">
+      <c r="H49" s="47" t="s">
         <v>132</v>
       </c>
-      <c r="I49" s="36"/>
+      <c r="I49" s="48"/>
       <c r="J49" s="9"/>
-      <c r="K49" s="35" t="s">
+      <c r="K49" s="47" t="s">
         <v>135</v>
       </c>
-      <c r="L49" s="36"/>
+      <c r="L49" s="48"/>
       <c r="M49" s="9"/>
-      <c r="N49" s="35" t="s">
+      <c r="N49" s="47" t="s">
         <v>128</v>
       </c>
-      <c r="O49" s="36"/>
+      <c r="O49" s="48"/>
       <c r="P49" s="9"/>
       <c r="Q49" s="17"/>
       <c r="R49" s="9"/>
       <c r="S49" s="9"/>
-      <c r="T49" s="43"/>
-      <c r="U49" s="43"/>
+      <c r="T49" s="34"/>
+      <c r="U49" s="34"/>
       <c r="V49" s="9"/>
-      <c r="W49" s="43"/>
-      <c r="X49" s="43"/>
+      <c r="W49" s="34"/>
+      <c r="X49" s="34"/>
       <c r="Y49" s="9"/>
-      <c r="Z49" s="43"/>
-      <c r="AA49" s="43"/>
+      <c r="Z49" s="34"/>
+      <c r="AA49" s="34"/>
       <c r="AB49" s="9"/>
       <c r="AC49" s="9"/>
-      <c r="AD49" s="45"/>
-      <c r="AE49" s="45"/>
+      <c r="AD49" s="33"/>
+      <c r="AE49" s="33"/>
       <c r="AF49" s="9"/>
       <c r="AG49" s="9"/>
     </row>
@@ -7100,41 +7144,41 @@
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
       <c r="D50" s="15"/>
-      <c r="E50" s="37" t="s">
+      <c r="E50" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="F50" s="38"/>
+      <c r="F50" s="40"/>
       <c r="G50" s="9"/>
-      <c r="H50" s="37" t="s">
+      <c r="H50" s="39" t="s">
         <v>133</v>
       </c>
-      <c r="I50" s="38"/>
+      <c r="I50" s="40"/>
       <c r="J50" s="9"/>
-      <c r="K50" s="37" t="s">
+      <c r="K50" s="39" t="s">
         <v>136</v>
       </c>
-      <c r="L50" s="38"/>
+      <c r="L50" s="40"/>
       <c r="M50" s="9"/>
-      <c r="N50" s="37" t="s">
+      <c r="N50" s="39" t="s">
         <v>129</v>
       </c>
-      <c r="O50" s="38"/>
+      <c r="O50" s="40"/>
       <c r="P50" s="9"/>
       <c r="Q50" s="17"/>
       <c r="R50" s="9"/>
       <c r="S50" s="9"/>
-      <c r="T50" s="45"/>
-      <c r="U50" s="45"/>
+      <c r="T50" s="33"/>
+      <c r="U50" s="33"/>
       <c r="V50" s="9"/>
-      <c r="W50" s="45"/>
-      <c r="X50" s="45"/>
+      <c r="W50" s="33"/>
+      <c r="X50" s="33"/>
       <c r="Y50" s="9"/>
-      <c r="Z50" s="45"/>
-      <c r="AA50" s="45"/>
+      <c r="Z50" s="33"/>
+      <c r="AA50" s="33"/>
       <c r="AB50" s="11"/>
       <c r="AC50" s="9"/>
-      <c r="AD50" s="44"/>
-      <c r="AE50" s="44"/>
+      <c r="AD50" s="35"/>
+      <c r="AE50" s="35"/>
       <c r="AF50" s="9"/>
       <c r="AG50" s="9"/>
     </row>
@@ -7143,29 +7187,29 @@
       <c r="B51" s="9"/>
       <c r="C51" s="9"/>
       <c r="D51" s="15"/>
-      <c r="E51" s="39"/>
-      <c r="F51" s="40"/>
+      <c r="E51" s="41"/>
+      <c r="F51" s="42"/>
       <c r="G51" s="9"/>
-      <c r="H51" s="39"/>
-      <c r="I51" s="40"/>
+      <c r="H51" s="41"/>
+      <c r="I51" s="42"/>
       <c r="J51" s="9"/>
-      <c r="K51" s="39"/>
-      <c r="L51" s="40"/>
+      <c r="K51" s="41"/>
+      <c r="L51" s="42"/>
       <c r="M51" s="9"/>
-      <c r="N51" s="39"/>
-      <c r="O51" s="40"/>
+      <c r="N51" s="41"/>
+      <c r="O51" s="42"/>
       <c r="P51" s="9"/>
       <c r="Q51" s="17"/>
       <c r="R51" s="9"/>
       <c r="S51" s="9"/>
-      <c r="T51" s="45"/>
-      <c r="U51" s="45"/>
+      <c r="T51" s="33"/>
+      <c r="U51" s="33"/>
       <c r="V51" s="9"/>
-      <c r="W51" s="45"/>
-      <c r="X51" s="45"/>
+      <c r="W51" s="33"/>
+      <c r="X51" s="33"/>
       <c r="Y51" s="9"/>
-      <c r="Z51" s="45"/>
-      <c r="AA51" s="45"/>
+      <c r="Z51" s="33"/>
+      <c r="AA51" s="33"/>
       <c r="AB51" s="28"/>
       <c r="AC51" s="9"/>
       <c r="AD51" s="9"/>
@@ -7178,37 +7222,37 @@
       <c r="B52" s="9"/>
       <c r="C52" s="9"/>
       <c r="D52" s="15"/>
-      <c r="E52" s="41">
+      <c r="E52" s="45">
         <v>18</v>
       </c>
-      <c r="F52" s="42"/>
+      <c r="F52" s="46"/>
       <c r="G52" s="9"/>
-      <c r="H52" s="41">
+      <c r="H52" s="45">
         <v>35</v>
       </c>
-      <c r="I52" s="42"/>
+      <c r="I52" s="46"/>
       <c r="J52" s="9"/>
-      <c r="K52" s="41" t="s">
+      <c r="K52" s="45" t="s">
         <v>159</v>
       </c>
-      <c r="L52" s="42"/>
+      <c r="L52" s="46"/>
       <c r="M52" s="9"/>
-      <c r="N52" s="41">
+      <c r="N52" s="45">
         <v>42</v>
       </c>
-      <c r="O52" s="42"/>
+      <c r="O52" s="46"/>
       <c r="P52" s="9"/>
       <c r="Q52" s="17"/>
       <c r="R52" s="9"/>
       <c r="S52" s="9"/>
-      <c r="T52" s="44"/>
-      <c r="U52" s="44"/>
+      <c r="T52" s="35"/>
+      <c r="U52" s="35"/>
       <c r="V52" s="9"/>
-      <c r="W52" s="44"/>
-      <c r="X52" s="44"/>
+      <c r="W52" s="35"/>
+      <c r="X52" s="35"/>
       <c r="Y52" s="9"/>
-      <c r="Z52" s="44"/>
-      <c r="AA52" s="44"/>
+      <c r="Z52" s="35"/>
+      <c r="AA52" s="35"/>
       <c r="AB52" s="27"/>
       <c r="AC52" s="9"/>
       <c r="AD52" s="9"/>
@@ -7307,34 +7351,34 @@
       <c r="B55" s="9"/>
       <c r="C55" s="9"/>
       <c r="D55" s="15"/>
-      <c r="E55" s="35" t="s">
+      <c r="E55" s="47" t="s">
         <v>165</v>
       </c>
-      <c r="F55" s="36"/>
+      <c r="F55" s="48"/>
       <c r="G55" s="9"/>
-      <c r="H55" s="46" t="s">
+      <c r="H55" s="43" t="s">
         <v>167</v>
       </c>
-      <c r="I55" s="47"/>
+      <c r="I55" s="44"/>
       <c r="J55" s="9"/>
-      <c r="K55" s="46" t="s">
+      <c r="K55" s="43" t="s">
         <v>166</v>
       </c>
-      <c r="L55" s="47"/>
+      <c r="L55" s="44"/>
       <c r="M55" s="9"/>
-      <c r="N55" s="35" t="s">
+      <c r="N55" s="47" t="s">
         <v>164</v>
       </c>
-      <c r="O55" s="36"/>
+      <c r="O55" s="48"/>
       <c r="P55" s="9"/>
       <c r="Q55" s="17"/>
       <c r="R55" s="9"/>
       <c r="S55" s="9"/>
-      <c r="T55" s="43"/>
-      <c r="U55" s="43"/>
+      <c r="T55" s="34"/>
+      <c r="U55" s="34"/>
       <c r="V55" s="9"/>
-      <c r="W55" s="43"/>
-      <c r="X55" s="43"/>
+      <c r="W55" s="34"/>
+      <c r="X55" s="34"/>
       <c r="Y55" s="9"/>
       <c r="Z55" s="9"/>
       <c r="AA55" s="9"/>
@@ -7350,34 +7394,34 @@
       <c r="B56" s="9"/>
       <c r="C56" s="9"/>
       <c r="D56" s="15"/>
-      <c r="E56" s="37" t="s">
+      <c r="E56" s="39" t="s">
         <v>139</v>
       </c>
-      <c r="F56" s="38"/>
+      <c r="F56" s="40"/>
       <c r="G56" s="9"/>
-      <c r="H56" s="37" t="s">
+      <c r="H56" s="39" t="s">
         <v>168</v>
       </c>
-      <c r="I56" s="38"/>
+      <c r="I56" s="40"/>
       <c r="J56" s="9"/>
-      <c r="K56" s="37" t="s">
+      <c r="K56" s="39" t="s">
         <v>137</v>
       </c>
-      <c r="L56" s="38"/>
+      <c r="L56" s="40"/>
       <c r="M56" s="9"/>
-      <c r="N56" s="37" t="s">
+      <c r="N56" s="39" t="s">
         <v>138</v>
       </c>
-      <c r="O56" s="38"/>
+      <c r="O56" s="40"/>
       <c r="P56" s="9"/>
       <c r="Q56" s="17"/>
       <c r="R56" s="9"/>
       <c r="S56" s="9"/>
-      <c r="T56" s="45"/>
-      <c r="U56" s="45"/>
+      <c r="T56" s="33"/>
+      <c r="U56" s="33"/>
       <c r="V56" s="9"/>
-      <c r="W56" s="45"/>
-      <c r="X56" s="45"/>
+      <c r="W56" s="33"/>
+      <c r="X56" s="33"/>
       <c r="Y56" s="9"/>
       <c r="Z56" s="9"/>
       <c r="AA56" s="9"/>
@@ -7393,26 +7437,26 @@
       <c r="B57" s="9"/>
       <c r="C57" s="9"/>
       <c r="D57" s="15"/>
-      <c r="E57" s="39"/>
-      <c r="F57" s="40"/>
+      <c r="E57" s="41"/>
+      <c r="F57" s="42"/>
       <c r="G57" s="9"/>
-      <c r="H57" s="39"/>
-      <c r="I57" s="40"/>
+      <c r="H57" s="41"/>
+      <c r="I57" s="42"/>
       <c r="J57" s="9"/>
-      <c r="K57" s="39"/>
-      <c r="L57" s="40"/>
+      <c r="K57" s="41"/>
+      <c r="L57" s="42"/>
       <c r="M57" s="9"/>
-      <c r="N57" s="39"/>
-      <c r="O57" s="40"/>
+      <c r="N57" s="41"/>
+      <c r="O57" s="42"/>
       <c r="P57" s="9"/>
       <c r="Q57" s="17"/>
       <c r="R57" s="9"/>
       <c r="S57" s="9"/>
-      <c r="T57" s="45"/>
-      <c r="U57" s="45"/>
+      <c r="T57" s="33"/>
+      <c r="U57" s="33"/>
       <c r="V57" s="9"/>
-      <c r="W57" s="45"/>
-      <c r="X57" s="45"/>
+      <c r="W57" s="33"/>
+      <c r="X57" s="33"/>
       <c r="Y57" s="9"/>
       <c r="Z57" s="9"/>
       <c r="AA57" s="9"/>
@@ -7428,33 +7472,33 @@
       <c r="B58" s="9"/>
       <c r="C58" s="9"/>
       <c r="D58" s="15"/>
-      <c r="E58" s="41" t="s">
+      <c r="E58" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="F58" s="42"/>
+      <c r="F58" s="46"/>
       <c r="G58" s="9"/>
-      <c r="H58" s="49" t="s">
+      <c r="H58" s="37" t="s">
         <v>169</v>
       </c>
-      <c r="I58" s="50"/>
+      <c r="I58" s="38"/>
       <c r="J58" s="9"/>
-      <c r="K58" s="49">
+      <c r="K58" s="37">
         <v>43</v>
       </c>
-      <c r="L58" s="50"/>
+      <c r="L58" s="38"/>
       <c r="M58" s="9"/>
-      <c r="N58" s="41" t="s">
+      <c r="N58" s="45" t="s">
         <v>153</v>
       </c>
-      <c r="O58" s="42"/>
+      <c r="O58" s="46"/>
       <c r="P58" s="9"/>
       <c r="Q58" s="17"/>
       <c r="S58" s="9"/>
-      <c r="T58" s="44"/>
-      <c r="U58" s="44"/>
+      <c r="T58" s="35"/>
+      <c r="U58" s="35"/>
       <c r="V58" s="9"/>
-      <c r="W58" s="44"/>
-      <c r="X58" s="44"/>
+      <c r="W58" s="35"/>
+      <c r="X58" s="35"/>
       <c r="Y58" s="9"/>
       <c r="Z58" s="9"/>
       <c r="AA58" s="9"/>
@@ -7502,6 +7546,204 @@
     </row>
   </sheetData>
   <mergeCells count="222">
+    <mergeCell ref="D2:AF2"/>
+    <mergeCell ref="D3:AF3"/>
+    <mergeCell ref="D4:AF4"/>
+    <mergeCell ref="D5:AF5"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="W7:X7"/>
+    <mergeCell ref="Z7:AA7"/>
+    <mergeCell ref="AC7:AD7"/>
+    <mergeCell ref="AC10:AD10"/>
+    <mergeCell ref="B11:C12"/>
+    <mergeCell ref="E11:F12"/>
+    <mergeCell ref="H11:I12"/>
+    <mergeCell ref="K11:L12"/>
+    <mergeCell ref="N11:O12"/>
+    <mergeCell ref="Q11:R12"/>
+    <mergeCell ref="T11:U12"/>
+    <mergeCell ref="W11:X12"/>
+    <mergeCell ref="Z11:AA12"/>
+    <mergeCell ref="AC11:AD12"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="Q10:R10"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="W10:X10"/>
+    <mergeCell ref="Z10:AA10"/>
+    <mergeCell ref="AC13:AD13"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="W16:X16"/>
+    <mergeCell ref="Z16:AA16"/>
+    <mergeCell ref="AC16:AD16"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="T13:U13"/>
+    <mergeCell ref="W13:X13"/>
+    <mergeCell ref="Z13:AA13"/>
+    <mergeCell ref="AC17:AD18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="W19:X19"/>
+    <mergeCell ref="Z19:AA19"/>
+    <mergeCell ref="AC19:AD19"/>
+    <mergeCell ref="B17:C18"/>
+    <mergeCell ref="E17:F18"/>
+    <mergeCell ref="H17:I18"/>
+    <mergeCell ref="K17:L18"/>
+    <mergeCell ref="N17:O18"/>
+    <mergeCell ref="Q17:R18"/>
+    <mergeCell ref="T17:U18"/>
+    <mergeCell ref="W17:X18"/>
+    <mergeCell ref="Z17:AA18"/>
+    <mergeCell ref="AC22:AD22"/>
+    <mergeCell ref="B23:C24"/>
+    <mergeCell ref="E23:F24"/>
+    <mergeCell ref="H23:I24"/>
+    <mergeCell ref="K23:L24"/>
+    <mergeCell ref="N23:O24"/>
+    <mergeCell ref="Q23:R24"/>
+    <mergeCell ref="T23:U24"/>
+    <mergeCell ref="W23:X24"/>
+    <mergeCell ref="Z23:AA24"/>
+    <mergeCell ref="AC23:AD24"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="W22:X22"/>
+    <mergeCell ref="Z22:AA22"/>
+    <mergeCell ref="AC25:AD25"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="T28:U28"/>
+    <mergeCell ref="W28:X28"/>
+    <mergeCell ref="Z28:AA28"/>
+    <mergeCell ref="AC28:AD28"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="T25:U25"/>
+    <mergeCell ref="W25:X25"/>
+    <mergeCell ref="Z25:AA25"/>
+    <mergeCell ref="AC29:AD30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="T31:U31"/>
+    <mergeCell ref="W31:X31"/>
+    <mergeCell ref="Z31:AA31"/>
+    <mergeCell ref="AC31:AD31"/>
+    <mergeCell ref="B29:C30"/>
+    <mergeCell ref="E29:F30"/>
+    <mergeCell ref="H29:I30"/>
+    <mergeCell ref="K29:L30"/>
+    <mergeCell ref="N29:O30"/>
+    <mergeCell ref="Q29:R30"/>
+    <mergeCell ref="T29:U30"/>
+    <mergeCell ref="W29:X30"/>
+    <mergeCell ref="Z29:AA30"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="Q34:R34"/>
+    <mergeCell ref="T34:U34"/>
+    <mergeCell ref="W34:X34"/>
+    <mergeCell ref="Z34:AA34"/>
+    <mergeCell ref="E35:F36"/>
+    <mergeCell ref="H35:I36"/>
+    <mergeCell ref="K35:L36"/>
+    <mergeCell ref="N35:O36"/>
+    <mergeCell ref="Q35:R36"/>
+    <mergeCell ref="T35:U36"/>
+    <mergeCell ref="W35:X36"/>
+    <mergeCell ref="Z35:AA36"/>
+    <mergeCell ref="W37:X37"/>
+    <mergeCell ref="Z37:AA37"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="N43:O43"/>
+    <mergeCell ref="N55:O55"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="N37:O37"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="T37:U37"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="N46:O46"/>
+    <mergeCell ref="T43:U43"/>
+    <mergeCell ref="Z43:AA43"/>
+    <mergeCell ref="Z49:AA49"/>
+    <mergeCell ref="Z46:AA46"/>
+    <mergeCell ref="Z52:AA52"/>
+    <mergeCell ref="Z44:AA45"/>
+    <mergeCell ref="N58:O58"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="E44:F45"/>
+    <mergeCell ref="H44:I45"/>
+    <mergeCell ref="K44:L45"/>
+    <mergeCell ref="N44:O45"/>
+    <mergeCell ref="N56:O57"/>
+    <mergeCell ref="E56:F57"/>
+    <mergeCell ref="AD47:AE47"/>
+    <mergeCell ref="AD48:AE49"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="N49:O49"/>
+    <mergeCell ref="T55:U55"/>
+    <mergeCell ref="K55:L55"/>
+    <mergeCell ref="K56:L57"/>
+    <mergeCell ref="AD50:AE50"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="K52:L52"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="T58:U58"/>
+    <mergeCell ref="T46:U46"/>
     <mergeCell ref="Z50:AA51"/>
     <mergeCell ref="W55:X55"/>
     <mergeCell ref="W56:X57"/>
@@ -7526,204 +7768,6 @@
     <mergeCell ref="T50:U51"/>
     <mergeCell ref="W44:X45"/>
     <mergeCell ref="W50:X51"/>
-    <mergeCell ref="N58:O58"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="E44:F45"/>
-    <mergeCell ref="H44:I45"/>
-    <mergeCell ref="K44:L45"/>
-    <mergeCell ref="N44:O45"/>
-    <mergeCell ref="N56:O57"/>
-    <mergeCell ref="E56:F57"/>
-    <mergeCell ref="AD47:AE47"/>
-    <mergeCell ref="AD48:AE49"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="N49:O49"/>
-    <mergeCell ref="T55:U55"/>
-    <mergeCell ref="K55:L55"/>
-    <mergeCell ref="K56:L57"/>
-    <mergeCell ref="AD50:AE50"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="K52:L52"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="T58:U58"/>
-    <mergeCell ref="T46:U46"/>
-    <mergeCell ref="W37:X37"/>
-    <mergeCell ref="Z37:AA37"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="K43:L43"/>
-    <mergeCell ref="N43:O43"/>
-    <mergeCell ref="N55:O55"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="N37:O37"/>
-    <mergeCell ref="Q37:R37"/>
-    <mergeCell ref="T37:U37"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="K46:L46"/>
-    <mergeCell ref="N46:O46"/>
-    <mergeCell ref="T43:U43"/>
-    <mergeCell ref="Z43:AA43"/>
-    <mergeCell ref="Z49:AA49"/>
-    <mergeCell ref="Z46:AA46"/>
-    <mergeCell ref="Z52:AA52"/>
-    <mergeCell ref="Z44:AA45"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="N34:O34"/>
-    <mergeCell ref="Q34:R34"/>
-    <mergeCell ref="T34:U34"/>
-    <mergeCell ref="W34:X34"/>
-    <mergeCell ref="Z34:AA34"/>
-    <mergeCell ref="E35:F36"/>
-    <mergeCell ref="H35:I36"/>
-    <mergeCell ref="K35:L36"/>
-    <mergeCell ref="N35:O36"/>
-    <mergeCell ref="Q35:R36"/>
-    <mergeCell ref="T35:U36"/>
-    <mergeCell ref="W35:X36"/>
-    <mergeCell ref="Z35:AA36"/>
-    <mergeCell ref="AC29:AD30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="T31:U31"/>
-    <mergeCell ref="W31:X31"/>
-    <mergeCell ref="Z31:AA31"/>
-    <mergeCell ref="AC31:AD31"/>
-    <mergeCell ref="B29:C30"/>
-    <mergeCell ref="E29:F30"/>
-    <mergeCell ref="H29:I30"/>
-    <mergeCell ref="K29:L30"/>
-    <mergeCell ref="N29:O30"/>
-    <mergeCell ref="Q29:R30"/>
-    <mergeCell ref="T29:U30"/>
-    <mergeCell ref="W29:X30"/>
-    <mergeCell ref="Z29:AA30"/>
-    <mergeCell ref="AC25:AD25"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="T28:U28"/>
-    <mergeCell ref="W28:X28"/>
-    <mergeCell ref="Z28:AA28"/>
-    <mergeCell ref="AC28:AD28"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="T25:U25"/>
-    <mergeCell ref="W25:X25"/>
-    <mergeCell ref="Z25:AA25"/>
-    <mergeCell ref="AC22:AD22"/>
-    <mergeCell ref="B23:C24"/>
-    <mergeCell ref="E23:F24"/>
-    <mergeCell ref="H23:I24"/>
-    <mergeCell ref="K23:L24"/>
-    <mergeCell ref="N23:O24"/>
-    <mergeCell ref="Q23:R24"/>
-    <mergeCell ref="T23:U24"/>
-    <mergeCell ref="W23:X24"/>
-    <mergeCell ref="Z23:AA24"/>
-    <mergeCell ref="AC23:AD24"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="W22:X22"/>
-    <mergeCell ref="Z22:AA22"/>
-    <mergeCell ref="AC17:AD18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="W19:X19"/>
-    <mergeCell ref="Z19:AA19"/>
-    <mergeCell ref="AC19:AD19"/>
-    <mergeCell ref="B17:C18"/>
-    <mergeCell ref="E17:F18"/>
-    <mergeCell ref="H17:I18"/>
-    <mergeCell ref="K17:L18"/>
-    <mergeCell ref="N17:O18"/>
-    <mergeCell ref="Q17:R18"/>
-    <mergeCell ref="T17:U18"/>
-    <mergeCell ref="W17:X18"/>
-    <mergeCell ref="Z17:AA18"/>
-    <mergeCell ref="AC13:AD13"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="T16:U16"/>
-    <mergeCell ref="W16:X16"/>
-    <mergeCell ref="Z16:AA16"/>
-    <mergeCell ref="AC16:AD16"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="T13:U13"/>
-    <mergeCell ref="W13:X13"/>
-    <mergeCell ref="Z13:AA13"/>
-    <mergeCell ref="AC10:AD10"/>
-    <mergeCell ref="B11:C12"/>
-    <mergeCell ref="E11:F12"/>
-    <mergeCell ref="H11:I12"/>
-    <mergeCell ref="K11:L12"/>
-    <mergeCell ref="N11:O12"/>
-    <mergeCell ref="Q11:R12"/>
-    <mergeCell ref="T11:U12"/>
-    <mergeCell ref="W11:X12"/>
-    <mergeCell ref="Z11:AA12"/>
-    <mergeCell ref="AC11:AD12"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="Q10:R10"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="W10:X10"/>
-    <mergeCell ref="Z10:AA10"/>
-    <mergeCell ref="D2:AF2"/>
-    <mergeCell ref="D3:AF3"/>
-    <mergeCell ref="D4:AF4"/>
-    <mergeCell ref="D5:AF5"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="Q7:R7"/>
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="W7:X7"/>
-    <mergeCell ref="Z7:AA7"/>
-    <mergeCell ref="AC7:AD7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
